--- a/002/002_SISMO_VIENTO_SALVADOR_2.1.xlsx
+++ b/002/002_SISMO_VIENTO_SALVADOR_2.1.xlsx
@@ -6480,7 +6480,7 @@
         <v>68</v>
       </c>
       <c r="F137" s="36">
-        <v>0.69136</v>
+        <v>0.69385</v>
       </c>
       <c r="G137" t="s">
         <v>66</v>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="F139" s="52">
         <f>P33*Q85*P55/P99*(P57/MAX(P57,MIN(F137,6*P57)))^(2/3)</f>
-        <v>0.155972442667178</v>
+        <v>0.155599063172964</v>
       </c>
     </row>
     <row r="140" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="F143" s="54">
         <f>MAX(F141,F139)</f>
-        <v>0.155972442667178</v>
+        <v>0.155599063172964</v>
       </c>
     </row>
     <row r="148" spans="2:25" s="39" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -6635,14 +6635,14 @@
         <v>87</v>
       </c>
       <c r="E165" s="82">
-        <v>13076.56</v>
+        <v>13196.88</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>85</v>
       </c>
       <c r="G165" s="55">
         <f>E165/1000</f>
-        <v>13.07656</v>
+        <v>13.19688</v>
       </c>
       <c r="H165" s="1" t="s">
         <v>86</v>
@@ -6653,14 +6653,14 @@
         <v>88</v>
       </c>
       <c r="E166" s="82">
-        <v>13076.56</v>
+        <v>13196.88</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>85</v>
       </c>
       <c r="G166" s="55">
         <f>E166/1000</f>
-        <v>13.07656</v>
+        <v>13.19688</v>
       </c>
       <c r="H166" s="1" t="s">
         <v>86</v>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="G170" s="51">
         <f>G168*G165</f>
-        <v>2.241696</v>
+        <v>2.26232228571429</v>
       </c>
       <c r="H170" s="1" t="s">
         <v>86</v>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="G171" s="51">
         <f>G168*G166</f>
-        <v>2.241696</v>
+        <v>2.26232228571429</v>
       </c>
       <c r="H171" s="1" t="s">
         <v>86</v>
@@ -6826,13 +6826,13 @@
         <v>1</v>
       </c>
       <c r="C177" s="28">
-        <v>1.446</v>
+        <v>1.441</v>
       </c>
       <c r="D177" s="64">
-        <v>0.69136</v>
+        <v>0.69385</v>
       </c>
       <c r="E177" s="28">
-        <v>80.18</v>
+        <v>80.02</v>
       </c>
       <c r="F177" s="28">
         <v>0</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="K177" s="32">
         <f>J177*$K$221*E177/100</f>
-        <v>1637.48579750817</v>
+        <v>1649.25494087403</v>
       </c>
       <c r="L177" s="34">
         <f>J177*$K$222*G177/100</f>
@@ -6875,13 +6875,13 @@
         <v>2</v>
       </c>
       <c r="C178" s="28">
-        <v>2.682</v>
+        <v>2.68</v>
       </c>
       <c r="D178" s="64">
-        <v>0.37285</v>
+        <v>0.37312</v>
       </c>
       <c r="E178" s="28">
-        <v>0.01</v>
+        <v>5.39</v>
       </c>
       <c r="F178" s="28">
         <v>0</v>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="K178" s="32">
         <f>J178*$K$221*E178/100</f>
-        <v>0.2241696</v>
+        <v>121.9391712</v>
       </c>
       <c r="L178" s="34">
         <f>J178*$K$222*G178/100</f>
@@ -6965,13 +6965,13 @@
         <v>4</v>
       </c>
       <c r="C180" s="28">
-        <v>2.689</v>
+        <v>2.682</v>
       </c>
       <c r="D180" s="64">
-        <v>0.3719</v>
+        <v>0.37285</v>
       </c>
       <c r="E180" s="28">
-        <v>5.37</v>
+        <v>0.01</v>
       </c>
       <c r="F180" s="28">
         <v>0</v>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="K180" s="32">
         <f t="shared" ref="K180:K218" si="7">J180*$K$221*E180/100</f>
-        <v>120.3790752</v>
+        <v>0.226232228571429</v>
       </c>
       <c r="L180" s="34">
         <f t="shared" ref="L180:L218" si="8">J180*$K$222*G180/100</f>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="K182" s="32">
         <f t="shared" si="7"/>
-        <v>0.4483392</v>
+        <v>0.452464457142857</v>
       </c>
       <c r="L182" s="34">
         <f t="shared" si="8"/>
@@ -7088,10 +7088,10 @@
         <v>7</v>
       </c>
       <c r="C183" s="28">
-        <v>3.323</v>
+        <v>3.319</v>
       </c>
       <c r="D183" s="64">
-        <v>0.3009</v>
+        <v>0.30132</v>
       </c>
       <c r="E183" s="28">
         <v>0</v>
@@ -7100,7 +7100,7 @@
         <v>0</v>
       </c>
       <c r="G183" s="28">
-        <v>57.3</v>
+        <v>57.6</v>
       </c>
       <c r="H183" s="28" t="s">
         <v>113</v>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="L183" s="34">
         <f t="shared" si="8"/>
-        <v>1284.491808</v>
+        <v>1303.09763657143</v>
       </c>
       <c r="N183" s="10"/>
       <c r="O183" s="26"/>
@@ -7129,13 +7129,13 @@
         <v>8</v>
       </c>
       <c r="C184" s="28">
-        <v>4.2</v>
+        <v>4.199</v>
       </c>
       <c r="D184" s="64">
-        <v>0.23812</v>
+        <v>0.23814</v>
       </c>
       <c r="E184" s="28">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="F184" s="28">
         <v>0</v>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="K184" s="32">
         <f t="shared" si="7"/>
-        <v>10.7601408</v>
+        <v>10.6329147428571</v>
       </c>
       <c r="L184" s="34">
         <f t="shared" si="8"/>
@@ -7170,10 +7170,10 @@
         <v>9</v>
       </c>
       <c r="C185" s="28">
-        <v>4.302</v>
+        <v>4.296</v>
       </c>
       <c r="D185" s="64">
-        <v>0.23247</v>
+        <v>0.23279</v>
       </c>
       <c r="E185" s="28">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="G185" s="28">
-        <v>16.22</v>
+        <v>16.34</v>
       </c>
       <c r="H185" s="28" t="s">
         <v>113</v>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="L185" s="34">
         <f t="shared" si="8"/>
-        <v>363.6030912</v>
+        <v>369.663461485714</v>
       </c>
       <c r="N185" s="10"/>
     </row>
@@ -7292,10 +7292,10 @@
         <v>12</v>
       </c>
       <c r="C188" s="28">
-        <v>4.688</v>
+        <v>4.683</v>
       </c>
       <c r="D188" s="64">
-        <v>0.21329</v>
+        <v>0.21355</v>
       </c>
       <c r="E188" s="28">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="G188" s="28">
-        <v>14.55</v>
+        <v>14.04</v>
       </c>
       <c r="H188" s="28" t="s">
         <v>113</v>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="L188" s="34">
         <f t="shared" si="8"/>
-        <v>326.166768</v>
+        <v>317.630048914286</v>
       </c>
       <c r="N188" s="10" t="s">
         <v>114</v>
@@ -7493,10 +7493,10 @@
         <v>15</v>
       </c>
       <c r="C191" s="28">
-        <v>6.624</v>
+        <v>7.039</v>
       </c>
       <c r="D191" s="64">
-        <v>0.15096</v>
+        <v>0.14207</v>
       </c>
       <c r="E191" s="28">
         <v>0</v>
@@ -7512,11 +7512,11 @@
       </c>
       <c r="I191" s="29">
         <f t="shared" si="5"/>
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="J191" s="31">
         <f t="shared" si="6"/>
-        <v>0.142857142857143</v>
+        <v>0.137142857142857</v>
       </c>
       <c r="K191" s="32">
         <f t="shared" si="7"/>
@@ -7557,13 +7557,13 @@
         <v>16</v>
       </c>
       <c r="C192" s="28">
-        <v>6.804</v>
+        <v>7.081</v>
       </c>
       <c r="D192" s="64">
-        <v>0.14697</v>
+        <v>0.14122</v>
       </c>
       <c r="E192" s="28">
-        <v>1.16</v>
+        <v>0.29</v>
       </c>
       <c r="F192" s="28">
         <v>0</v>
@@ -7576,15 +7576,15 @@
       </c>
       <c r="I192" s="29">
         <f t="shared" si="5"/>
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="J192" s="31">
         <f t="shared" si="6"/>
-        <v>0.142857142857143</v>
+        <v>0.137142857142857</v>
       </c>
       <c r="K192" s="32">
         <f t="shared" si="7"/>
-        <v>21.669728</v>
+        <v>5.24858770285714</v>
       </c>
       <c r="L192" s="34">
         <f t="shared" si="8"/>
@@ -7621,13 +7621,13 @@
         <v>17</v>
       </c>
       <c r="C193" s="28">
-        <v>7.118</v>
+        <v>7.14</v>
       </c>
       <c r="D193" s="64">
-        <v>0.1405</v>
+        <v>0.14006</v>
       </c>
       <c r="E193" s="28">
-        <v>0.16</v>
+        <v>0.9</v>
       </c>
       <c r="F193" s="28">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="K193" s="32">
         <f t="shared" si="7"/>
-        <v>2.86937088</v>
+        <v>16.2887204571429</v>
       </c>
       <c r="L193" s="34">
         <f t="shared" si="8"/>
@@ -7810,10 +7810,10 @@
         <v>20</v>
       </c>
       <c r="C196" s="28">
-        <v>7.37</v>
+        <v>7.377</v>
       </c>
       <c r="D196" s="64">
-        <v>0.13568</v>
+        <v>0.13556</v>
       </c>
       <c r="E196" s="28">
         <v>0</v>
@@ -7873,10 +7873,10 @@
         <v>21</v>
       </c>
       <c r="C197" s="28">
-        <v>7.408</v>
+        <v>7.405</v>
       </c>
       <c r="D197" s="64">
-        <v>0.13499</v>
+        <v>0.13504</v>
       </c>
       <c r="E197" s="28">
         <v>0</v>
@@ -7892,11 +7892,11 @@
       </c>
       <c r="I197" s="29">
         <f t="shared" si="5"/>
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="J197" s="31">
         <f t="shared" si="6"/>
-        <v>0.131428571428571</v>
+        <v>0.137142857142857</v>
       </c>
       <c r="K197" s="32">
         <f t="shared" si="7"/>
@@ -7936,13 +7936,13 @@
         <v>22</v>
       </c>
       <c r="C198" s="28">
-        <v>7.429</v>
+        <v>7.428</v>
       </c>
       <c r="D198" s="64">
-        <v>0.13461</v>
+        <v>0.13463</v>
       </c>
       <c r="E198" s="28">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
       <c r="F198" s="28">
         <v>0</v>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="K198" s="32">
         <f t="shared" si="7"/>
-        <v>33.34149184</v>
+        <v>36.5968335085714</v>
       </c>
       <c r="L198" s="34">
         <f t="shared" si="8"/>
@@ -7999,10 +7999,10 @@
         <v>23</v>
       </c>
       <c r="C199" s="28">
-        <v>7.499</v>
+        <v>7.498</v>
       </c>
       <c r="D199" s="64">
-        <v>0.13335</v>
+        <v>0.13336</v>
       </c>
       <c r="E199" s="28">
         <v>0</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="L199" s="34">
         <f t="shared" si="8"/>
-        <v>1.03118016</v>
+        <v>1.04066825142857</v>
       </c>
       <c r="T199">
         <v>12</v>
@@ -8125,13 +8125,13 @@
         <v>25</v>
       </c>
       <c r="C201" s="28">
-        <v>7.565</v>
+        <v>7.566</v>
       </c>
       <c r="D201" s="64">
-        <v>0.13219</v>
+        <v>0.13217</v>
       </c>
       <c r="E201" s="28">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="F201" s="28">
         <v>0</v>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="K201" s="32">
         <f t="shared" si="7"/>
-        <v>6.0152176</v>
+        <v>5.55023067428571</v>
       </c>
       <c r="L201" s="34">
         <f t="shared" si="8"/>
@@ -8257,7 +8257,7 @@
         <v>0.13181</v>
       </c>
       <c r="E203" s="28">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="F203" s="28">
         <v>0</v>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="K203" s="32">
         <f t="shared" si="7"/>
-        <v>4.296584</v>
+        <v>4.50956242285714</v>
       </c>
       <c r="L203" s="34">
         <f t="shared" si="8"/>
@@ -8378,13 +8378,13 @@
         <v>29</v>
       </c>
       <c r="C205" s="28">
-        <v>7.593</v>
+        <v>7.594</v>
       </c>
       <c r="D205" s="64">
         <v>0.13169</v>
       </c>
       <c r="E205" s="28">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F205" s="28">
         <v>0</v>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="K205" s="32">
         <f t="shared" si="7"/>
-        <v>0.8593168</v>
+        <v>0.693778834285714</v>
       </c>
       <c r="L205" s="34">
         <f t="shared" si="8"/>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="K207" s="32">
         <f t="shared" si="7"/>
-        <v>0.51559008</v>
+        <v>0.520334125714286</v>
       </c>
       <c r="L207" s="34">
         <f t="shared" si="8"/>
@@ -8756,13 +8756,13 @@
         <v>35</v>
       </c>
       <c r="C211" s="28">
-        <v>7.647</v>
+        <v>7.65</v>
       </c>
       <c r="D211" s="64">
-        <v>0.13077</v>
+        <v>0.13072</v>
       </c>
       <c r="E211" s="28">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F211" s="28">
         <v>0</v>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="K211" s="32">
         <f t="shared" si="7"/>
-        <v>0.34372672</v>
+        <v>0.693778834285714</v>
       </c>
       <c r="L211" s="34">
         <f t="shared" si="8"/>
@@ -8846,7 +8846,7 @@
       </c>
       <c r="K212" s="32">
         <f t="shared" si="7"/>
-        <v>7.7338512</v>
+        <v>7.80501188571429</v>
       </c>
       <c r="L212" s="34">
         <f t="shared" si="8"/>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="K213" s="32">
         <f t="shared" si="7"/>
-        <v>7.04639776</v>
+        <v>7.11123305142857</v>
       </c>
       <c r="L213" s="34">
         <f t="shared" si="8"/>
@@ -8945,13 +8945,13 @@
         <v>38</v>
       </c>
       <c r="C214" s="28">
-        <v>8.177</v>
+        <v>8.185</v>
       </c>
       <c r="D214" s="64">
-        <v>0.12229</v>
+        <v>0.12218</v>
       </c>
       <c r="E214" s="28">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="F214" s="28">
         <v>0</v>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="K214" s="32">
         <f t="shared" si="7"/>
-        <v>0.16439104</v>
+        <v>0.497710902857143</v>
       </c>
       <c r="L214" s="34">
         <f t="shared" si="8"/>
@@ -9008,19 +9008,19 @@
         <v>39</v>
       </c>
       <c r="C215" s="28">
-        <v>9.307</v>
+        <v>9.274</v>
       </c>
       <c r="D215" s="64">
-        <v>0.10745</v>
+        <v>0.10783</v>
       </c>
       <c r="E215" s="28">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F215" s="28">
         <v>0</v>
       </c>
       <c r="G215" s="28">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H215" s="28" t="s">
         <v>113</v>
@@ -9035,11 +9035,11 @@
       </c>
       <c r="K215" s="32">
         <f t="shared" si="7"/>
-        <v>0.15691872</v>
+        <v>0.31672512</v>
       </c>
       <c r="L215" s="34">
         <f t="shared" si="8"/>
-        <v>0.62767488</v>
+        <v>0.7918128</v>
       </c>
       <c r="T215">
         <v>30</v>
@@ -9071,19 +9071,19 @@
         <v>40</v>
       </c>
       <c r="C216" s="28">
-        <v>10.102</v>
+        <v>10.051</v>
       </c>
       <c r="D216" s="64">
-        <v>0.09899</v>
+        <v>0.09949</v>
       </c>
       <c r="E216" s="28">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F216" s="28">
         <v>0</v>
       </c>
       <c r="G216" s="28">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="H216" s="28" t="s">
         <v>113</v>
@@ -9098,11 +9098,11 @@
       </c>
       <c r="K216" s="32">
         <f t="shared" si="7"/>
-        <v>0.5977856</v>
+        <v>0.150821485714286</v>
       </c>
       <c r="L216" s="34">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.69189577142857</v>
       </c>
       <c r="T216">
         <v>31</v>
@@ -9134,19 +9134,19 @@
         <v>41</v>
       </c>
       <c r="C217" s="28">
-        <v>10.249</v>
+        <v>10.125</v>
       </c>
       <c r="D217" s="64">
-        <v>0.09757</v>
+        <v>0.09877</v>
       </c>
       <c r="E217" s="28">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="F217" s="28">
         <v>0</v>
       </c>
       <c r="G217" s="28">
-        <v>0.07</v>
+        <v>3.2</v>
       </c>
       <c r="H217" s="28" t="s">
         <v>113</v>
@@ -9161,11 +9161,11 @@
       </c>
       <c r="K217" s="32">
         <f t="shared" si="7"/>
-        <v>1.3450176</v>
+        <v>0.301642971428571</v>
       </c>
       <c r="L217" s="34">
         <f t="shared" si="8"/>
-        <v>1.0461248</v>
+        <v>48.2628754285714</v>
       </c>
       <c r="T217">
         <v>32</v>
@@ -9197,19 +9197,19 @@
         <v>42</v>
       </c>
       <c r="C218" s="28">
-        <v>10.455</v>
+        <v>10.155</v>
       </c>
       <c r="D218" s="64">
-        <v>0.09564</v>
+        <v>0.09847</v>
       </c>
       <c r="E218" s="28">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="F218" s="28">
         <v>0</v>
       </c>
       <c r="G218" s="28">
-        <v>4.46</v>
+        <v>0.78</v>
       </c>
       <c r="H218" s="28" t="s">
         <v>113</v>
@@ -9224,11 +9224,11 @@
       </c>
       <c r="K218" s="32">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.80985782857143</v>
       </c>
       <c r="L218" s="34">
         <f t="shared" si="8"/>
-        <v>66.6530944</v>
+        <v>11.7640758857143</v>
       </c>
       <c r="T218">
         <v>50</v>
@@ -9263,7 +9263,7 @@
       <c r="D219" s="115"/>
       <c r="E219" s="116">
         <f>SUM(E177:E218)</f>
-        <v>91.03</v>
+        <v>90.96</v>
       </c>
       <c r="F219" s="116">
         <f t="shared" ref="F219" si="9">SUM(F177:F218)</f>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="G219" s="116">
         <f>SUM(G177:G218)</f>
-        <v>92.7</v>
+        <v>92.58</v>
       </c>
       <c r="H219" s="140" t="s">
         <v>131</v>
@@ -9280,11 +9280,11 @@
       <c r="J219" s="142"/>
       <c r="K219" s="117">
         <f>SQRT(SUMSQ(K177:K218))</f>
-        <v>1642.47490217752</v>
+        <v>1654.33495229314</v>
       </c>
       <c r="L219" s="117">
         <f>SQRT(SUMSQ(L177:L218))</f>
-        <v>1375.84750607592</v>
+        <v>1392.16807426887</v>
       </c>
       <c r="T219">
         <v>51</v>
@@ -9346,7 +9346,7 @@
       </c>
       <c r="K221" s="30">
         <f>E165</f>
-        <v>13076.56</v>
+        <v>13196.88</v>
       </c>
       <c r="L221" t="s">
         <v>134</v>
@@ -9385,7 +9385,7 @@
       </c>
       <c r="K222" s="30">
         <f>E166</f>
-        <v>13076.56</v>
+        <v>13196.88</v>
       </c>
       <c r="L222" t="s">
         <v>134</v>
@@ -9452,11 +9452,11 @@
       </c>
       <c r="K224" s="30">
         <f>K221*VLOOKUP(MAX(E177:E218),E177:J218,6,0)</f>
-        <v>2042.26215703189</v>
+        <v>2061.05341273936</v>
       </c>
       <c r="L224" s="30">
         <f>K221*VLOOKUP(MAX(G177:G218),G177:J218,4,0)</f>
-        <v>2241.696</v>
+        <v>2262.32228571429</v>
       </c>
       <c r="T224">
         <v>56</v>
@@ -9489,11 +9489,11 @@
       </c>
       <c r="K225" s="30">
         <f>0.9*K224</f>
-        <v>1838.0359413287</v>
+        <v>1854.94807146542</v>
       </c>
       <c r="L225" s="30">
         <f>0.9*L224</f>
-        <v>2017.5264</v>
+        <v>2036.09005714286</v>
       </c>
       <c r="T225">
         <v>57</v>
@@ -9558,11 +9558,11 @@
       </c>
       <c r="K227" s="30">
         <f>K221*G168</f>
-        <v>2241.696</v>
+        <v>2262.32228571429</v>
       </c>
       <c r="L227" s="30">
         <f>K221*G168</f>
-        <v>2241.696</v>
+        <v>2262.32228571429</v>
       </c>
       <c r="T227">
         <v>59</v>
@@ -9595,11 +9595,11 @@
       </c>
       <c r="K228" s="30">
         <f>0.8*K227</f>
-        <v>1793.3568</v>
+        <v>1809.85782857143</v>
       </c>
       <c r="L228" s="30">
         <f>0.8*L227</f>
-        <v>1793.3568</v>
+        <v>1809.85782857143</v>
       </c>
       <c r="T228">
         <v>60</v>
@@ -9688,11 +9688,11 @@
       </c>
       <c r="K231" s="44">
         <f>MAX(K228,K225)</f>
-        <v>1838.0359413287</v>
+        <v>1854.94807146542</v>
       </c>
       <c r="L231" s="44">
         <f>MAX(L228,L225)</f>
-        <v>2017.5264</v>
+        <v>2036.09005714286</v>
       </c>
       <c r="T231">
         <v>63</v>
@@ -9814,11 +9814,11 @@
       </c>
       <c r="K235" s="47">
         <f>K231/1000</f>
-        <v>1.8380359413287</v>
+        <v>1.85494807146542</v>
       </c>
       <c r="L235" s="47">
         <f>L231/1000</f>
-        <v>2.0175264</v>
+        <v>2.03609005714286</v>
       </c>
       <c r="T235">
         <v>67</v>
@@ -9851,11 +9851,11 @@
       </c>
       <c r="K236" s="47">
         <f>K219/1000</f>
-        <v>1.64247490217752</v>
+        <v>1.65433495229314</v>
       </c>
       <c r="L236" s="47">
         <f>L219/1000</f>
-        <v>1.37584750607592</v>
+        <v>1.39216807426887</v>
       </c>
       <c r="T236">
         <v>68</v>
@@ -9925,11 +9925,11 @@
       </c>
       <c r="K238" s="86">
         <f>MAX(K235/K236,1)</f>
-        <v>1.1190648568766</v>
+        <v>1.12126511556454</v>
       </c>
       <c r="L238" s="86">
         <f>MAX(L235/L236,1)</f>
-        <v>1.46638809249596</v>
+        <v>1.46253178389553</v>
       </c>
       <c r="T238">
         <v>70</v>
@@ -9988,11 +9988,11 @@
       </c>
       <c r="K240" s="86">
         <f>IF(K225/K219&lt;1,"N/A",K225/K219)</f>
-        <v>1.1190648568766</v>
+        <v>1.12126511556454</v>
       </c>
       <c r="L240" s="86">
         <f>IF(L225/L219&lt;1,"N/A",L225/L219)</f>
-        <v>1.46638809249596</v>
+        <v>1.46253178389553</v>
       </c>
       <c r="T240">
         <v>72</v>
@@ -10048,11 +10048,11 @@
     <row r="242" spans="2:27" x14ac:dyDescent="0.3">
       <c r="K242" s="53">
         <f>K224/K219</f>
-        <v>1.24340539652956</v>
+        <v>1.24585012840505</v>
       </c>
       <c r="L242" s="53">
         <f>L224/L219</f>
-        <v>1.62932010277329</v>
+        <v>1.62503531543948</v>
       </c>
       <c r="T242">
         <v>74</v>

--- a/002/002_SISMO_VIENTO_SALVADOR_2.1.xlsx
+++ b/002/002_SISMO_VIENTO_SALVADOR_2.1.xlsx
@@ -2330,7 +2330,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CARGAS Y SISMO F1'!$H$251:$H$550</c:f>
+              <c:f>'CARGAS Y SISMO F1'!$H$255:$H$554</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="300"/>
@@ -3239,7 +3239,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CARGAS Y SISMO F1'!$I$251:$I$550</c:f>
+              <c:f>'CARGAS Y SISMO F1'!$I$255:$I$554</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="300"/>
@@ -4459,13 +4459,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>143435</xdr:colOff>
-      <xdr:row>251</xdr:row>
+      <xdr:row>255</xdr:row>
       <xdr:rowOff>123265</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>179294</xdr:colOff>
-      <xdr:row>269</xdr:row>
+      <xdr:row>273</xdr:row>
       <xdr:rowOff>134471</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4935,13 +4935,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>459440</xdr:colOff>
-      <xdr:row>255</xdr:row>
+      <xdr:row>259</xdr:row>
       <xdr:rowOff>179295</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>377985</xdr:colOff>
-      <xdr:row>279</xdr:row>
+      <xdr:row>283</xdr:row>
       <xdr:rowOff>73236</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5889,7 +5889,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B2:AM550"/>
+  <dimension ref="B2:AM554"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.109375" customWidth="1"/>
@@ -6480,7 +6480,7 @@
         <v>68</v>
       </c>
       <c r="F137" s="36">
-        <v>0.69385</v>
+        <v>0.68858</v>
       </c>
       <c r="G137" t="s">
         <v>66</v>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="F139" s="52">
         <f>P33*Q85*P55/P99*(P57/MAX(P57,MIN(F137,6*P57)))^(2/3)</f>
-        <v>0.155599063172964</v>
+        <v>0.156391965113218</v>
       </c>
     </row>
     <row r="140" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="F143" s="54">
         <f>MAX(F141,F139)</f>
-        <v>0.155599063172964</v>
+        <v>0.156391965113218</v>
       </c>
     </row>
     <row r="148" spans="2:25" s="39" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -6635,14 +6635,14 @@
         <v>87</v>
       </c>
       <c r="E165" s="82">
-        <v>13196.88</v>
+        <v>13470.77</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>85</v>
       </c>
       <c r="G165" s="55">
         <f>E165/1000</f>
-        <v>13.19688</v>
+        <v>13.47077</v>
       </c>
       <c r="H165" s="1" t="s">
         <v>86</v>
@@ -6653,14 +6653,14 @@
         <v>88</v>
       </c>
       <c r="E166" s="82">
-        <v>13196.88</v>
+        <v>13470.77</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>85</v>
       </c>
       <c r="G166" s="55">
         <f>E166/1000</f>
-        <v>13.19688</v>
+        <v>13.47077</v>
       </c>
       <c r="H166" s="1" t="s">
         <v>86</v>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="G170" s="51">
         <f>G168*G165</f>
-        <v>2.26232228571429</v>
+        <v>2.30927485714286</v>
       </c>
       <c r="H170" s="1" t="s">
         <v>86</v>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="G171" s="51">
         <f>G168*G166</f>
-        <v>2.26232228571429</v>
+        <v>2.30927485714286</v>
       </c>
       <c r="H171" s="1" t="s">
         <v>86</v>
@@ -6826,13 +6826,13 @@
         <v>1</v>
       </c>
       <c r="C177" s="28">
-        <v>1.441</v>
+        <v>1.452</v>
       </c>
       <c r="D177" s="64">
-        <v>0.69385</v>
+        <v>0.68858</v>
       </c>
       <c r="E177" s="28">
-        <v>80.02</v>
+        <v>77.53</v>
       </c>
       <c r="F177" s="28">
         <v>0</v>
@@ -6848,15 +6848,15 @@
         <v>0.69</v>
       </c>
       <c r="J177" s="31">
-        <f>VLOOKUP(I177,$H$251:$I$550,2,0)</f>
+        <f>VLOOKUP(I177,$H$255:$I$554,2,0)</f>
         <v>0.156177324696395</v>
       </c>
       <c r="K177" s="32">
-        <f>J177*$K$221*E177/100</f>
-        <v>1649.25494087403</v>
+        <f>J177*$K$225*E177/100</f>
+        <v>1631.09848430141</v>
       </c>
       <c r="L177" s="34">
-        <f>J177*$K$222*G177/100</f>
+        <f>J177*$K$226*G177/100</f>
         <v>0</v>
       </c>
       <c r="N177" s="10" t="s">
@@ -6875,13 +6875,13 @@
         <v>2</v>
       </c>
       <c r="C178" s="28">
-        <v>2.68</v>
+        <v>2.682</v>
       </c>
       <c r="D178" s="64">
-        <v>0.37312</v>
+        <v>0.37285</v>
       </c>
       <c r="E178" s="28">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="F178" s="28">
         <v>0</v>
@@ -6897,15 +6897,15 @@
         <v>0.37</v>
       </c>
       <c r="J178" s="31">
-        <f>VLOOKUP(I178,$H$251:$I$550,2,0)</f>
+        <f>VLOOKUP(I178,$H$255:$I$554,2,0)</f>
         <v>0.17142857142857146</v>
       </c>
       <c r="K178" s="32">
-        <f>J178*$K$221*E178/100</f>
-        <v>121.9391712</v>
+        <f>J178*$K$225*E178/100</f>
+        <v>0</v>
       </c>
       <c r="L178" s="34">
-        <f>J178*$K$222*G178/100</f>
+        <f>J178*$K$226*G178/100</f>
         <v>0</v>
       </c>
       <c r="N178" s="10" t="s">
@@ -6930,7 +6930,7 @@
         <v>0.37285</v>
       </c>
       <c r="E179" s="28">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F179" s="28">
         <v>0</v>
@@ -6946,15 +6946,15 @@
         <v>0.37</v>
       </c>
       <c r="J179" s="31">
-        <f t="shared" ref="J179" si="2">VLOOKUP(I179,$H$251:$I$550,2,0)</f>
+        <f t="shared" ref="J179" si="2">VLOOKUP(I179,$H$255:$I$554,2,0)</f>
         <v>0.17142857142857146</v>
       </c>
       <c r="K179" s="32">
-        <f t="shared" ref="K179" si="3">J179*$K$221*E179/100</f>
-        <v>0</v>
+        <f t="shared" ref="K179" si="3">J179*$K$225*E179/100</f>
+        <v>0.230927485714286</v>
       </c>
       <c r="L179" s="34">
-        <f t="shared" ref="L179" si="4">J179*$K$222*G179/100</f>
+        <f t="shared" ref="L179" si="4">J179*$K$226*G179/100</f>
         <v>0</v>
       </c>
       <c r="N179" s="10"/>
@@ -6965,13 +6965,13 @@
         <v>4</v>
       </c>
       <c r="C180" s="28">
-        <v>2.682</v>
+        <v>2.801</v>
       </c>
       <c r="D180" s="64">
-        <v>0.37285</v>
+        <v>0.35706</v>
       </c>
       <c r="E180" s="28">
-        <v>0.01</v>
+        <v>7.97</v>
       </c>
       <c r="F180" s="28">
         <v>0</v>
@@ -6983,19 +6983,19 @@
         <v>113</v>
       </c>
       <c r="I180" s="29">
-        <f t="shared" ref="I180:I218" si="5">ROUND(D180,2)</f>
-        <v>0.37</v>
+        <f t="shared" ref="I180:I222" si="5">ROUND(D180,2)</f>
+        <v>0.36</v>
       </c>
       <c r="J180" s="31">
-        <f t="shared" ref="J180:J218" si="6">VLOOKUP(I180,$H$251:$I$550,2,0)</f>
+        <f t="shared" ref="J180:J222" si="6">VLOOKUP(I180,$H$255:$I$554,2,0)</f>
         <v>0.17142857142857146</v>
       </c>
       <c r="K180" s="32">
-        <f t="shared" ref="K180:K218" si="7">J180*$K$221*E180/100</f>
-        <v>0.226232228571429</v>
+        <f t="shared" ref="K180:K222" si="7">J180*$K$225*E180/100</f>
+        <v>184.049206114286</v>
       </c>
       <c r="L180" s="34">
-        <f t="shared" ref="L180:L218" si="8">J180*$K$222*G180/100</f>
+        <f t="shared" ref="L180:L222" si="8">J180*$K$226*G180/100</f>
         <v>0</v>
       </c>
       <c r="N180" s="10"/>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="K182" s="32">
         <f t="shared" si="7"/>
-        <v>0.452464457142857</v>
+        <v>0.461854971428572</v>
       </c>
       <c r="L182" s="34">
         <f t="shared" si="8"/>
@@ -7088,10 +7088,10 @@
         <v>7</v>
       </c>
       <c r="C183" s="28">
-        <v>3.319</v>
+        <v>3.437</v>
       </c>
       <c r="D183" s="64">
-        <v>0.30132</v>
+        <v>0.29098</v>
       </c>
       <c r="E183" s="28">
         <v>0</v>
@@ -7100,14 +7100,14 @@
         <v>0</v>
       </c>
       <c r="G183" s="28">
-        <v>57.6</v>
+        <v>61.3</v>
       </c>
       <c r="H183" s="28" t="s">
         <v>113</v>
       </c>
       <c r="I183" s="29">
         <f t="shared" si="5"/>
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="J183" s="31">
         <f t="shared" si="6"/>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="L183" s="34">
         <f t="shared" si="8"/>
-        <v>1303.09763657143</v>
+        <v>1415.58548742857</v>
       </c>
       <c r="N183" s="10"/>
       <c r="O183" s="26"/>
@@ -7129,13 +7129,13 @@
         <v>8</v>
       </c>
       <c r="C184" s="28">
-        <v>4.199</v>
+        <v>4.169</v>
       </c>
       <c r="D184" s="64">
-        <v>0.23814</v>
+        <v>0.23988</v>
       </c>
       <c r="E184" s="28">
-        <v>0.47</v>
+        <v>0.71</v>
       </c>
       <c r="F184" s="28">
         <v>0</v>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="K184" s="32">
         <f t="shared" si="7"/>
-        <v>10.6329147428571</v>
+        <v>16.3958514857143</v>
       </c>
       <c r="L184" s="34">
         <f t="shared" si="8"/>
@@ -7170,10 +7170,10 @@
         <v>9</v>
       </c>
       <c r="C185" s="28">
-        <v>4.296</v>
+        <v>4.401</v>
       </c>
       <c r="D185" s="64">
-        <v>0.23279</v>
+        <v>0.2272</v>
       </c>
       <c r="E185" s="28">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="G185" s="28">
-        <v>16.34</v>
+        <v>6.52</v>
       </c>
       <c r="H185" s="28" t="s">
         <v>113</v>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="L185" s="34">
         <f t="shared" si="8"/>
-        <v>369.663461485714</v>
+        <v>150.564720685714</v>
       </c>
       <c r="N185" s="10"/>
     </row>
@@ -7292,10 +7292,10 @@
         <v>12</v>
       </c>
       <c r="C188" s="28">
-        <v>4.683</v>
+        <v>4.806</v>
       </c>
       <c r="D188" s="64">
-        <v>0.21355</v>
+        <v>0.20808</v>
       </c>
       <c r="E188" s="28">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="G188" s="28">
-        <v>14.04</v>
+        <v>18.27</v>
       </c>
       <c r="H188" s="28" t="s">
         <v>113</v>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="L188" s="34">
         <f t="shared" si="8"/>
-        <v>317.630048914286</v>
+        <v>421.9045164</v>
       </c>
       <c r="N188" s="10" t="s">
         <v>114</v>
@@ -7493,10 +7493,10 @@
         <v>15</v>
       </c>
       <c r="C191" s="28">
-        <v>7.039</v>
+        <v>6.105</v>
       </c>
       <c r="D191" s="64">
-        <v>0.14207</v>
+        <v>0.16379</v>
       </c>
       <c r="E191" s="28">
         <v>0</v>
@@ -7512,11 +7512,11 @@
       </c>
       <c r="I191" s="29">
         <f t="shared" si="5"/>
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="J191" s="31">
         <f t="shared" si="6"/>
-        <v>0.137142857142857</v>
+        <v>0.148571428571429</v>
       </c>
       <c r="K191" s="32">
         <f t="shared" si="7"/>
@@ -7557,13 +7557,13 @@
         <v>16</v>
       </c>
       <c r="C192" s="28">
-        <v>7.081</v>
+        <v>6.339</v>
       </c>
       <c r="D192" s="64">
-        <v>0.14122</v>
+        <v>0.15776</v>
       </c>
       <c r="E192" s="28">
-        <v>0.29</v>
+        <v>1.3</v>
       </c>
       <c r="F192" s="28">
         <v>0</v>
@@ -7576,15 +7576,15 @@
       </c>
       <c r="I192" s="29">
         <f t="shared" si="5"/>
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="J192" s="31">
         <f t="shared" si="6"/>
-        <v>0.137142857142857</v>
+        <v>0.148571428571429</v>
       </c>
       <c r="K192" s="32">
         <f t="shared" si="7"/>
-        <v>5.24858770285714</v>
+        <v>26.0178300571429</v>
       </c>
       <c r="L192" s="34">
         <f t="shared" si="8"/>
@@ -7621,13 +7621,13 @@
         <v>17</v>
       </c>
       <c r="C193" s="28">
-        <v>7.14</v>
+        <v>7.114</v>
       </c>
       <c r="D193" s="64">
-        <v>0.14006</v>
+        <v>0.14057</v>
       </c>
       <c r="E193" s="28">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="F193" s="28">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="K193" s="32">
         <f t="shared" si="7"/>
-        <v>16.2887204571429</v>
+        <v>0</v>
       </c>
       <c r="L193" s="34">
         <f t="shared" si="8"/>
@@ -7684,13 +7684,13 @@
         <v>18</v>
       </c>
       <c r="C194" s="28">
-        <v>7.212</v>
+        <v>7.211</v>
       </c>
       <c r="D194" s="64">
-        <v>0.13865</v>
+        <v>0.13868</v>
       </c>
       <c r="E194" s="28">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="F194" s="28">
         <v>0</v>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="K194" s="32">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>29.3739761828572</v>
       </c>
       <c r="L194" s="34">
         <f t="shared" si="8"/>
@@ -7810,13 +7810,13 @@
         <v>20</v>
       </c>
       <c r="C196" s="28">
-        <v>7.377</v>
+        <v>7.212</v>
       </c>
       <c r="D196" s="64">
-        <v>0.13556</v>
+        <v>0.13865</v>
       </c>
       <c r="E196" s="28">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F196" s="28">
         <v>0</v>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="K196" s="32">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.184741988571429</v>
       </c>
       <c r="L196" s="34">
         <f t="shared" si="8"/>
@@ -7873,13 +7873,13 @@
         <v>21</v>
       </c>
       <c r="C197" s="28">
-        <v>7.405</v>
+        <v>7.236</v>
       </c>
       <c r="D197" s="64">
-        <v>0.13504</v>
+        <v>0.13819</v>
       </c>
       <c r="E197" s="28">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="F197" s="28">
         <v>0</v>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="K197" s="32">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6.83545357714286</v>
       </c>
       <c r="L197" s="34">
         <f t="shared" si="8"/>
@@ -7936,13 +7936,13 @@
         <v>22</v>
       </c>
       <c r="C198" s="28">
-        <v>7.428</v>
+        <v>7.419</v>
       </c>
       <c r="D198" s="64">
-        <v>0.13463</v>
+        <v>0.13479</v>
       </c>
       <c r="E198" s="28">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="F198" s="28">
         <v>0</v>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="K198" s="32">
         <f t="shared" si="7"/>
-        <v>36.5968335085714</v>
+        <v>0</v>
       </c>
       <c r="L198" s="34">
         <f t="shared" si="8"/>
@@ -7999,10 +7999,10 @@
         <v>23</v>
       </c>
       <c r="C199" s="28">
-        <v>7.498</v>
+        <v>7.501</v>
       </c>
       <c r="D199" s="64">
-        <v>0.13336</v>
+        <v>0.13332</v>
       </c>
       <c r="E199" s="28">
         <v>0</v>
@@ -8011,7 +8011,7 @@
         <v>0</v>
       </c>
       <c r="G199" s="28">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="H199" s="28" t="s">
         <v>113</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="L199" s="34">
         <f t="shared" si="8"/>
-        <v>1.04066825142857</v>
+        <v>1.23931084</v>
       </c>
       <c r="T199">
         <v>12</v>
@@ -8062,10 +8062,10 @@
         <v>24</v>
       </c>
       <c r="C200" s="28">
-        <v>7.553</v>
+        <v>7.54</v>
       </c>
       <c r="D200" s="64">
-        <v>0.1324</v>
+        <v>0.13263</v>
       </c>
       <c r="E200" s="28">
         <v>0</v>
@@ -8125,13 +8125,13 @@
         <v>25</v>
       </c>
       <c r="C201" s="28">
-        <v>7.566</v>
+        <v>7.549</v>
       </c>
       <c r="D201" s="64">
-        <v>0.13217</v>
+        <v>0.13247</v>
       </c>
       <c r="E201" s="28">
-        <v>0.32</v>
+        <v>0.62</v>
       </c>
       <c r="F201" s="28">
         <v>0</v>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="K201" s="32">
         <f t="shared" si="7"/>
-        <v>5.55023067428571</v>
+        <v>10.9767531542857</v>
       </c>
       <c r="L201" s="34">
         <f t="shared" si="8"/>
@@ -8188,10 +8188,10 @@
         <v>26</v>
       </c>
       <c r="C202" s="28">
-        <v>7.585</v>
+        <v>7.582</v>
       </c>
       <c r="D202" s="64">
-        <v>0.13185</v>
+        <v>0.1319</v>
       </c>
       <c r="E202" s="28">
         <v>0</v>
@@ -8251,13 +8251,13 @@
         <v>27</v>
       </c>
       <c r="C203" s="28">
-        <v>7.587</v>
+        <v>7.583</v>
       </c>
       <c r="D203" s="64">
-        <v>0.13181</v>
+        <v>0.13187</v>
       </c>
       <c r="E203" s="28">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="F203" s="28">
         <v>0</v>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="K203" s="32">
         <f t="shared" si="7"/>
-        <v>4.50956242285714</v>
+        <v>3.89497692571429</v>
       </c>
       <c r="L203" s="34">
         <f t="shared" si="8"/>
@@ -8314,10 +8314,10 @@
         <v>28</v>
       </c>
       <c r="C204" s="28">
-        <v>7.593</v>
+        <v>7.592</v>
       </c>
       <c r="D204" s="64">
-        <v>0.13171</v>
+        <v>0.13172</v>
       </c>
       <c r="E204" s="28">
         <v>0</v>
@@ -8378,13 +8378,13 @@
         <v>29</v>
       </c>
       <c r="C205" s="28">
-        <v>7.594</v>
+        <v>7.592</v>
       </c>
       <c r="D205" s="64">
-        <v>0.13169</v>
+        <v>0.13171</v>
       </c>
       <c r="E205" s="28">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="F205" s="28">
         <v>0</v>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="K205" s="32">
         <f t="shared" si="7"/>
-        <v>0.693778834285714</v>
+        <v>1.41635524571429</v>
       </c>
       <c r="L205" s="34">
         <f t="shared" si="8"/>
@@ -8441,7 +8441,7 @@
         <v>30</v>
       </c>
       <c r="C206" s="28">
-        <v>7.597</v>
+        <v>7.596</v>
       </c>
       <c r="D206" s="64">
         <v>0.13164</v>
@@ -8504,13 +8504,13 @@
         <v>31</v>
       </c>
       <c r="C207" s="28">
-        <v>7.597</v>
+        <v>7.596</v>
       </c>
       <c r="D207" s="64">
-        <v>0.13163</v>
+        <v>0.13164</v>
       </c>
       <c r="E207" s="28">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F207" s="28">
         <v>0</v>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="K207" s="32">
         <f t="shared" si="7"/>
-        <v>0.520334125714286</v>
+        <v>0.354088811428571</v>
       </c>
       <c r="L207" s="34">
         <f t="shared" si="8"/>
@@ -8693,10 +8693,10 @@
         <v>34</v>
       </c>
       <c r="C210" s="28">
-        <v>7.631</v>
+        <v>7.63</v>
       </c>
       <c r="D210" s="64">
-        <v>0.13105</v>
+        <v>0.13106</v>
       </c>
       <c r="E210" s="28">
         <v>0</v>
@@ -8756,13 +8756,13 @@
         <v>35</v>
       </c>
       <c r="C211" s="28">
-        <v>7.65</v>
+        <v>7.64</v>
       </c>
       <c r="D211" s="64">
-        <v>0.13072</v>
+        <v>0.13088</v>
       </c>
       <c r="E211" s="28">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="F211" s="28">
         <v>0</v>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="K211" s="32">
         <f t="shared" si="7"/>
-        <v>0.693778834285714</v>
+        <v>0</v>
       </c>
       <c r="L211" s="34">
         <f t="shared" si="8"/>
@@ -8825,7 +8825,7 @@
         <v>0.13058</v>
       </c>
       <c r="E212" s="28">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="F212" s="28">
         <v>0</v>
@@ -8846,7 +8846,7 @@
       </c>
       <c r="K212" s="32">
         <f t="shared" si="7"/>
-        <v>7.80501188571429</v>
+        <v>7.61290944571429</v>
       </c>
       <c r="L212" s="34">
         <f t="shared" si="8"/>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="K213" s="32">
         <f t="shared" si="7"/>
-        <v>7.11123305142857</v>
+        <v>7.25882063428572</v>
       </c>
       <c r="L213" s="34">
         <f t="shared" si="8"/>
@@ -8945,13 +8945,13 @@
         <v>38</v>
       </c>
       <c r="C214" s="28">
-        <v>8.185</v>
+        <v>8.202</v>
       </c>
       <c r="D214" s="64">
-        <v>0.12218</v>
+        <v>0.12192</v>
       </c>
       <c r="E214" s="28">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F214" s="28">
         <v>0</v>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="K214" s="32">
         <f t="shared" si="7"/>
-        <v>0.497710902857143</v>
+        <v>0.169346822857143</v>
       </c>
       <c r="L214" s="34">
         <f t="shared" si="8"/>
@@ -9008,19 +9008,19 @@
         <v>39</v>
       </c>
       <c r="C215" s="28">
-        <v>9.274</v>
+        <v>9.386</v>
       </c>
       <c r="D215" s="64">
-        <v>0.10783</v>
+        <v>0.10654</v>
       </c>
       <c r="E215" s="28">
+        <v>0</v>
+      </c>
+      <c r="F215" s="28">
+        <v>0</v>
+      </c>
+      <c r="G215" s="28">
         <v>0.02</v>
-      </c>
-      <c r="F215" s="28">
-        <v>0</v>
-      </c>
-      <c r="G215" s="28">
-        <v>0.05</v>
       </c>
       <c r="H215" s="28" t="s">
         <v>113</v>
@@ -9035,11 +9035,11 @@
       </c>
       <c r="K215" s="32">
         <f t="shared" si="7"/>
-        <v>0.31672512</v>
+        <v>0</v>
       </c>
       <c r="L215" s="34">
         <f t="shared" si="8"/>
-        <v>0.7918128</v>
+        <v>0.32329848</v>
       </c>
       <c r="T215">
         <v>30</v>
@@ -9071,19 +9071,19 @@
         <v>40</v>
       </c>
       <c r="C216" s="28">
-        <v>10.051</v>
+        <v>10.17</v>
       </c>
       <c r="D216" s="64">
-        <v>0.09949</v>
+        <v>0.09833</v>
       </c>
       <c r="E216" s="28">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="F216" s="28">
         <v>0</v>
       </c>
       <c r="G216" s="28">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="H216" s="28" t="s">
         <v>113</v>
@@ -9098,11 +9098,11 @@
       </c>
       <c r="K216" s="32">
         <f t="shared" si="7"/>
-        <v>0.150821485714286</v>
+        <v>0.923709942857143</v>
       </c>
       <c r="L216" s="34">
         <f t="shared" si="8"/>
-        <v>7.69189577142857</v>
+        <v>0</v>
       </c>
       <c r="T216">
         <v>31</v>
@@ -9134,38 +9134,38 @@
         <v>41</v>
       </c>
       <c r="C217" s="28">
-        <v>10.125</v>
+        <v>10.672</v>
       </c>
       <c r="D217" s="64">
-        <v>0.09877</v>
+        <v>0.09371</v>
       </c>
       <c r="E217" s="28">
-        <v>0.02</v>
+        <v>0.31</v>
       </c>
       <c r="F217" s="28">
         <v>0</v>
       </c>
       <c r="G217" s="28">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H217" s="28" t="s">
         <v>113</v>
       </c>
       <c r="I217" s="29">
         <f t="shared" si="5"/>
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J217" s="31">
         <f t="shared" si="6"/>
-        <v>0.114285714285714</v>
+        <v>0.108571428571429</v>
       </c>
       <c r="K217" s="32">
         <f t="shared" si="7"/>
-        <v>0.301642971428571</v>
+        <v>4.53387630285714</v>
       </c>
       <c r="L217" s="34">
         <f t="shared" si="8"/>
-        <v>48.2628754285714</v>
+        <v>0</v>
       </c>
       <c r="T217">
         <v>32</v>
@@ -9197,38 +9197,38 @@
         <v>42</v>
       </c>
       <c r="C218" s="28">
-        <v>10.155</v>
+        <v>11.028</v>
       </c>
       <c r="D218" s="64">
-        <v>0.09847</v>
+        <v>0.09068</v>
       </c>
       <c r="E218" s="28">
-        <v>0.12</v>
+        <v>0.02</v>
       </c>
       <c r="F218" s="28">
         <v>0</v>
       </c>
       <c r="G218" s="28">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="H218" s="28" t="s">
         <v>113</v>
       </c>
       <c r="I218" s="29">
         <f t="shared" si="5"/>
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J218" s="31">
         <f t="shared" si="6"/>
-        <v>0.114285714285714</v>
+        <v>0.108571428571429</v>
       </c>
       <c r="K218" s="32">
         <f t="shared" si="7"/>
-        <v>1.80985782857143</v>
+        <v>0.292508148571429</v>
       </c>
       <c r="L218" s="34">
         <f t="shared" si="8"/>
-        <v>11.7640758857143</v>
+        <v>0</v>
       </c>
       <c r="T218">
         <v>50</v>
@@ -9255,36 +9255,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="2:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B219" s="114" t="s">
-        <v>130</v>
-      </c>
-      <c r="C219" s="115"/>
-      <c r="D219" s="115"/>
-      <c r="E219" s="116">
-        <f>SUM(E177:E218)</f>
-        <v>90.96</v>
-      </c>
-      <c r="F219" s="116">
-        <f t="shared" ref="F219" si="9">SUM(F177:F218)</f>
-        <v>0</v>
-      </c>
-      <c r="G219" s="116">
-        <f>SUM(G177:G218)</f>
-        <v>92.58</v>
-      </c>
-      <c r="H219" s="140" t="s">
-        <v>131</v>
-      </c>
-      <c r="I219" s="141"/>
-      <c r="J219" s="142"/>
-      <c r="K219" s="117">
-        <f>SQRT(SUMSQ(K177:K218))</f>
-        <v>1654.33495229314</v>
-      </c>
-      <c r="L219" s="117">
-        <f>SQRT(SUMSQ(L177:L218))</f>
-        <v>1392.16807426887</v>
+    <row r="219" spans="2:27" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B219" s="33">
+        <v>43</v>
+      </c>
+      <c r="C219" s="28">
+        <v>11.719</v>
+      </c>
+      <c r="D219" s="64">
+        <v>0.08533</v>
+      </c>
+      <c r="E219" s="28">
+        <v>0</v>
+      </c>
+      <c r="F219" s="28">
+        <v>0</v>
+      </c>
+      <c r="G219" s="28">
+        <v>0.22</v>
+      </c>
+      <c r="H219" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="I219" s="29">
+        <f t="shared" si="5"/>
+        <v>0.09</v>
+      </c>
+      <c r="J219" s="31">
+        <f t="shared" si="6"/>
+        <v>0.108571428571429</v>
+      </c>
+      <c r="K219" s="32">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L219" s="34">
+        <f t="shared" si="8"/>
+        <v>3.21758963428571</v>
       </c>
       <c r="T219">
         <v>51</v>
@@ -9311,7 +9318,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:27" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B220" s="33">
+        <v>44</v>
+      </c>
+      <c r="C220" s="28">
+        <v>11.759</v>
+      </c>
+      <c r="D220" s="64">
+        <v>0.08504</v>
+      </c>
+      <c r="E220" s="28">
+        <v>0</v>
+      </c>
+      <c r="F220" s="28">
+        <v>0</v>
+      </c>
+      <c r="G220" s="28">
+        <v>0</v>
+      </c>
+      <c r="H220" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="I220" s="29">
+        <f t="shared" si="5"/>
+        <v>0.09</v>
+      </c>
+      <c r="J220" s="31">
+        <f t="shared" si="6"/>
+        <v>0.108571428571429</v>
+      </c>
+      <c r="K220" s="32">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L220" s="34">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="T220">
         <v>52</v>
       </c>
@@ -9337,19 +9381,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H221" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="J221" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="K221" s="30">
-        <f>E165</f>
-        <v>13196.88</v>
-      </c>
-      <c r="L221" t="s">
-        <v>134</v>
+    <row r="221" spans="2:27" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B221" s="33">
+        <v>45</v>
+      </c>
+      <c r="C221" s="28">
+        <v>12.403</v>
+      </c>
+      <c r="D221" s="64">
+        <v>0.08063</v>
+      </c>
+      <c r="E221" s="28">
+        <v>0</v>
+      </c>
+      <c r="F221" s="28">
+        <v>0</v>
+      </c>
+      <c r="G221" s="28">
+        <v>6.08</v>
+      </c>
+      <c r="H221" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="I221" s="29">
+        <f t="shared" si="5"/>
+        <v>0.08</v>
+      </c>
+      <c r="J221" s="31">
+        <f t="shared" si="6"/>
+        <v>0.102857142857143</v>
+      </c>
+      <c r="K221" s="32">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L221" s="34">
+        <f t="shared" si="8"/>
+        <v>84.2423467885714</v>
       </c>
       <c r="T221">
         <v>53</v>
@@ -9376,19 +9444,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H222" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="J222" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="K222" s="30">
-        <f>E166</f>
-        <v>13196.88</v>
-      </c>
-      <c r="L222" t="s">
-        <v>134</v>
+    <row r="222" spans="2:27" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B222" s="33">
+        <v>46</v>
+      </c>
+      <c r="C222" s="28">
+        <v>12.717</v>
+      </c>
+      <c r="D222" s="64">
+        <v>0.07863</v>
+      </c>
+      <c r="E222" s="28">
+        <v>0</v>
+      </c>
+      <c r="F222" s="28">
+        <v>0</v>
+      </c>
+      <c r="G222" s="28">
+        <v>0</v>
+      </c>
+      <c r="H222" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="I222" s="29">
+        <f t="shared" si="5"/>
+        <v>0.08</v>
+      </c>
+      <c r="J222" s="31">
+        <f t="shared" si="6"/>
+        <v>0.102857142857143</v>
+      </c>
+      <c r="K222" s="32">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L222" s="34">
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="T222">
         <v>54</v>
@@ -9415,9 +9507,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="K223" s="53"/>
-      <c r="L223" s="53"/>
+    <row r="223" spans="2:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B223" s="114" t="s">
+        <v>130</v>
+      </c>
+      <c r="C223" s="115"/>
+      <c r="D223" s="115"/>
+      <c r="E223" s="116">
+        <f>SUM(E177:E222)</f>
+        <v>91.69</v>
+      </c>
+      <c r="F223" s="116">
+        <f t="shared" ref="F223" si="9">SUM(F177:F222)</f>
+        <v>0</v>
+      </c>
+      <c r="G223" s="116">
+        <f>SUM(G177:G222)</f>
+        <v>92.48</v>
+      </c>
+      <c r="H223" s="140" t="s">
+        <v>131</v>
+      </c>
+      <c r="I223" s="141"/>
+      <c r="J223" s="142"/>
+      <c r="K223" s="117">
+        <f>SQRT(SUMSQ(K177:K222))</f>
+        <v>1642.09681311277</v>
+      </c>
+      <c r="L223" s="117">
+        <f>SQRT(SUMSQ(L177:L222))</f>
+        <v>1487.16649860768</v>
+      </c>
       <c r="T223">
         <v>55</v>
       </c>
@@ -9444,20 +9564,6 @@
       </c>
     </row>
     <row r="224" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H224" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="J224" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="K224" s="30">
-        <f>K221*VLOOKUP(MAX(E177:E218),E177:J218,6,0)</f>
-        <v>2061.05341273936</v>
-      </c>
-      <c r="L224" s="30">
-        <f>K221*VLOOKUP(MAX(G177:G218),G177:J218,4,0)</f>
-        <v>2262.32228571429</v>
-      </c>
       <c r="T224">
         <v>56</v>
       </c>
@@ -9484,16 +9590,18 @@
       </c>
     </row>
     <row r="225" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H225" s="12" t="s">
+        <v>132</v>
+      </c>
       <c r="J225" s="12" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="K225" s="30">
-        <f>0.9*K224</f>
-        <v>1854.94807146542</v>
-      </c>
-      <c r="L225" s="30">
-        <f>0.9*L224</f>
-        <v>2036.09005714286</v>
+        <f>E165</f>
+        <v>13470.77</v>
+      </c>
+      <c r="L225" t="s">
+        <v>134</v>
       </c>
       <c r="T225">
         <v>57</v>
@@ -9521,9 +9629,19 @@
       </c>
     </row>
     <row r="226" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="J226" s="12"/>
-      <c r="K226" s="53"/>
-      <c r="L226" s="53"/>
+      <c r="H226" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="J226" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="K226" s="30">
+        <f>E166</f>
+        <v>13470.77</v>
+      </c>
+      <c r="L226" t="s">
+        <v>134</v>
+      </c>
       <c r="T226">
         <v>58</v>
       </c>
@@ -9550,20 +9668,8 @@
       </c>
     </row>
     <row r="227" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H227" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="J227" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="K227" s="30">
-        <f>K221*G168</f>
-        <v>2262.32228571429</v>
-      </c>
-      <c r="L227" s="30">
-        <f>K221*G168</f>
-        <v>2262.32228571429</v>
-      </c>
+      <c r="K227" s="53"/>
+      <c r="L227" s="53"/>
       <c r="T227">
         <v>59</v>
       </c>
@@ -9590,16 +9696,19 @@
       </c>
     </row>
     <row r="228" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H228" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="J228" s="12" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="K228" s="30">
-        <f>0.8*K227</f>
-        <v>1809.85782857143</v>
+        <f>K225*VLOOKUP(MAX(E177:E222),E177:J222,6,0)</f>
+        <v>2103.82882020045</v>
       </c>
       <c r="L228" s="30">
-        <f>0.8*L227</f>
-        <v>1809.85782857143</v>
+        <f>K225*VLOOKUP(MAX(G177:G222),G177:J222,4,0)</f>
+        <v>2309.27485714286</v>
       </c>
       <c r="T228">
         <v>60</v>
@@ -9627,7 +9736,17 @@
       </c>
     </row>
     <row r="229" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="J229" s="12"/>
+      <c r="J229" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="K229" s="30">
+        <f>0.9*K228</f>
+        <v>1893.44593818041</v>
+      </c>
+      <c r="L229" s="30">
+        <f>0.9*L228</f>
+        <v>2078.34737142857</v>
+      </c>
       <c r="T229">
         <v>61</v>
       </c>
@@ -9654,6 +9773,9 @@
       </c>
     </row>
     <row r="230" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="J230" s="12"/>
+      <c r="K230" s="53"/>
+      <c r="L230" s="53"/>
       <c r="T230">
         <v>62</v>
       </c>
@@ -9681,18 +9803,18 @@
     </row>
     <row r="231" spans="2:27" x14ac:dyDescent="0.3">
       <c r="H231" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J231" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="K231" s="44">
-        <f>MAX(K228,K225)</f>
-        <v>1854.94807146542</v>
-      </c>
-      <c r="L231" s="44">
-        <f>MAX(L228,L225)</f>
-        <v>2036.09005714286</v>
+        <v>141</v>
+      </c>
+      <c r="K231" s="30">
+        <f>K225*G168</f>
+        <v>2309.27485714286</v>
+      </c>
+      <c r="L231" s="30">
+        <f>K225*G168</f>
+        <v>2309.27485714286</v>
       </c>
       <c r="T231">
         <v>63</v>
@@ -9720,7 +9842,17 @@
       </c>
     </row>
     <row r="232" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H232" s="12"/>
+      <c r="J232" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="K232" s="30">
+        <f>0.8*K231</f>
+        <v>1847.41988571429</v>
+      </c>
+      <c r="L232" s="30">
+        <f>0.8*L231</f>
+        <v>1847.41988571429</v>
+      </c>
       <c r="T232">
         <v>64</v>
       </c>
@@ -9747,10 +9879,7 @@
       </c>
     </row>
     <row r="233" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="K233" s="134" t="s">
-        <v>145</v>
-      </c>
-      <c r="L233" s="135"/>
+      <c r="J233" s="12"/>
       <c r="T233">
         <v>65</v>
       </c>
@@ -9777,12 +9906,6 @@
       </c>
     </row>
     <row r="234" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="K234" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="L234" s="23" t="s">
-        <v>147</v>
-      </c>
       <c r="T234">
         <v>66</v>
       </c>
@@ -9809,16 +9932,19 @@
       </c>
     </row>
     <row r="235" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H235" s="12" t="s">
+        <v>143</v>
+      </c>
       <c r="J235" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="K235" s="47">
-        <f>K231/1000</f>
-        <v>1.85494807146542</v>
-      </c>
-      <c r="L235" s="47">
-        <f>L231/1000</f>
-        <v>2.03609005714286</v>
+        <v>144</v>
+      </c>
+      <c r="K235" s="44">
+        <f>MAX(K232,K229)</f>
+        <v>1893.44593818041</v>
+      </c>
+      <c r="L235" s="44">
+        <f>MAX(L232,L229)</f>
+        <v>2078.34737142857</v>
       </c>
       <c r="T235">
         <v>67</v>
@@ -9846,17 +9972,7 @@
       </c>
     </row>
     <row r="236" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="J236" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="K236" s="47">
-        <f>K219/1000</f>
-        <v>1.65433495229314</v>
-      </c>
-      <c r="L236" s="47">
-        <f>L219/1000</f>
-        <v>1.39216807426887</v>
-      </c>
+      <c r="H236" s="12"/>
       <c r="T236">
         <v>68</v>
       </c>
@@ -9883,17 +9999,10 @@
       </c>
     </row>
     <row r="237" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="J237" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="K237" s="68" t="str">
-        <f>IF(K219&gt;=K231,"Se Cumple","No se Cumple")</f>
-        <v>No se Cumple</v>
-      </c>
-      <c r="L237" s="68" t="str">
-        <f>IF(L219&gt;=K231,"Se Cumple","No se Cumple")</f>
-        <v>No se Cumple</v>
-      </c>
+      <c r="K237" s="134" t="s">
+        <v>145</v>
+      </c>
+      <c r="L237" s="135"/>
       <c r="T237">
         <v>69</v>
       </c>
@@ -9920,16 +10029,11 @@
       </c>
     </row>
     <row r="238" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="J238" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="K238" s="86">
-        <f>MAX(K235/K236,1)</f>
-        <v>1.12126511556454</v>
-      </c>
-      <c r="L238" s="86">
-        <f>MAX(L235/L236,1)</f>
-        <v>1.46253178389553</v>
+      <c r="K238" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="L238" s="23" t="s">
+        <v>147</v>
       </c>
       <c r="T238">
         <v>70</v>
@@ -9957,6 +10061,17 @@
       </c>
     </row>
     <row r="239" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="J239" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="K239" s="47">
+        <f>K235/1000</f>
+        <v>1.89344593818041</v>
+      </c>
+      <c r="L239" s="47">
+        <f>L235/1000</f>
+        <v>2.07834737142857</v>
+      </c>
       <c r="T239">
         <v>71</v>
       </c>
@@ -9983,16 +10098,16 @@
       </c>
     </row>
     <row r="240" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="J240" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="K240" s="86">
-        <f>IF(K225/K219&lt;1,"N/A",K225/K219)</f>
-        <v>1.12126511556454</v>
-      </c>
-      <c r="L240" s="86">
-        <f>IF(L225/L219&lt;1,"N/A",L225/L219)</f>
-        <v>1.46253178389553</v>
+      <c r="J240" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="K240" s="47">
+        <f>K223/1000</f>
+        <v>1.64209681311277</v>
+      </c>
+      <c r="L240" s="47">
+        <f>L223/1000</f>
+        <v>1.48716649860768</v>
       </c>
       <c r="T240">
         <v>72</v>
@@ -10020,6 +10135,17 @@
       </c>
     </row>
     <row r="241" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="J241" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="K241" s="68" t="str">
+        <f>IF(K223&gt;=K235,"Se Cumple","No se Cumple")</f>
+        <v>No se Cumple</v>
+      </c>
+      <c r="L241" s="68" t="str">
+        <f>IF(L223&gt;=K235,"Se Cumple","No se Cumple")</f>
+        <v>No se Cumple</v>
+      </c>
       <c r="T241">
         <v>73</v>
       </c>
@@ -10046,13 +10172,16 @@
       </c>
     </row>
     <row r="242" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="K242" s="53">
-        <f>K224/K219</f>
-        <v>1.24585012840505</v>
-      </c>
-      <c r="L242" s="53">
-        <f>L224/L219</f>
-        <v>1.62503531543948</v>
+      <c r="J242" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="K242" s="86">
+        <f>MAX(K239/K240,1)</f>
+        <v>1.15306595997296</v>
+      </c>
+      <c r="L242" s="86">
+        <f>MAX(L239/L240,1)</f>
+        <v>1.39752164493644</v>
       </c>
       <c r="T242">
         <v>74</v>
@@ -10106,6 +10235,17 @@
       </c>
     </row>
     <row r="244" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="J244" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="K244" s="86">
+        <f>IF(K229/K223&lt;1,"N/A",K229/K223)</f>
+        <v>1.15306595997296</v>
+      </c>
+      <c r="L244" s="86">
+        <f>IF(L229/L223&lt;1,"N/A",L229/L223)</f>
+        <v>1.39752164493644</v>
+      </c>
       <c r="T244">
         <v>76</v>
       </c>
@@ -10132,22 +10272,6 @@
       </c>
     </row>
     <row r="245" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B245" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C245" s="4"/>
-      <c r="D245" s="4"/>
-      <c r="E245" s="4"/>
-      <c r="F245" s="4"/>
-      <c r="G245" s="4"/>
-      <c r="H245" s="4"/>
-      <c r="I245" s="4"/>
-      <c r="J245" s="4"/>
-      <c r="K245" s="4"/>
-      <c r="L245" s="4"/>
-      <c r="M245" s="4"/>
-      <c r="N245" s="4"/>
-      <c r="O245" s="4"/>
       <c r="T245">
         <v>77</v>
       </c>
@@ -10174,6 +10298,14 @@
       </c>
     </row>
     <row r="246" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="K246" s="53">
+        <f>K228/K223</f>
+        <v>1.28118439996995</v>
+      </c>
+      <c r="L246" s="53">
+        <f>L228/L223</f>
+        <v>1.55280182770715</v>
+      </c>
       <c r="T246">
         <v>78</v>
       </c>
@@ -10200,9 +10332,6 @@
       </c>
     </row>
     <row r="247" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B247" t="s">
-        <v>154</v>
-      </c>
       <c r="T247">
         <v>79</v>
       </c>
@@ -10255,844 +10384,835 @@
       </c>
     </row>
     <row r="249" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B249" s="12" t="s">
+      <c r="B249" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C249" s="4"/>
+      <c r="D249" s="4"/>
+      <c r="E249" s="4"/>
+      <c r="F249" s="4"/>
+      <c r="G249" s="4"/>
+      <c r="H249" s="4"/>
+      <c r="I249" s="4"/>
+      <c r="J249" s="4"/>
+      <c r="K249" s="4"/>
+      <c r="L249" s="4"/>
+      <c r="M249" s="4"/>
+      <c r="N249" s="4"/>
+      <c r="O249" s="4"/>
+      <c r="T249">
+        <v>81</v>
+      </c>
+      <c r="U249" t="s">
+        <v>129</v>
+      </c>
+      <c r="V249">
+        <v>2E-3</v>
+      </c>
+      <c r="W249">
+        <v>-0.50600000000000001</v>
+      </c>
+      <c r="X249">
+        <v>-1.109</v>
+      </c>
+      <c r="Y249">
+        <v>0</v>
+      </c>
+      <c r="Z249">
+        <v>0</v>
+      </c>
+      <c r="AA249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="T250">
+        <v>82</v>
+      </c>
+      <c r="U250" t="s">
+        <v>129</v>
+      </c>
+      <c r="V250">
+        <v>1.9E-2</v>
+      </c>
+      <c r="W250">
+        <v>-0.83599999999999997</v>
+      </c>
+      <c r="X250">
+        <v>-1.57</v>
+      </c>
+      <c r="Y250">
+        <v>0</v>
+      </c>
+      <c r="Z250">
+        <v>0</v>
+      </c>
+      <c r="AA250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B251" t="s">
+        <v>154</v>
+      </c>
+      <c r="T251">
+        <v>83</v>
+      </c>
+      <c r="U251" t="s">
+        <v>129</v>
+      </c>
+      <c r="V251">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="W251">
+        <v>-1.24</v>
+      </c>
+      <c r="X251">
+        <v>-1.492</v>
+      </c>
+      <c r="Y251">
+        <v>0</v>
+      </c>
+      <c r="Z251">
+        <v>0</v>
+      </c>
+      <c r="AA251">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="T252">
+        <v>84</v>
+      </c>
+      <c r="U252" t="s">
+        <v>129</v>
+      </c>
+      <c r="V252">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="W252">
+        <v>-1.847</v>
+      </c>
+      <c r="X252">
+        <v>-1.571</v>
+      </c>
+      <c r="Y252">
+        <v>0</v>
+      </c>
+      <c r="Z252">
+        <v>0</v>
+      </c>
+      <c r="AA252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B253" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C249" s="40">
+      <c r="C253" s="40">
         <f>P33</f>
         <v>0.4</v>
       </c>
-      <c r="H249" t="s">
+      <c r="H253" t="s">
         <v>99</v>
       </c>
-      <c r="I249" t="s">
+      <c r="I253" t="s">
         <v>155</v>
       </c>
-      <c r="T249">
-        <v>81</v>
-      </c>
-      <c r="U249" t="s">
+      <c r="T253">
+        <v>85</v>
+      </c>
+      <c r="U253" t="s">
         <v>129</v>
       </c>
-      <c r="V249">
-        <v>2E-3</v>
-      </c>
-      <c r="W249">
-        <v>-0.50600000000000001</v>
-      </c>
-      <c r="X249">
-        <v>-1.109</v>
-      </c>
-      <c r="Y249">
-        <v>0</v>
-      </c>
-      <c r="Z249">
-        <v>0</v>
-      </c>
-      <c r="AA249">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B250" s="12" t="s">
+      <c r="V253">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="W253">
+        <v>-1.621</v>
+      </c>
+      <c r="X253">
+        <v>-0.97299999999999998</v>
+      </c>
+      <c r="Y253">
+        <v>0</v>
+      </c>
+      <c r="Z253">
+        <v>0</v>
+      </c>
+      <c r="AA253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B254" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C250" s="40">
+      <c r="C254" s="40">
         <f>P55</f>
         <v>3</v>
       </c>
-      <c r="H250" t="s">
+      <c r="H254" t="s">
         <v>108</v>
       </c>
-      <c r="I250" t="s">
+      <c r="I254" t="s">
         <v>110</v>
       </c>
-      <c r="T250">
-        <v>82</v>
-      </c>
-      <c r="U250" t="s">
+      <c r="T254">
+        <v>88</v>
+      </c>
+      <c r="U254" t="s">
         <v>129</v>
       </c>
-      <c r="V250">
-        <v>1.9E-2</v>
-      </c>
-      <c r="W250">
-        <v>-0.83599999999999997</v>
-      </c>
-      <c r="X250">
-        <v>-1.57</v>
-      </c>
-      <c r="Y250">
-        <v>0</v>
-      </c>
-      <c r="Z250">
-        <v>0</v>
-      </c>
-      <c r="AA250">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B251" s="12" t="s">
+      <c r="V254">
+        <v>-3.0379999999999998</v>
+      </c>
+      <c r="W254">
+        <v>-4.657</v>
+      </c>
+      <c r="X254">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="Y254">
+        <v>0</v>
+      </c>
+      <c r="Z254">
+        <v>0</v>
+      </c>
+      <c r="AA254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B255" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="C251" s="40">
+      <c r="C255" s="40">
         <f>P57</f>
         <v>0.6</v>
       </c>
-      <c r="H251">
+      <c r="H255">
         <v>0.01</v>
       </c>
-      <c r="I251" s="53">
+      <c r="I255" s="53">
         <v>6.2857142857142861E-2</v>
       </c>
-      <c r="T251">
-        <v>83</v>
-      </c>
-      <c r="U251" t="s">
+      <c r="T255">
+        <v>90</v>
+      </c>
+      <c r="U255" t="s">
         <v>129</v>
       </c>
-      <c r="V251">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="W251">
-        <v>-1.24</v>
-      </c>
-      <c r="X251">
-        <v>-1.492</v>
-      </c>
-      <c r="Y251">
-        <v>0</v>
-      </c>
-      <c r="Z251">
-        <v>0</v>
-      </c>
-      <c r="AA251">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B252" s="12" t="s">
+      <c r="V255">
+        <v>-2.149</v>
+      </c>
+      <c r="W255">
+        <v>-1.8620000000000001</v>
+      </c>
+      <c r="X255">
+        <v>1.2E-2</v>
+      </c>
+      <c r="Y255">
+        <v>0</v>
+      </c>
+      <c r="Z255">
+        <v>0</v>
+      </c>
+      <c r="AA255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B256" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="C252" s="40">
+      <c r="C256" s="40">
         <f>Q85</f>
         <v>1</v>
       </c>
-      <c r="H252">
+      <c r="H256">
         <v>0.02</v>
       </c>
-      <c r="I252" s="53">
-        <f>IF(H252&lt;$C$251/3,   ($C$252*$C$249/$C$253)*(1+(3*($C$250-1)*H252/$C$251)),   IF(H252&lt;=$C$251,   $C$252*$C$249*$C$250/$C$253,   $C$252*$C$249*$C$250/$C$253*($C$251/H252)^(2/3)   ))</f>
+      <c r="I256" s="53">
+        <f>IF(H256&lt;$C$255/3,   ($C$256*$C$253/$C$257)*(1+(3*($C$254-1)*H256/$C$255)),   IF(H256&lt;=$C$255,   $C$256*$C$253*$C$254/$C$257,   $C$256*$C$253*$C$254/$C$257*($C$255/H256)^(2/3)   ))</f>
         <v>6.8571428571428575E-2</v>
       </c>
-      <c r="T252">
-        <v>84</v>
-      </c>
-      <c r="U252" t="s">
+      <c r="T256">
+        <v>92</v>
+      </c>
+      <c r="U256" t="s">
         <v>129</v>
       </c>
-      <c r="V252">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="W252">
-        <v>-1.847</v>
-      </c>
-      <c r="X252">
-        <v>-1.571</v>
-      </c>
-      <c r="Y252">
-        <v>0</v>
-      </c>
-      <c r="Z252">
-        <v>0</v>
-      </c>
-      <c r="AA252">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B253" s="12" t="s">
+      <c r="V256">
+        <v>-4.29</v>
+      </c>
+      <c r="W256">
+        <v>0.99299999999999999</v>
+      </c>
+      <c r="X256">
+        <v>2E-3</v>
+      </c>
+      <c r="Y256">
+        <v>0</v>
+      </c>
+      <c r="Z256">
+        <v>0</v>
+      </c>
+      <c r="AA256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B257" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="C253" s="40">
+      <c r="C257" s="40">
         <f>P99</f>
         <v>7</v>
       </c>
-      <c r="H253">
+      <c r="H257">
         <v>0.03</v>
       </c>
-      <c r="I253" s="53">
-        <f t="shared" ref="I253:I315" si="10">IF(H253&lt;$C$251/3,   ($C$252*$C$249/$C$253)*(1+(3*($C$250-1)*H253/$C$251)),   IF(H253&lt;=$C$251,   $C$252*$C$249*$C$250/$C$253,   $C$252*$C$249*$C$250/$C$253*($C$251/H253)^(2/3)   ))</f>
+      <c r="I257" s="53">
+        <f t="shared" ref="I257:I319" si="10">IF(H257&lt;$C$255/3,   ($C$256*$C$253/$C$257)*(1+(3*($C$254-1)*H257/$C$255)),   IF(H257&lt;=$C$255,   $C$256*$C$253*$C$254/$C$257,   $C$256*$C$253*$C$254/$C$257*($C$255/H257)^(2/3)   ))</f>
         <v>7.4285714285714288E-2</v>
       </c>
-      <c r="T253">
-        <v>85</v>
-      </c>
-      <c r="U253" t="s">
+      <c r="T257">
+        <v>94</v>
+      </c>
+      <c r="U257" t="s">
         <v>129</v>
       </c>
-      <c r="V253">
+      <c r="V257">
+        <v>-3.952</v>
+      </c>
+      <c r="W257">
+        <v>1.1240000000000001</v>
+      </c>
+      <c r="X257">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="W253">
-        <v>-1.621</v>
-      </c>
-      <c r="X253">
-        <v>-0.97299999999999998</v>
-      </c>
-      <c r="Y253">
-        <v>0</v>
-      </c>
-      <c r="Z253">
-        <v>0</v>
-      </c>
-      <c r="AA253">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B254" s="12" t="s">
+      <c r="Y257">
+        <v>0</v>
+      </c>
+      <c r="Z257">
+        <v>0</v>
+      </c>
+      <c r="AA257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B258" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="C254" s="40">
+      <c r="C258" s="40">
         <f>P97</f>
         <v>6</v>
       </c>
-      <c r="H254">
+      <c r="H258">
         <v>0.04</v>
       </c>
-      <c r="I254" s="53">
+      <c r="I258" s="53">
         <f t="shared" si="10"/>
         <v>0.08</v>
       </c>
-      <c r="T254">
-        <v>88</v>
-      </c>
-      <c r="U254" t="s">
+      <c r="T258">
+        <v>97</v>
+      </c>
+      <c r="U258" t="s">
         <v>129</v>
       </c>
-      <c r="V254">
-        <v>-3.0379999999999998</v>
-      </c>
-      <c r="W254">
-        <v>-4.657</v>
-      </c>
-      <c r="X254">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="Y254">
-        <v>0</v>
-      </c>
-      <c r="Z254">
-        <v>0</v>
-      </c>
-      <c r="AA254">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H255">
+      <c r="V258">
+        <v>-3.2480000000000002</v>
+      </c>
+      <c r="W258">
+        <v>0.83499999999999996</v>
+      </c>
+      <c r="X258">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="Y258">
+        <v>0</v>
+      </c>
+      <c r="Z258">
+        <v>0</v>
+      </c>
+      <c r="AA258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H259">
         <v>0.05</v>
       </c>
-      <c r="I255" s="53">
-        <f>IF(H255&lt;$C$251/3,   ($C$252*$C$249/$C$253)*(1+(3*($C$250-1)*H255/$C$251)),   IF(H255&lt;=$C$251,   $C$252*$C$249*$C$250/$C$253,   $C$252*$C$249*$C$250/$C$253*($C$251/H255)^(2/3)   ))</f>
+      <c r="I259" s="53">
+        <f>IF(H259&lt;$C$255/3,   ($C$256*$C$253/$C$257)*(1+(3*($C$254-1)*H259/$C$255)),   IF(H259&lt;=$C$255,   $C$256*$C$253*$C$254/$C$257,   $C$256*$C$253*$C$254/$C$257*($C$255/H259)^(2/3)   ))</f>
         <v>8.5714285714285715E-2</v>
       </c>
-      <c r="T255">
-        <v>90</v>
-      </c>
-      <c r="U255" t="s">
+      <c r="T259">
+        <v>101</v>
+      </c>
+      <c r="U259" t="s">
         <v>129</v>
       </c>
-      <c r="V255">
-        <v>-2.149</v>
-      </c>
-      <c r="W255">
-        <v>-1.8620000000000001</v>
-      </c>
-      <c r="X255">
-        <v>1.2E-2</v>
-      </c>
-      <c r="Y255">
-        <v>0</v>
-      </c>
-      <c r="Z255">
-        <v>0</v>
-      </c>
-      <c r="AA255">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H256">
+      <c r="V259">
+        <v>-2.6339999999999999</v>
+      </c>
+      <c r="W259">
+        <v>0.66200000000000003</v>
+      </c>
+      <c r="X259">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="Y259">
+        <v>0</v>
+      </c>
+      <c r="Z259">
+        <v>0</v>
+      </c>
+      <c r="AA259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H260">
         <v>0.06</v>
       </c>
-      <c r="I256" s="53">
+      <c r="I260" s="53">
         <f t="shared" si="10"/>
         <v>9.1428571428571442E-2</v>
       </c>
-      <c r="T256">
-        <v>92</v>
-      </c>
-      <c r="U256" t="s">
+      <c r="T260">
+        <v>104</v>
+      </c>
+      <c r="U260" t="s">
         <v>129</v>
       </c>
-      <c r="V256">
-        <v>-4.29</v>
-      </c>
-      <c r="W256">
-        <v>0.99299999999999999</v>
-      </c>
-      <c r="X256">
+      <c r="V260">
+        <v>-2.2410000000000001</v>
+      </c>
+      <c r="W260">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="X260">
         <v>2E-3</v>
       </c>
-      <c r="Y256">
-        <v>0</v>
-      </c>
-      <c r="Z256">
-        <v>0</v>
-      </c>
-      <c r="AA256">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H257">
+      <c r="Y260">
+        <v>0</v>
+      </c>
+      <c r="Z260">
+        <v>0</v>
+      </c>
+      <c r="AA260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H261">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I257" s="53">
+      <c r="I261" s="53">
         <f t="shared" si="10"/>
         <v>9.7142857142857156E-2</v>
       </c>
-      <c r="T257">
-        <v>94</v>
-      </c>
-      <c r="U257" t="s">
+      <c r="T261">
+        <v>107</v>
+      </c>
+      <c r="U261" t="s">
         <v>129</v>
       </c>
-      <c r="V257">
-        <v>-3.952</v>
-      </c>
-      <c r="W257">
-        <v>1.1240000000000001</v>
-      </c>
-      <c r="X257">
+      <c r="V261">
+        <v>-1.9279999999999999</v>
+      </c>
+      <c r="W261">
+        <v>0.443</v>
+      </c>
+      <c r="X261">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="Y257">
-        <v>0</v>
-      </c>
-      <c r="Z257">
-        <v>0</v>
-      </c>
-      <c r="AA257">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H258">
+      <c r="Y261">
+        <v>0</v>
+      </c>
+      <c r="Z261">
+        <v>0</v>
+      </c>
+      <c r="AA261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H262">
         <v>0.08</v>
       </c>
-      <c r="I258" s="53">
+      <c r="I262" s="53">
         <f t="shared" si="10"/>
         <v>0.10285714285714287</v>
       </c>
-      <c r="T258">
-        <v>97</v>
-      </c>
-      <c r="U258" t="s">
+      <c r="T262">
+        <v>111</v>
+      </c>
+      <c r="U262" t="s">
         <v>129</v>
       </c>
-      <c r="V258">
-        <v>-3.2480000000000002</v>
-      </c>
-      <c r="W258">
-        <v>0.83499999999999996</v>
-      </c>
-      <c r="X258">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="Y258">
-        <v>0</v>
-      </c>
-      <c r="Z258">
-        <v>0</v>
-      </c>
-      <c r="AA258">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H259">
+      <c r="V262">
+        <v>-1.6220000000000001</v>
+      </c>
+      <c r="W262">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="X262">
+        <v>0.01</v>
+      </c>
+      <c r="Y262">
+        <v>0</v>
+      </c>
+      <c r="Z262">
+        <v>0</v>
+      </c>
+      <c r="AA262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H263">
         <v>0.09</v>
       </c>
-      <c r="I259" s="53">
+      <c r="I263" s="53">
         <f t="shared" si="10"/>
         <v>0.10857142857142858</v>
       </c>
-      <c r="T259">
-        <v>101</v>
-      </c>
-      <c r="U259" t="s">
+      <c r="T263">
+        <v>115</v>
+      </c>
+      <c r="U263" t="s">
         <v>129</v>
       </c>
-      <c r="V259">
-        <v>-2.6339999999999999</v>
-      </c>
-      <c r="W259">
-        <v>0.66200000000000003</v>
-      </c>
-      <c r="X259">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="Y259">
-        <v>0</v>
-      </c>
-      <c r="Z259">
-        <v>0</v>
-      </c>
-      <c r="AA259">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H260">
+      <c r="V263">
+        <v>-1.383</v>
+      </c>
+      <c r="W263">
+        <v>0.33100000000000002</v>
+      </c>
+      <c r="X263">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="Y263">
+        <v>0</v>
+      </c>
+      <c r="Z263">
+        <v>0</v>
+      </c>
+      <c r="AA263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H264">
         <v>0.1</v>
       </c>
-      <c r="I260" s="53">
+      <c r="I264" s="53">
         <f t="shared" si="10"/>
         <v>0.1142857142857143</v>
       </c>
-      <c r="T260">
-        <v>104</v>
-      </c>
-      <c r="U260" t="s">
+      <c r="T264">
+        <v>116</v>
+      </c>
+      <c r="U264" t="s">
         <v>129</v>
       </c>
-      <c r="V260">
-        <v>-2.2410000000000001</v>
-      </c>
-      <c r="W260">
-        <v>0.56100000000000005</v>
-      </c>
-      <c r="X260">
-        <v>2E-3</v>
-      </c>
-      <c r="Y260">
-        <v>0</v>
-      </c>
-      <c r="Z260">
-        <v>0</v>
-      </c>
-      <c r="AA260">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H261">
+      <c r="V264">
+        <v>-0.06</v>
+      </c>
+      <c r="W264">
+        <v>-0.06</v>
+      </c>
+      <c r="X264">
+        <v>-0.371</v>
+      </c>
+      <c r="Y264">
+        <v>-1.704</v>
+      </c>
+      <c r="Z264">
+        <v>0</v>
+      </c>
+      <c r="AA264">
+        <v>0.27600000000000002</v>
+      </c>
+    </row>
+    <row r="265" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H265">
         <v>0.11</v>
       </c>
-      <c r="I261" s="53">
+      <c r="I265" s="53">
         <f t="shared" si="10"/>
         <v>0.12000000000000001</v>
       </c>
-      <c r="T261">
-        <v>107</v>
-      </c>
-      <c r="U261" t="s">
+      <c r="T265">
+        <v>120</v>
+      </c>
+      <c r="U265" t="s">
         <v>129</v>
       </c>
-      <c r="V261">
-        <v>-1.9279999999999999</v>
-      </c>
-      <c r="W261">
-        <v>0.443</v>
-      </c>
-      <c r="X261">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="Y261">
-        <v>0</v>
-      </c>
-      <c r="Z261">
-        <v>0</v>
-      </c>
-      <c r="AA261">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H262">
+      <c r="V265">
+        <v>-1.2230000000000001</v>
+      </c>
+      <c r="W265">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="X265">
+        <v>0</v>
+      </c>
+      <c r="Y265">
+        <v>0</v>
+      </c>
+      <c r="Z265">
+        <v>0</v>
+      </c>
+      <c r="AA265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H266">
         <v>0.12</v>
       </c>
-      <c r="I262" s="53">
+      <c r="I266" s="53">
         <f t="shared" si="10"/>
         <v>0.12571428571428572</v>
       </c>
-      <c r="T262">
-        <v>111</v>
-      </c>
-      <c r="U262" t="s">
+      <c r="T266">
+        <v>121</v>
+      </c>
+      <c r="U266" t="s">
         <v>129</v>
       </c>
-      <c r="V262">
-        <v>-1.6220000000000001</v>
-      </c>
-      <c r="W262">
-        <v>0.38900000000000001</v>
-      </c>
-      <c r="X262">
-        <v>0.01</v>
-      </c>
-      <c r="Y262">
-        <v>0</v>
-      </c>
-      <c r="Z262">
-        <v>0</v>
-      </c>
-      <c r="AA262">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H263">
+      <c r="V266">
+        <v>-1.123</v>
+      </c>
+      <c r="W266">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="X266">
+        <v>0</v>
+      </c>
+      <c r="Y266">
+        <v>0</v>
+      </c>
+      <c r="Z266">
+        <v>0</v>
+      </c>
+      <c r="AA266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H267">
         <v>0.13</v>
       </c>
-      <c r="I263" s="53">
+      <c r="I267" s="53">
         <f t="shared" si="10"/>
         <v>0.13142857142857142</v>
       </c>
-      <c r="T263">
-        <v>115</v>
-      </c>
-      <c r="U263" t="s">
+      <c r="T267">
+        <v>122</v>
+      </c>
+      <c r="U267" t="s">
         <v>129</v>
       </c>
-      <c r="V263">
-        <v>-1.383</v>
-      </c>
-      <c r="W263">
-        <v>0.33100000000000002</v>
-      </c>
-      <c r="X263">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="Y263">
-        <v>0</v>
-      </c>
-      <c r="Z263">
-        <v>0</v>
-      </c>
-      <c r="AA263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H264">
+      <c r="V267">
+        <v>-1.0820000000000001</v>
+      </c>
+      <c r="W267">
+        <v>-0.16600000000000001</v>
+      </c>
+      <c r="X267">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="Y267">
+        <v>0</v>
+      </c>
+      <c r="Z267">
+        <v>0</v>
+      </c>
+      <c r="AA267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H268">
         <v>0.14000000000000001</v>
       </c>
-      <c r="I264" s="53">
+      <c r="I268" s="53">
         <f t="shared" si="10"/>
         <v>0.13714285714285718</v>
       </c>
-      <c r="T264">
-        <v>116</v>
-      </c>
-      <c r="U264" t="s">
+      <c r="T268">
+        <v>124</v>
+      </c>
+      <c r="U268" t="s">
         <v>129</v>
       </c>
-      <c r="V264">
-        <v>-0.06</v>
-      </c>
-      <c r="W264">
-        <v>-0.06</v>
-      </c>
-      <c r="X264">
-        <v>-0.371</v>
-      </c>
-      <c r="Y264">
-        <v>-1.704</v>
-      </c>
-      <c r="Z264">
-        <v>0</v>
-      </c>
-      <c r="AA264">
-        <v>0.27600000000000002</v>
-      </c>
-    </row>
-    <row r="265" spans="8:27" x14ac:dyDescent="0.3">
-      <c r="H265">
+      <c r="V268">
+        <v>-0.92200000000000004</v>
+      </c>
+      <c r="W268">
+        <v>-0.33700000000000002</v>
+      </c>
+      <c r="X268">
+        <v>1.2E-2</v>
+      </c>
+      <c r="Y268">
+        <v>0</v>
+      </c>
+      <c r="Z268">
+        <v>0</v>
+      </c>
+      <c r="AA268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="8:27" x14ac:dyDescent="0.3">
+      <c r="H269">
         <v>0.15</v>
       </c>
-      <c r="I265" s="53">
+      <c r="I269" s="53">
         <f t="shared" si="10"/>
         <v>0.14285714285714288</v>
       </c>
-      <c r="T265">
-        <v>120</v>
-      </c>
-      <c r="U265" t="s">
+      <c r="T269">
+        <v>125</v>
+      </c>
+      <c r="U269" t="s">
         <v>129</v>
       </c>
-      <c r="V265">
-        <v>-1.2230000000000001</v>
-      </c>
-      <c r="W265">
-        <v>0.28699999999999998</v>
-      </c>
-      <c r="X265">
-        <v>0</v>
-      </c>
-      <c r="Y265">
-        <v>0</v>
-      </c>
-      <c r="Z265">
-        <v>0</v>
-      </c>
-      <c r="AA265">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" spans="8:27" x14ac:dyDescent="0.3">
-      <c r="H266">
+      <c r="V269">
+        <v>-0.81899999999999995</v>
+      </c>
+      <c r="W269">
+        <v>-0.23100000000000001</v>
+      </c>
+      <c r="X269">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="Y269">
+        <v>0</v>
+      </c>
+      <c r="Z269">
+        <v>0</v>
+      </c>
+      <c r="AA269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="8:27" x14ac:dyDescent="0.3">
+      <c r="H270">
         <v>0.16</v>
       </c>
-      <c r="I266" s="53">
+      <c r="I270" s="53">
         <f t="shared" si="10"/>
         <v>0.14857142857142858</v>
       </c>
-      <c r="T266">
-        <v>121</v>
-      </c>
-      <c r="U266" t="s">
+      <c r="T270">
+        <v>126</v>
+      </c>
+      <c r="U270" t="s">
         <v>129</v>
       </c>
-      <c r="V266">
-        <v>-1.123</v>
-      </c>
-      <c r="W266">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="X266">
-        <v>0</v>
-      </c>
-      <c r="Y266">
-        <v>0</v>
-      </c>
-      <c r="Z266">
-        <v>0</v>
-      </c>
-      <c r="AA266">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" spans="8:27" x14ac:dyDescent="0.3">
-      <c r="H267">
+      <c r="V270">
+        <v>-0.90400000000000003</v>
+      </c>
+      <c r="W270">
+        <v>-9.8000000000000004E-2</v>
+      </c>
+      <c r="X270">
+        <v>0</v>
+      </c>
+      <c r="Y270">
+        <v>0</v>
+      </c>
+      <c r="Z270">
+        <v>0</v>
+      </c>
+      <c r="AA270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="8:27" x14ac:dyDescent="0.3">
+      <c r="H271">
         <v>0.17</v>
       </c>
-      <c r="I267" s="53">
+      <c r="I271" s="53">
         <f t="shared" si="10"/>
         <v>0.1542857142857143</v>
       </c>
-      <c r="T267">
-        <v>122</v>
-      </c>
-      <c r="U267" t="s">
+      <c r="T271">
+        <v>127</v>
+      </c>
+      <c r="U271" t="s">
         <v>129</v>
       </c>
-      <c r="V267">
-        <v>-1.0820000000000001</v>
-      </c>
-      <c r="W267">
-        <v>-0.16600000000000001</v>
-      </c>
-      <c r="X267">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="Y267">
-        <v>0</v>
-      </c>
-      <c r="Z267">
-        <v>0</v>
-      </c>
-      <c r="AA267">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" spans="8:27" x14ac:dyDescent="0.3">
-      <c r="H268">
+      <c r="V271">
+        <v>-1.0409999999999999</v>
+      </c>
+      <c r="W271">
+        <v>-0.17</v>
+      </c>
+      <c r="X271">
+        <v>0</v>
+      </c>
+      <c r="Y271">
+        <v>0</v>
+      </c>
+      <c r="Z271">
+        <v>0</v>
+      </c>
+      <c r="AA271">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="8:27" x14ac:dyDescent="0.3">
+      <c r="H272">
         <v>0.18</v>
       </c>
-      <c r="I268" s="53">
+      <c r="I272" s="53">
         <f t="shared" si="10"/>
         <v>0.16000000000000003</v>
       </c>
-      <c r="T268">
-        <v>124</v>
-      </c>
-      <c r="U268" t="s">
+      <c r="T272">
+        <v>128</v>
+      </c>
+      <c r="U272" t="s">
         <v>129</v>
       </c>
-      <c r="V268">
-        <v>-0.92200000000000004</v>
-      </c>
-      <c r="W268">
-        <v>-0.33700000000000002</v>
-      </c>
-      <c r="X268">
-        <v>1.2E-2</v>
-      </c>
-      <c r="Y268">
-        <v>0</v>
-      </c>
-      <c r="Z268">
-        <v>0</v>
-      </c>
-      <c r="AA268">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269" spans="8:27" x14ac:dyDescent="0.3">
-      <c r="H269">
+      <c r="V272">
+        <v>-1.222</v>
+      </c>
+      <c r="W272">
+        <v>-0.42699999999999999</v>
+      </c>
+      <c r="X272">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="Y272">
+        <v>0</v>
+      </c>
+      <c r="Z272">
+        <v>0</v>
+      </c>
+      <c r="AA272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="8:27" x14ac:dyDescent="0.3">
+      <c r="H273">
         <v>0.19</v>
       </c>
-      <c r="I269" s="53">
+      <c r="I273" s="53">
         <f t="shared" si="10"/>
         <v>0.16571428571428576</v>
       </c>
-      <c r="T269">
-        <v>125</v>
-      </c>
-      <c r="U269" t="s">
-        <v>129</v>
-      </c>
-      <c r="V269">
-        <v>-0.81899999999999995</v>
-      </c>
-      <c r="W269">
-        <v>-0.23100000000000001</v>
-      </c>
-      <c r="X269">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="Y269">
-        <v>0</v>
-      </c>
-      <c r="Z269">
-        <v>0</v>
-      </c>
-      <c r="AA269">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270" spans="8:27" x14ac:dyDescent="0.3">
-      <c r="H270">
-        <v>0.2</v>
-      </c>
-      <c r="I270" s="53">
-        <f t="shared" si="10"/>
-        <v>0.17142857142857146</v>
-      </c>
-      <c r="T270">
-        <v>126</v>
-      </c>
-      <c r="U270" t="s">
-        <v>129</v>
-      </c>
-      <c r="V270">
-        <v>-0.90400000000000003</v>
-      </c>
-      <c r="W270">
-        <v>-9.8000000000000004E-2</v>
-      </c>
-      <c r="X270">
-        <v>0</v>
-      </c>
-      <c r="Y270">
-        <v>0</v>
-      </c>
-      <c r="Z270">
-        <v>0</v>
-      </c>
-      <c r="AA270">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="271" spans="8:27" x14ac:dyDescent="0.3">
-      <c r="H271">
-        <v>0.21</v>
-      </c>
-      <c r="I271" s="53">
-        <f t="shared" si="10"/>
-        <v>0.17142857142857146</v>
-      </c>
-      <c r="T271">
-        <v>127</v>
-      </c>
-      <c r="U271" t="s">
-        <v>129</v>
-      </c>
-      <c r="V271">
-        <v>-1.0409999999999999</v>
-      </c>
-      <c r="W271">
-        <v>-0.17</v>
-      </c>
-      <c r="X271">
-        <v>0</v>
-      </c>
-      <c r="Y271">
-        <v>0</v>
-      </c>
-      <c r="Z271">
-        <v>0</v>
-      </c>
-      <c r="AA271">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272" spans="8:27" x14ac:dyDescent="0.3">
-      <c r="H272">
-        <v>0.22</v>
-      </c>
-      <c r="I272" s="53">
-        <f t="shared" si="10"/>
-        <v>0.17142857142857146</v>
-      </c>
-      <c r="T272">
-        <v>128</v>
-      </c>
-      <c r="U272" t="s">
-        <v>129</v>
-      </c>
-      <c r="V272">
-        <v>-1.222</v>
-      </c>
-      <c r="W272">
-        <v>-0.42699999999999999</v>
-      </c>
-      <c r="X272">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="Y272">
-        <v>0</v>
-      </c>
-      <c r="Z272">
-        <v>0</v>
-      </c>
-      <c r="AA272">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273" spans="8:27" x14ac:dyDescent="0.3">
-      <c r="H273">
-        <v>0.23</v>
-      </c>
-      <c r="I273" s="53">
-        <f t="shared" si="10"/>
-        <v>0.17142857142857146</v>
-      </c>
       <c r="T273">
         <v>130</v>
       </c>
@@ -11120,18 +11240,12 @@
     </row>
     <row r="274" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H274">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="I274" s="53">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
-      <c r="K274">
-        <v>0.5</v>
-      </c>
-      <c r="L274">
-        <v>0</v>
-      </c>
       <c r="T274">
         <v>131</v>
       </c>
@@ -11159,18 +11273,12 @@
     </row>
     <row r="275" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H275">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="I275" s="53">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
-      <c r="K275">
-        <v>0.5</v>
-      </c>
-      <c r="L275">
-        <v>0.33</v>
-      </c>
       <c r="T275">
         <v>132</v>
       </c>
@@ -11198,7 +11306,7 @@
     </row>
     <row r="276" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H276">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="I276" s="53">
         <f t="shared" si="10"/>
@@ -11231,18 +11339,12 @@
     </row>
     <row r="277" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H277">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="I277" s="53">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
-      <c r="K277">
-        <v>0.71</v>
-      </c>
-      <c r="L277">
-        <v>0</v>
-      </c>
       <c r="T277">
         <v>135</v>
       </c>
@@ -11270,17 +11372,17 @@
     </row>
     <row r="278" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H278">
-        <v>0.28000000000000003</v>
+        <v>0.24</v>
       </c>
       <c r="I278" s="53">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
       <c r="K278">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="L278">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="T278">
         <v>136</v>
@@ -11309,12 +11411,18 @@
     </row>
     <row r="279" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H279">
-        <v>0.28999999999999998</v>
+        <v>0.25</v>
       </c>
       <c r="I279" s="53">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
+      <c r="K279">
+        <v>0.5</v>
+      </c>
+      <c r="L279">
+        <v>0.33</v>
+      </c>
       <c r="T279">
         <v>137</v>
       </c>
@@ -11342,18 +11450,12 @@
     </row>
     <row r="280" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H280">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="I280" s="53">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
-      <c r="K280">
-        <v>0.94</v>
-      </c>
-      <c r="L280">
-        <v>0</v>
-      </c>
       <c r="T280">
         <v>138</v>
       </c>
@@ -11381,17 +11483,17 @@
     </row>
     <row r="281" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H281">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="I281" s="53">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
       <c r="K281">
-        <v>0.94</v>
+        <v>0.71</v>
       </c>
       <c r="L281">
-        <v>0.217</v>
+        <v>0</v>
       </c>
       <c r="T281">
         <v>140</v>
@@ -11420,16 +11522,22 @@
     </row>
     <row r="282" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H282">
-        <v>0.32</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I282" s="53">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
+      <c r="K282">
+        <v>0.71</v>
+      </c>
+      <c r="L282">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="283" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H283">
-        <v>0.33</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I283" s="53">
         <f t="shared" si="10"/>
@@ -11442,25 +11550,37 @@
     </row>
     <row r="284" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H284">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="I284" s="53">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
+      <c r="K284">
+        <v>0.94</v>
+      </c>
+      <c r="L284">
+        <v>0</v>
+      </c>
     </row>
     <row r="285" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H285">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="I285" s="53">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
+      <c r="K285">
+        <v>0.94</v>
+      </c>
+      <c r="L285">
+        <v>0.217</v>
+      </c>
     </row>
     <row r="286" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H286">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="I286" s="53">
         <f t="shared" si="10"/>
@@ -11469,7 +11589,7 @@
     </row>
     <row r="287" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H287">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="I287" s="53">
         <f t="shared" si="10"/>
@@ -11478,7 +11598,7 @@
     </row>
     <row r="288" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H288">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="I288" s="53">
         <f t="shared" si="10"/>
@@ -11487,7 +11607,7 @@
     </row>
     <row r="289" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H289">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="I289" s="53">
         <f t="shared" si="10"/>
@@ -11496,7 +11616,7 @@
     </row>
     <row r="290" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H290">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="I290" s="53">
         <f t="shared" si="10"/>
@@ -11505,7 +11625,7 @@
     </row>
     <row r="291" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H291">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
       <c r="I291" s="53">
         <f t="shared" si="10"/>
@@ -11514,7 +11634,7 @@
     </row>
     <row r="292" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H292">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="I292" s="53">
         <f t="shared" si="10"/>
@@ -11523,7 +11643,7 @@
     </row>
     <row r="293" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H293">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="I293" s="53">
         <f t="shared" si="10"/>
@@ -11532,7 +11652,7 @@
     </row>
     <row r="294" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H294">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="I294" s="53">
         <f t="shared" si="10"/>
@@ -11541,7 +11661,7 @@
     </row>
     <row r="295" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H295">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="I295" s="53">
         <f t="shared" si="10"/>
@@ -11550,7 +11670,7 @@
     </row>
     <row r="296" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H296">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="I296" s="53">
         <f t="shared" si="10"/>
@@ -11559,7 +11679,7 @@
     </row>
     <row r="297" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H297">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="I297" s="53">
         <f t="shared" si="10"/>
@@ -11568,7 +11688,7 @@
     </row>
     <row r="298" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H298">
-        <v>0.48</v>
+        <v>0.44</v>
       </c>
       <c r="I298" s="53">
         <f t="shared" si="10"/>
@@ -11577,7 +11697,7 @@
     </row>
     <row r="299" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H299">
-        <v>0.49</v>
+        <v>0.45</v>
       </c>
       <c r="I299" s="53">
         <f t="shared" si="10"/>
@@ -11586,7 +11706,7 @@
     </row>
     <row r="300" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H300">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="I300" s="53">
         <f t="shared" si="10"/>
@@ -11595,7 +11715,7 @@
     </row>
     <row r="301" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H301">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="I301" s="53">
         <f t="shared" si="10"/>
@@ -11604,7 +11724,7 @@
     </row>
     <row r="302" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H302">
-        <v>0.52</v>
+        <v>0.48</v>
       </c>
       <c r="I302" s="53">
         <f t="shared" si="10"/>
@@ -11613,7 +11733,7 @@
     </row>
     <row r="303" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H303">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="I303" s="53">
         <f t="shared" si="10"/>
@@ -11622,7 +11742,7 @@
     </row>
     <row r="304" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H304">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="I304" s="53">
         <f t="shared" si="10"/>
@@ -11631,7 +11751,7 @@
     </row>
     <row r="305" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H305">
-        <v>0.55000000000000004</v>
+        <v>0.51</v>
       </c>
       <c r="I305" s="53">
         <f t="shared" si="10"/>
@@ -11640,7 +11760,7 @@
     </row>
     <row r="306" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H306">
-        <v>0.56000000000000005</v>
+        <v>0.52</v>
       </c>
       <c r="I306" s="53">
         <f t="shared" si="10"/>
@@ -11649,7 +11769,7 @@
     </row>
     <row r="307" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H307">
-        <v>0.56999999999999995</v>
+        <v>0.53</v>
       </c>
       <c r="I307" s="53">
         <f t="shared" si="10"/>
@@ -11658,7 +11778,7 @@
     </row>
     <row r="308" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H308">
-        <v>0.57999999999999996</v>
+        <v>0.54</v>
       </c>
       <c r="I308" s="53">
         <f t="shared" si="10"/>
@@ -11667,7 +11787,7 @@
     </row>
     <row r="309" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H309">
-        <v>0.59</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="I309" s="53">
         <f t="shared" si="10"/>
@@ -11676,7 +11796,7 @@
     </row>
     <row r="310" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H310">
-        <v>0.6</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I310" s="53">
         <f t="shared" si="10"/>
@@ -11685,2160 +11805,2196 @@
     </row>
     <row r="311" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H311">
-        <v>0.61</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I311" s="53">
         <f t="shared" si="10"/>
-        <v>0.16954987852001016</v>
+        <v>0.17142857142857146</v>
       </c>
     </row>
     <row r="312" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H312">
-        <v>0.62</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I312" s="53">
         <f t="shared" si="10"/>
-        <v>0.1677218252289068</v>
-      </c>
-    </row>
-    <row r="313" spans="8:9" x14ac:dyDescent="0.3">
+        <v>0.17142857142857146</v>
+      </c>
+    </row>
+    <row r="313" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H313">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="I313" s="53">
         <f t="shared" si="10"/>
-        <v>0.16594226233711895</v>
-      </c>
-    </row>
-    <row r="314" spans="8:9" x14ac:dyDescent="0.3">
+        <v>0.17142857142857146</v>
+      </c>
+    </row>
+    <row r="314" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H314">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="I314" s="53">
         <f t="shared" si="10"/>
-        <v>0.16420916408433284</v>
-      </c>
-    </row>
-    <row r="315" spans="8:9" x14ac:dyDescent="0.3">
+        <v>0.17142857142857146</v>
+      </c>
+    </row>
+    <row r="315" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H315">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="I315" s="53">
         <f t="shared" si="10"/>
-        <v>0.16252061928129335</v>
-      </c>
-    </row>
-    <row r="316" spans="8:9" x14ac:dyDescent="0.3">
+        <v>0.16954987852001016</v>
+      </c>
+    </row>
+    <row r="316" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H316">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="I316" s="53">
-        <f t="shared" ref="I316:I379" si="11">IF(H316&lt;$C$251/3,   ($C$252*$C$249/$C$253)*(1+(3*($C$250-1)*H316/$C$251)),   IF(H316&lt;=$C$251,   $C$252*$C$249*$C$250/$C$253,   $C$252*$C$249*$C$250/$C$253*($C$251/H316)^(2/3)   ))</f>
-        <v>0.16087482318800531</v>
+        <f t="shared" si="10"/>
+        <v>0.1677218252289068</v>
       </c>
     </row>
     <row r="317" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H317">
+        <v>0.63</v>
+      </c>
+      <c r="I317" s="53">
+        <f t="shared" si="10"/>
+        <v>0.16594226233711895</v>
+      </c>
+    </row>
+    <row r="318" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H318">
+        <v>0.64</v>
+      </c>
+      <c r="I318" s="53">
+        <f t="shared" si="10"/>
+        <v>0.16420916408433284</v>
+      </c>
+    </row>
+    <row r="319" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H319">
+        <v>0.65</v>
+      </c>
+      <c r="I319" s="53">
+        <f t="shared" si="10"/>
+        <v>0.16252061928129335</v>
+      </c>
+    </row>
+    <row r="320" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H320">
+        <v>0.66</v>
+      </c>
+      <c r="I320" s="53">
+        <f t="shared" ref="I320:I383" si="11">IF(H320&lt;$C$255/3,   ($C$256*$C$253/$C$257)*(1+(3*($C$254-1)*H320/$C$255)),   IF(H320&lt;=$C$255,   $C$256*$C$253*$C$254/$C$257,   $C$256*$C$253*$C$254/$C$257*($C$255/H320)^(2/3)   ))</f>
+        <v>0.16087482318800531</v>
+      </c>
+    </row>
+    <row r="321" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H321">
         <v>0.67</v>
       </c>
-      <c r="I317" s="53">
+      <c r="I321" s="53">
         <f t="shared" si="11"/>
         <v>0.15927007008059582</v>
       </c>
     </row>
-    <row r="318" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H318">
+    <row r="322" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H322">
         <v>0.68</v>
       </c>
-      <c r="I318" s="53">
+      <c r="I322" s="53">
         <f t="shared" si="11"/>
         <v>0.15770474643915294</v>
       </c>
     </row>
-    <row r="319" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H319">
+    <row r="323" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H323">
         <v>0.69</v>
       </c>
-      <c r="I319" s="53">
+      <c r="I323" s="53">
         <f t="shared" si="11"/>
         <v>0.15617732469639467</v>
       </c>
     </row>
-    <row r="320" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H320">
+    <row r="324" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H324">
         <v>0.7</v>
       </c>
-      <c r="I320" s="53">
+      <c r="I324" s="53">
         <f t="shared" si="11"/>
         <v>0.15468635749362564</v>
       </c>
     </row>
-    <row r="321" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H321">
+    <row r="325" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H325">
         <v>0.71</v>
       </c>
-      <c r="I321" s="53">
+      <c r="I325" s="53">
         <f t="shared" si="11"/>
         <v>0.15323047239623552</v>
       </c>
     </row>
-    <row r="322" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H322">
+    <row r="326" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H326">
         <v>0.72</v>
       </c>
-      <c r="I322" s="53">
+      <c r="I326" s="53">
         <f t="shared" si="11"/>
         <v>0.15180836702608733</v>
       </c>
     </row>
-    <row r="323" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H323">
+    <row r="327" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H327">
         <v>0.73</v>
       </c>
-      <c r="I323" s="53">
+      <c r="I327" s="53">
         <f t="shared" si="11"/>
         <v>0.15041880457263548</v>
       </c>
     </row>
-    <row r="324" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H324">
+    <row r="328" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H328">
         <v>0.74</v>
       </c>
-      <c r="I324" s="53">
+      <c r="I328" s="53">
         <f t="shared" si="11"/>
         <v>0.14906060964857532</v>
       </c>
     </row>
-    <row r="325" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H325">
+    <row r="329" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H329">
         <v>0.75</v>
       </c>
-      <c r="I325" s="53">
+      <c r="I329" s="53">
         <f t="shared" si="11"/>
         <v>0.1477326644593292</v>
       </c>
     </row>
-    <row r="326" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H326">
+    <row r="330" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H330">
         <v>0.76</v>
       </c>
-      <c r="I326" s="53">
+      <c r="I330" s="53">
         <f t="shared" si="11"/>
         <v>0.14643390525877864</v>
       </c>
     </row>
-    <row r="327" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H327">
+    <row r="331" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H331">
         <v>0.77</v>
       </c>
-      <c r="I327" s="53">
+      <c r="I331" s="53">
         <f t="shared" si="11"/>
         <v>0.14516331906640431</v>
       </c>
     </row>
-    <row r="328" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H328">
+    <row r="332" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H332">
         <v>0.78</v>
       </c>
-      <c r="I328" s="53">
+      <c r="I332" s="53">
         <f t="shared" si="11"/>
         <v>0.14391994062344254</v>
       </c>
     </row>
-    <row r="329" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H329">
+    <row r="333" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H333">
         <v>0.79</v>
       </c>
-      <c r="I329" s="53">
+      <c r="I333" s="53">
         <f t="shared" si="11"/>
         <v>0.1427028495678451</v>
       </c>
     </row>
-    <row r="330" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H330">
+    <row r="334" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H334">
         <v>0.8</v>
       </c>
-      <c r="I330" s="53">
+      <c r="I334" s="53">
         <f t="shared" si="11"/>
         <v>0.14151116780976972</v>
       </c>
     </row>
-    <row r="331" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H331">
+    <row r="335" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H335">
         <v>0.81</v>
       </c>
-      <c r="I331" s="53">
+      <c r="I335" s="53">
         <f t="shared" si="11"/>
         <v>0.14034405709106237</v>
       </c>
     </row>
-    <row r="332" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H332">
+    <row r="336" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H336">
         <v>0.82</v>
       </c>
-      <c r="I332" s="53">
+      <c r="I336" s="53">
         <f t="shared" si="11"/>
         <v>0.13920071671374129</v>
       </c>
     </row>
-    <row r="333" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H333">
+    <row r="337" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H337">
         <v>0.83</v>
       </c>
-      <c r="I333" s="53">
+      <c r="I337" s="53">
         <f t="shared" si="11"/>
         <v>0.13808038142388113</v>
       </c>
     </row>
-    <row r="334" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H334">
+    <row r="338" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H338">
         <v>0.84</v>
       </c>
-      <c r="I334" s="53">
+      <c r="I338" s="53">
         <f t="shared" si="11"/>
         <v>0.13698231943853842</v>
       </c>
     </row>
-    <row r="335" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H335">
+    <row r="339" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H339">
         <v>0.85</v>
       </c>
-      <c r="I335" s="53">
+      <c r="I339" s="53">
         <f t="shared" si="11"/>
         <v>0.13590583060447733</v>
       </c>
     </row>
-    <row r="336" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H336">
+    <row r="340" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H340">
         <v>0.86</v>
       </c>
-      <c r="I336" s="53">
+      <c r="I340" s="53">
         <f t="shared" si="11"/>
         <v>0.13485024467845858</v>
       </c>
     </row>
-    <row r="337" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H337">
+    <row r="341" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H341">
         <v>0.87</v>
       </c>
-      <c r="I337" s="53">
+      <c r="I341" s="53">
         <f t="shared" si="11"/>
         <v>0.13381491971975773</v>
       </c>
     </row>
-    <row r="338" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H338">
+    <row r="342" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H342">
         <v>0.88</v>
       </c>
-      <c r="I338" s="53">
+      <c r="I342" s="53">
         <f t="shared" si="11"/>
         <v>0.13279924058639495</v>
       </c>
     </row>
-    <row r="339" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H339">
+    <row r="343" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H343">
         <v>0.89</v>
       </c>
-      <c r="I339" s="53">
+      <c r="I343" s="53">
         <f t="shared" si="11"/>
         <v>0.131802617527292</v>
       </c>
     </row>
-    <row r="340" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H340">
+    <row r="344" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H344">
         <v>0.9</v>
       </c>
-      <c r="I340" s="53">
+      <c r="I344" s="53">
         <f t="shared" si="11"/>
         <v>0.13082448486323794</v>
       </c>
     </row>
-    <row r="341" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H341">
+    <row r="345" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H345">
         <v>0.91</v>
       </c>
-      <c r="I341" s="53">
+      <c r="I345" s="53">
         <f t="shared" si="11"/>
         <v>0.12986429975014538</v>
       </c>
     </row>
-    <row r="342" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H342">
+    <row r="346" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H346">
         <v>0.92</v>
       </c>
-      <c r="I342" s="53">
+      <c r="I346" s="53">
         <f t="shared" si="11"/>
         <v>0.1289215410186223</v>
       </c>
     </row>
-    <row r="343" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H343">
+    <row r="347" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H347">
         <v>0.93</v>
       </c>
-      <c r="I343" s="53">
+      <c r="I347" s="53">
         <f t="shared" si="11"/>
         <v>0.12799570808438024</v>
       </c>
     </row>
-    <row r="344" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H344">
+    <row r="348" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H348">
         <v>0.94</v>
       </c>
-      <c r="I344" s="53">
+      <c r="I348" s="53">
         <f t="shared" si="11"/>
         <v>0.12708631992444461</v>
       </c>
     </row>
-    <row r="345" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H345">
+    <row r="349" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H349">
         <v>0.95</v>
       </c>
-      <c r="I345" s="53">
+      <c r="I349" s="53">
         <f t="shared" si="11"/>
         <v>0.126192914114542</v>
       </c>
     </row>
-    <row r="346" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H346">
+    <row r="350" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H350">
         <v>0.96</v>
       </c>
-      <c r="I346" s="53">
+      <c r="I350" s="53">
         <f t="shared" si="11"/>
         <v>0.12531504592340856</v>
       </c>
     </row>
-    <row r="347" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H347">
+    <row r="351" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H351">
         <v>0.97</v>
       </c>
-      <c r="I347" s="53">
+      <c r="I351" s="53">
         <f t="shared" si="11"/>
         <v>0.12445228746010001</v>
       </c>
     </row>
-    <row r="348" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H348">
+    <row r="352" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H352">
         <v>0.98</v>
       </c>
-      <c r="I348" s="53">
+      <c r="I352" s="53">
         <f t="shared" si="11"/>
         <v>0.123604226870692</v>
       </c>
     </row>
-    <row r="349" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H349">
+    <row r="353" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H353">
         <v>0.99</v>
       </c>
-      <c r="I349" s="53">
+      <c r="I353" s="53">
         <f t="shared" si="11"/>
         <v>0.12277046758103911</v>
       </c>
     </row>
-    <row r="350" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H350">
+    <row r="354" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H354">
         <v>1</v>
       </c>
-      <c r="I350" s="53">
+      <c r="I354" s="53">
         <f t="shared" si="11"/>
         <v>0.12195062758251644</v>
       </c>
     </row>
-    <row r="351" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H351">
+    <row r="355" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H355">
         <v>1.01</v>
       </c>
-      <c r="I351" s="53">
+      <c r="I355" s="53">
         <f t="shared" si="11"/>
         <v>0.12114433875790227</v>
       </c>
     </row>
-    <row r="352" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H352">
+    <row r="356" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H356">
         <v>1.02</v>
       </c>
-      <c r="I352" s="53">
+      <c r="I356" s="53">
         <f t="shared" si="11"/>
         <v>0.1203512462447735</v>
       </c>
     </row>
-    <row r="353" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H353">
+    <row r="357" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H357">
         <v>1.03</v>
       </c>
-      <c r="I353" s="53">
+      <c r="I357" s="53">
         <f t="shared" si="11"/>
         <v>0.11957100783398215</v>
       </c>
     </row>
-    <row r="354" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H354">
+    <row r="358" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H358">
         <v>1.04</v>
       </c>
-      <c r="I354" s="53">
+      <c r="I358" s="53">
         <f t="shared" si="11"/>
         <v>0.11880329340096042</v>
       </c>
     </row>
-    <row r="355" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H355">
+    <row r="359" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H359">
         <v>1.05</v>
       </c>
-      <c r="I355" s="53">
+      <c r="I359" s="53">
         <f t="shared" si="11"/>
         <v>0.11804778436776639</v>
       </c>
     </row>
-    <row r="356" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H356">
+    <row r="360" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H360">
         <v>1.06</v>
       </c>
-      <c r="I356" s="53">
+      <c r="I360" s="53">
         <f t="shared" si="11"/>
         <v>0.11730417319393414</v>
       </c>
     </row>
-    <row r="357" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H357">
+    <row r="361" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H361">
         <v>1.07</v>
       </c>
-      <c r="I357" s="53">
+      <c r="I361" s="53">
         <f t="shared" si="11"/>
         <v>0.11657216289433078</v>
       </c>
     </row>
-    <row r="358" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H358">
+    <row r="362" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H362">
         <v>1.08</v>
       </c>
-      <c r="I358" s="53">
+      <c r="I362" s="53">
         <f t="shared" si="11"/>
         <v>0.1158514665823505</v>
       </c>
     </row>
-    <row r="359" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H359">
+    <row r="363" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H363">
         <v>1.0900000000000001</v>
       </c>
-      <c r="I359" s="53">
+      <c r="I363" s="53">
         <f t="shared" si="11"/>
         <v>0.11514180703689374</v>
       </c>
     </row>
-    <row r="360" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H360">
+    <row r="364" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H364">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I360" s="53">
+      <c r="I364" s="53">
         <f t="shared" si="11"/>
         <v>0.11444291629168775</v>
       </c>
     </row>
-    <row r="361" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H361">
+    <row r="365" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H365">
         <v>1.1100000000000001</v>
       </c>
-      <c r="I361" s="53">
+      <c r="I365" s="53">
         <f t="shared" si="11"/>
         <v>0.1137545352456045</v>
       </c>
     </row>
-    <row r="362" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H362">
+    <row r="366" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H366">
         <v>1.1200000000000001</v>
       </c>
-      <c r="I362" s="53">
+      <c r="I366" s="53">
         <f t="shared" si="11"/>
         <v>0.11307641329272453</v>
       </c>
     </row>
-    <row r="363" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H363">
+    <row r="367" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H367">
         <v>1.1299999999999999</v>
       </c>
-      <c r="I363" s="53">
+      <c r="I367" s="53">
         <f t="shared" si="11"/>
         <v>0.11240830797097949</v>
       </c>
     </row>
-    <row r="364" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H364">
+    <row r="368" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H368">
         <v>1.1399999999999999</v>
       </c>
-      <c r="I364" s="53">
+      <c r="I368" s="53">
         <f t="shared" si="11"/>
         <v>0.11174998462828611</v>
       </c>
     </row>
-    <row r="365" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H365">
+    <row r="369" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H369">
         <v>1.1499999999999999</v>
       </c>
-      <c r="I365" s="53">
+      <c r="I369" s="53">
         <f t="shared" si="11"/>
         <v>0.11110121610515532</v>
       </c>
     </row>
-    <row r="366" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H366">
+    <row r="370" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H370">
         <v>1.1599999999999999</v>
       </c>
-      <c r="I366" s="53">
+      <c r="I370" s="53">
         <f t="shared" si="11"/>
         <v>0.11046178243282875</v>
       </c>
     </row>
-    <row r="367" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H367">
+    <row r="371" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H371">
         <v>1.17</v>
       </c>
-      <c r="I367" s="53">
+      <c r="I371" s="53">
         <f t="shared" si="11"/>
         <v>0.10983147054605637</v>
       </c>
     </row>
-    <row r="368" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H368">
+    <row r="372" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H372">
         <v>1.18</v>
       </c>
-      <c r="I368" s="53">
+      <c r="I372" s="53">
         <f t="shared" si="11"/>
         <v>0.10921007400968709</v>
       </c>
     </row>
-    <row r="369" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H369">
+    <row r="373" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H373">
         <v>1.19</v>
       </c>
-      <c r="I369" s="53">
+      <c r="I373" s="53">
         <f t="shared" si="11"/>
         <v>0.10859739275829733</v>
       </c>
     </row>
-    <row r="370" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H370">
+    <row r="374" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H374">
         <v>1.2</v>
       </c>
-      <c r="I370" s="53">
+      <c r="I374" s="53">
         <f t="shared" si="11"/>
         <v>0.107993232848132</v>
       </c>
     </row>
-    <row r="371" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H371">
+    <row r="375" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H375">
         <v>1.21</v>
       </c>
-      <c r="I371" s="53">
+      <c r="I375" s="53">
         <f t="shared" si="11"/>
         <v>0.10739740622067891</v>
       </c>
     </row>
-    <row r="372" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H372">
+    <row r="376" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H376">
         <v>1.22</v>
       </c>
-      <c r="I372" s="53">
+      <c r="I376" s="53">
         <f t="shared" si="11"/>
         <v>0.10680973047723971</v>
       </c>
     </row>
-    <row r="373" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H373">
+    <row r="377" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H377">
         <v>1.23</v>
       </c>
-      <c r="I373" s="53">
+      <c r="I377" s="53">
         <f t="shared" si="11"/>
         <v>0.10623002866390084</v>
       </c>
     </row>
-    <row r="374" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H374">
+    <row r="378" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H378">
         <v>1.24</v>
       </c>
-      <c r="I374" s="53">
+      <c r="I378" s="53">
         <f t="shared" si="11"/>
         <v>0.10565812906634435</v>
       </c>
     </row>
-    <row r="375" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H375">
+    <row r="379" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H379">
         <v>1.25</v>
       </c>
-      <c r="I375" s="53">
+      <c r="I379" s="53">
         <f t="shared" si="11"/>
         <v>0.10509386501397301</v>
       </c>
     </row>
-    <row r="376" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H376">
+    <row r="380" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H380">
         <v>1.26</v>
       </c>
-      <c r="I376" s="53">
+      <c r="I380" s="53">
         <f t="shared" si="11"/>
         <v>0.1045370746928567</v>
       </c>
     </row>
-    <row r="377" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H377">
+    <row r="381" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H381">
         <v>1.27</v>
       </c>
-      <c r="I377" s="53">
+      <c r="I381" s="53">
         <f t="shared" si="11"/>
         <v>0.10398760096703577</v>
       </c>
     </row>
-    <row r="378" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H378">
+    <row r="382" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H382">
         <v>1.28</v>
       </c>
-      <c r="I378" s="53">
+      <c r="I382" s="53">
         <f t="shared" si="11"/>
         <v>0.10344529120774607</v>
       </c>
     </row>
-    <row r="379" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H379">
+    <row r="383" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H383">
         <v>1.29</v>
       </c>
-      <c r="I379" s="53">
+      <c r="I383" s="53">
         <f t="shared" si="11"/>
         <v>0.10290999713015545</v>
       </c>
     </row>
-    <row r="380" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H380">
+    <row r="384" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H384">
         <v>1.3</v>
       </c>
-      <c r="I380" s="53">
-        <f t="shared" ref="I380:I443" si="12">IF(H380&lt;$C$251/3,   ($C$252*$C$249/$C$253)*(1+(3*($C$250-1)*H380/$C$251)),   IF(H380&lt;=$C$251,   $C$252*$C$249*$C$250/$C$253,   $C$252*$C$249*$C$250/$C$253*($C$251/H380)^(2/3)   ))</f>
+      <c r="I384" s="53">
+        <f t="shared" ref="I384:I447" si="12">IF(H384&lt;$C$255/3,   ($C$256*$C$253/$C$257)*(1+(3*($C$254-1)*H384/$C$255)),   IF(H384&lt;=$C$255,   $C$256*$C$253*$C$254/$C$257,   $C$256*$C$253*$C$254/$C$257*($C$255/H384)^(2/3)   ))</f>
         <v>0.10238157463722605</v>
       </c>
     </row>
-    <row r="381" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H381">
+    <row r="385" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H385">
         <v>1.31</v>
       </c>
-      <c r="I381" s="53">
+      <c r="I385" s="53">
         <f t="shared" si="12"/>
         <v>0.10185988367033932</v>
       </c>
     </row>
-    <row r="382" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H382">
+    <row r="386" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H386">
         <v>1.32</v>
       </c>
-      <c r="I382" s="53">
+      <c r="I386" s="53">
         <f t="shared" si="12"/>
         <v>0.10134478806634185</v>
       </c>
     </row>
-    <row r="383" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H383">
+    <row r="387" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H387">
         <v>1.33</v>
       </c>
-      <c r="I383" s="53">
+      <c r="I387" s="53">
         <f t="shared" si="12"/>
         <v>0.10083615542068967</v>
       </c>
     </row>
-    <row r="384" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H384">
+    <row r="388" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H388">
         <v>1.34</v>
       </c>
-      <c r="I384" s="53">
+      <c r="I388" s="53">
         <f t="shared" si="12"/>
         <v>0.10033385695638715</v>
       </c>
     </row>
-    <row r="385" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H385">
+    <row r="389" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H389">
         <v>1.35</v>
       </c>
-      <c r="I385" s="53">
+      <c r="I389" s="53">
         <f t="shared" si="12"/>
         <v>9.9837767398434168E-2</v>
       </c>
     </row>
-    <row r="386" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H386">
+    <row r="390" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H390">
         <v>1.36</v>
       </c>
-      <c r="I386" s="53">
+      <c r="I390" s="53">
         <f t="shared" si="12"/>
         <v>9.934776485351117E-2</v>
       </c>
     </row>
-    <row r="387" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H387">
+    <row r="391" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H391">
         <v>1.37</v>
       </c>
-      <c r="I387" s="53">
+      <c r="I391" s="53">
         <f t="shared" si="12"/>
         <v>9.8863730694646768E-2</v>
       </c>
     </row>
-    <row r="388" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H388">
+    <row r="392" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H392">
         <v>1.38</v>
       </c>
-      <c r="I388" s="53">
+      <c r="I392" s="53">
         <f t="shared" si="12"/>
         <v>9.8385549450627038E-2</v>
       </c>
     </row>
-    <row r="389" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H389">
+    <row r="393" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H393">
         <v>1.39</v>
       </c>
-      <c r="I389" s="53">
+      <c r="I393" s="53">
         <f t="shared" si="12"/>
         <v>9.7913108699918719E-2</v>
       </c>
     </row>
-    <row r="390" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H390">
+    <row r="394" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H394">
         <v>1.4</v>
       </c>
-      <c r="I390" s="53">
+      <c r="I394" s="53">
         <f t="shared" si="12"/>
         <v>9.7446298968891246E-2</v>
       </c>
     </row>
-    <row r="391" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H391">
+    <row r="395" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H395">
         <v>1.41</v>
       </c>
-      <c r="I391" s="53">
+      <c r="I395" s="53">
         <f t="shared" si="12"/>
         <v>9.6985013634134004E-2</v>
       </c>
     </row>
-    <row r="392" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H392">
+    <row r="396" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H396">
         <v>1.42</v>
       </c>
-      <c r="I392" s="53">
+      <c r="I396" s="53">
         <f t="shared" si="12"/>
         <v>9.6529148828676206E-2</v>
       </c>
     </row>
-    <row r="393" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H393">
+    <row r="397" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H397">
         <v>1.43</v>
       </c>
-      <c r="I393" s="53">
+      <c r="I397" s="53">
         <f t="shared" si="12"/>
         <v>9.6078603351927624E-2</v>
       </c>
     </row>
-    <row r="394" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H394">
+    <row r="398" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H398">
         <v>1.44</v>
       </c>
-      <c r="I394" s="53">
+      <c r="I398" s="53">
         <f t="shared" si="12"/>
         <v>9.56332785831671E-2</v>
       </c>
     </row>
-    <row r="395" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H395">
+    <row r="399" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H399">
         <v>1.45</v>
       </c>
-      <c r="I395" s="53">
+      <c r="I399" s="53">
         <f t="shared" si="12"/>
         <v>9.5193078398416328E-2</v>
       </c>
     </row>
-    <row r="396" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H396">
+    <row r="400" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H400">
         <v>1.46</v>
       </c>
-      <c r="I396" s="53">
+      <c r="I400" s="53">
         <f t="shared" si="12"/>
         <v>9.4757909090543324E-2</v>
       </c>
     </row>
-    <row r="397" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H397">
+    <row r="401" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H401">
         <v>1.47</v>
       </c>
-      <c r="I397" s="53">
+      <c r="I401" s="53">
         <f t="shared" si="12"/>
         <v>9.432767929244959E-2</v>
       </c>
     </row>
-    <row r="398" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H398">
+    <row r="402" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H402">
         <v>1.48</v>
       </c>
-      <c r="I398" s="53">
+      <c r="I402" s="53">
         <f t="shared" si="12"/>
         <v>9.3902299903201439E-2</v>
       </c>
     </row>
-    <row r="399" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H399">
+    <row r="403" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H403">
         <v>1.49</v>
       </c>
-      <c r="I399" s="53">
+      <c r="I403" s="53">
         <f t="shared" si="12"/>
         <v>9.3481684016974015E-2</v>
       </c>
     </row>
-    <row r="400" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H400">
+    <row r="404" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H404">
         <v>1.5</v>
       </c>
-      <c r="I400" s="53">
+      <c r="I404" s="53">
         <f t="shared" si="12"/>
         <v>9.3065746854682524E-2</v>
       </c>
     </row>
-    <row r="401" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H401">
+    <row r="405" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H405">
         <v>1.51</v>
       </c>
-      <c r="I401" s="53">
+      <c r="I405" s="53">
         <f t="shared" si="12"/>
         <v>9.2654405698182091E-2</v>
       </c>
     </row>
-    <row r="402" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H402">
+    <row r="406" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H406">
         <v>1.52</v>
       </c>
-      <c r="I402" s="53">
+      <c r="I406" s="53">
         <f t="shared" si="12"/>
         <v>9.2247579826923401E-2</v>
       </c>
     </row>
-    <row r="403" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H403">
+    <row r="407" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H407">
         <v>1.53</v>
       </c>
-      <c r="I403" s="53">
+      <c r="I407" s="53">
         <f t="shared" si="12"/>
         <v>9.1845190456956952E-2</v>
       </c>
     </row>
-    <row r="404" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H404">
+    <row r="408" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H408">
         <v>1.54</v>
       </c>
-      <c r="I404" s="53">
+      <c r="I408" s="53">
         <f t="shared" si="12"/>
         <v>9.1447160682184309E-2</v>
       </c>
     </row>
-    <row r="405" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H405">
+    <row r="409" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H409">
         <v>1.55</v>
       </c>
-      <c r="I405" s="53">
+      <c r="I409" s="53">
         <f t="shared" si="12"/>
         <v>9.105341541775934E-2</v>
       </c>
     </row>
-    <row r="406" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H406">
+    <row r="410" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H410">
         <v>1.56</v>
       </c>
-      <c r="I406" s="53">
+      <c r="I410" s="53">
         <f t="shared" si="12"/>
         <v>9.0663881345547773E-2</v>
       </c>
     </row>
-    <row r="407" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H407">
+    <row r="411" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H411">
         <v>1.57</v>
       </c>
-      <c r="I407" s="53">
+      <c r="I411" s="53">
         <f t="shared" si="12"/>
         <v>9.0278486861557219E-2</v>
       </c>
     </row>
-    <row r="408" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H408">
+    <row r="412" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H412">
         <v>1.58</v>
       </c>
-      <c r="I408" s="53">
+      <c r="I412" s="53">
         <f t="shared" si="12"/>
         <v>8.9897162025254787E-2</v>
       </c>
     </row>
-    <row r="409" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H409">
+    <row r="413" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H413">
         <v>1.59</v>
       </c>
-      <c r="I409" s="53">
+      <c r="I413" s="53">
         <f t="shared" si="12"/>
         <v>8.9519838510692798E-2</v>
       </c>
     </row>
-    <row r="410" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H410">
+    <row r="414" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H414">
         <v>1.6</v>
       </c>
-      <c r="I410" s="53">
+      <c r="I414" s="53">
         <f t="shared" si="12"/>
         <v>8.9146449559367333E-2</v>
       </c>
     </row>
-    <row r="411" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H411">
+    <row r="415" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H415">
         <v>1.61</v>
       </c>
-      <c r="I411" s="53">
+      <c r="I415" s="53">
         <f t="shared" si="12"/>
         <v>8.8776929934737764E-2</v>
       </c>
     </row>
-    <row r="412" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H412">
+    <row r="416" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H416">
         <v>1.62</v>
       </c>
-      <c r="I412" s="53">
+      <c r="I416" s="53">
         <f t="shared" si="12"/>
         <v>8.8411215878338653E-2</v>
       </c>
     </row>
-    <row r="413" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H413">
+    <row r="417" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H417">
         <v>1.63</v>
       </c>
-      <c r="I413" s="53">
+      <c r="I417" s="53">
         <f t="shared" si="12"/>
         <v>8.8049245067419249E-2</v>
       </c>
     </row>
-    <row r="414" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H414">
+    <row r="418" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H418">
         <v>1.64</v>
       </c>
-      <c r="I414" s="53">
+      <c r="I418" s="53">
         <f t="shared" si="12"/>
         <v>8.7690956574047879E-2</v>
       </c>
     </row>
-    <row r="415" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H415">
+    <row r="419" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H419">
         <v>1.65</v>
       </c>
-      <c r="I415" s="53">
+      <c r="I419" s="53">
         <f t="shared" si="12"/>
         <v>8.7336290825622484E-2</v>
       </c>
     </row>
-    <row r="416" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H416">
+    <row r="420" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H420">
         <v>1.66</v>
       </c>
-      <c r="I416" s="53">
+      <c r="I420" s="53">
         <f t="shared" si="12"/>
         <v>8.6985189566730431E-2</v>
       </c>
     </row>
-    <row r="417" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H417">
+    <row r="421" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H421">
         <v>1.67</v>
       </c>
-      <c r="I417" s="53">
+      <c r="I421" s="53">
         <f t="shared" si="12"/>
         <v>8.6637595822303889E-2</v>
       </c>
     </row>
-    <row r="418" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H418">
+    <row r="422" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H422">
         <v>1.68</v>
       </c>
-      <c r="I418" s="53">
+      <c r="I422" s="53">
         <f t="shared" si="12"/>
         <v>8.6293453862019115E-2</v>
       </c>
     </row>
-    <row r="419" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H419">
+    <row r="423" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H423">
         <v>1.69</v>
       </c>
-      <c r="I419" s="53">
+      <c r="I423" s="53">
         <f t="shared" si="12"/>
         <v>8.5952709165890706E-2</v>
       </c>
     </row>
-    <row r="420" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H420">
+    <row r="424" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H424">
         <v>1.7</v>
       </c>
-      <c r="I420" s="53">
+      <c r="I424" s="53">
         <f t="shared" si="12"/>
         <v>8.5615308391013945E-2</v>
       </c>
     </row>
-    <row r="421" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H421">
+    <row r="425" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H425">
         <v>1.71</v>
       </c>
-      <c r="I421" s="53">
+      <c r="I425" s="53">
         <f t="shared" si="12"/>
         <v>8.5281199339410016E-2</v>
       </c>
     </row>
-    <row r="422" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H422">
+    <row r="426" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H426">
         <v>1.72</v>
       </c>
-      <c r="I422" s="53">
+      <c r="I426" s="53">
         <f t="shared" si="12"/>
         <v>8.4950330926932036E-2</v>
       </c>
     </row>
-    <row r="423" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H423">
+    <row r="427" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H427">
         <v>1.73</v>
       </c>
-      <c r="I423" s="53">
+      <c r="I427" s="53">
         <f t="shared" si="12"/>
         <v>8.462265315319023E-2</v>
       </c>
     </row>
-    <row r="424" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H424">
+    <row r="428" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H428">
         <v>1.74</v>
       </c>
-      <c r="I424" s="53">
+      <c r="I428" s="53">
         <f t="shared" si="12"/>
         <v>8.4298117072457671E-2</v>
       </c>
     </row>
-    <row r="425" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H425">
+    <row r="429" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H429">
         <v>1.75</v>
       </c>
-      <c r="I425" s="53">
+      <c r="I429" s="53">
         <f t="shared" si="12"/>
         <v>8.3976674765518997E-2</v>
       </c>
     </row>
-    <row r="426" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H426">
+    <row r="430" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H430">
         <v>1.76</v>
       </c>
-      <c r="I426" s="53">
+      <c r="I430" s="53">
         <f t="shared" si="12"/>
         <v>8.3658279312426295E-2</v>
       </c>
     </row>
-    <row r="427" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H427">
+    <row r="431" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H431">
         <v>1.77</v>
       </c>
-      <c r="I427" s="53">
+      <c r="I431" s="53">
         <f t="shared" si="12"/>
         <v>8.3342884766128181E-2</v>
       </c>
     </row>
-    <row r="428" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H428">
+    <row r="432" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H432">
         <v>1.78</v>
       </c>
-      <c r="I428" s="53">
+      <c r="I432" s="53">
         <f t="shared" si="12"/>
         <v>8.3030446126939078E-2</v>
       </c>
     </row>
-    <row r="429" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H429">
+    <row r="433" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H433">
         <v>1.79</v>
       </c>
-      <c r="I429" s="53">
+      <c r="I433" s="53">
         <f t="shared" si="12"/>
         <v>8.2720919317817471E-2</v>
       </c>
     </row>
-    <row r="430" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H430">
+    <row r="434" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H434">
         <v>1.8</v>
       </c>
-      <c r="I430" s="53">
+      <c r="I434" s="53">
         <f t="shared" si="12"/>
         <v>8.2414261160423344E-2</v>
       </c>
     </row>
-    <row r="431" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H431">
+    <row r="435" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H435">
         <v>1.81</v>
       </c>
-      <c r="I431" s="53">
+      <c r="I435" s="53">
         <f t="shared" si="12"/>
         <v>8.2110429351925696E-2</v>
       </c>
     </row>
-    <row r="432" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H432">
+    <row r="436" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H436">
         <v>1.82</v>
       </c>
-      <c r="I432" s="53">
+      <c r="I436" s="53">
         <f t="shared" si="12"/>
         <v>8.180938244253283E-2</v>
       </c>
     </row>
-    <row r="433" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H433">
+    <row r="437" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H437">
         <v>1.83</v>
       </c>
-      <c r="I433" s="53">
+      <c r="I437" s="53">
         <f t="shared" si="12"/>
         <v>8.1511079813719314E-2</v>
       </c>
     </row>
-    <row r="434" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H434">
+    <row r="438" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H438">
         <v>1.84</v>
       </c>
-      <c r="I434" s="53">
+      <c r="I438" s="53">
         <f t="shared" si="12"/>
         <v>8.1215481657123792E-2</v>
       </c>
     </row>
-    <row r="435" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H435">
+    <row r="439" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H439">
         <v>1.85</v>
       </c>
-      <c r="I435" s="53">
+      <c r="I439" s="53">
         <f t="shared" si="12"/>
         <v>8.0922548954093912E-2</v>
       </c>
     </row>
-    <row r="436" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H436">
+    <row r="440" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H440">
         <v>1.86</v>
       </c>
-      <c r="I436" s="53">
+      <c r="I440" s="53">
         <f t="shared" si="12"/>
         <v>8.063224345585504E-2</v>
       </c>
     </row>
-    <row r="437" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H437">
+    <row r="441" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H441">
         <v>1.87</v>
       </c>
-      <c r="I437" s="53">
+      <c r="I441" s="53">
         <f t="shared" si="12"/>
         <v>8.0344527664280296E-2</v>
       </c>
     </row>
-    <row r="438" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H438">
+    <row r="442" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H442">
         <v>1.88</v>
       </c>
-      <c r="I438" s="53">
+      <c r="I442" s="53">
         <f t="shared" si="12"/>
         <v>8.0059364813240996E-2</v>
       </c>
     </row>
-    <row r="439" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H439">
+    <row r="443" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H443">
         <v>1.89</v>
       </c>
-      <c r="I439" s="53">
+      <c r="I443" s="53">
         <f t="shared" si="12"/>
         <v>7.9776718850516348E-2</v>
       </c>
     </row>
-    <row r="440" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H440">
+    <row r="444" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H444">
         <v>1.9</v>
       </c>
-      <c r="I440" s="53">
+      <c r="I444" s="53">
         <f t="shared" si="12"/>
         <v>7.9496554420243656E-2</v>
       </c>
     </row>
-    <row r="441" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H441">
+    <row r="445" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H445">
         <v>1.91</v>
       </c>
-      <c r="I441" s="53">
+      <c r="I445" s="53">
         <f t="shared" si="12"/>
         <v>7.9218836845889234E-2</v>
       </c>
     </row>
-    <row r="442" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H442">
+    <row r="446" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H446">
         <v>1.92</v>
       </c>
-      <c r="I442" s="53">
+      <c r="I446" s="53">
         <f t="shared" si="12"/>
         <v>7.8943532113722584E-2</v>
       </c>
     </row>
-    <row r="443" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H443">
+    <row r="447" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H447">
         <v>1.93</v>
       </c>
-      <c r="I443" s="53">
+      <c r="I447" s="53">
         <f t="shared" si="12"/>
         <v>7.8670606856776112E-2</v>
       </c>
     </row>
-    <row r="444" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H444">
+    <row r="448" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H448">
         <v>1.94</v>
       </c>
-      <c r="I444" s="53">
-        <f t="shared" ref="I444:I507" si="13">IF(H444&lt;$C$251/3,   ($C$252*$C$249/$C$253)*(1+(3*($C$250-1)*H444/$C$251)),   IF(H444&lt;=$C$251,   $C$252*$C$249*$C$250/$C$253,   $C$252*$C$249*$C$250/$C$253*($C$251/H444)^(2/3)   ))</f>
+      <c r="I448" s="53">
+        <f t="shared" ref="I448:I511" si="13">IF(H448&lt;$C$255/3,   ($C$256*$C$253/$C$257)*(1+(3*($C$254-1)*H448/$C$255)),   IF(H448&lt;=$C$255,   $C$256*$C$253*$C$254/$C$257,   $C$256*$C$253*$C$254/$C$257*($C$255/H448)^(2/3)   ))</f>
         <v>7.8400028339273883E-2</v>
       </c>
     </row>
-    <row r="445" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H445">
+    <row r="449" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H449">
         <v>1.95</v>
       </c>
-      <c r="I445" s="53">
+      <c r="I449" s="53">
         <f t="shared" si="13"/>
         <v>7.8131764441513082E-2</v>
       </c>
     </row>
-    <row r="446" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H446">
+    <row r="450" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H450">
         <v>1.96</v>
       </c>
-      <c r="I446" s="53">
+      <c r="I450" s="53">
         <f t="shared" si="13"/>
         <v>7.7865783645183179E-2</v>
       </c>
     </row>
-    <row r="447" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H447">
+    <row r="451" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H451">
         <v>1.97</v>
       </c>
-      <c r="I447" s="53">
+      <c r="I451" s="53">
         <f t="shared" si="13"/>
         <v>7.7602055019107566E-2</v>
       </c>
     </row>
-    <row r="448" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H448">
+    <row r="452" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H452">
         <v>1.98</v>
       </c>
-      <c r="I448" s="53">
+      <c r="I452" s="53">
         <f t="shared" si="13"/>
         <v>7.7340548205393655E-2</v>
       </c>
     </row>
-    <row r="449" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H449">
+    <row r="453" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H453">
         <v>1.99</v>
       </c>
-      <c r="I449" s="53">
+      <c r="I453" s="53">
         <f t="shared" si="13"/>
         <v>7.708123340597775E-2</v>
       </c>
     </row>
-    <row r="450" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H450">
+    <row r="454" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H454">
         <v>2</v>
       </c>
-      <c r="I450" s="53">
+      <c r="I454" s="53">
         <f t="shared" si="13"/>
         <v>7.6824081369551406E-2</v>
       </c>
     </row>
-    <row r="451" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H451">
+    <row r="455" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H455">
         <v>2.0099999999999998</v>
       </c>
-      <c r="I451" s="53">
+      <c r="I455" s="53">
         <f t="shared" si="13"/>
         <v>7.6569063378856717E-2</v>
       </c>
     </row>
-    <row r="452" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H452">
+    <row r="456" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H456">
         <v>2.02</v>
       </c>
-      <c r="I452" s="53">
+      <c r="I456" s="53">
         <f t="shared" si="13"/>
         <v>7.6316151238338195E-2</v>
       </c>
     </row>
-    <row r="453" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H453">
+    <row r="457" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H457">
         <v>2.0299999999999998</v>
       </c>
-      <c r="I453" s="53">
+      <c r="I457" s="53">
         <f t="shared" si="13"/>
         <v>7.6065317262139873E-2</v>
       </c>
     </row>
-    <row r="454" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H454">
+    <row r="458" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H458">
         <v>2.04</v>
       </c>
-      <c r="I454" s="53">
+      <c r="I458" s="53">
         <f t="shared" si="13"/>
         <v>7.5816534262435717E-2</v>
       </c>
     </row>
-    <row r="455" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H455">
+    <row r="459" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H459">
         <v>2.0499999999999998</v>
       </c>
-      <c r="I455" s="53">
+      <c r="I459" s="53">
         <f t="shared" si="13"/>
         <v>7.5569775538083292E-2</v>
       </c>
     </row>
-    <row r="456" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H456">
+    <row r="460" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H460">
         <v>2.06</v>
       </c>
-      <c r="I456" s="53">
+      <c r="I460" s="53">
         <f t="shared" si="13"/>
         <v>7.532501486358946E-2</v>
       </c>
     </row>
-    <row r="457" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H457">
+    <row r="461" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H461">
         <v>2.0699999999999998</v>
       </c>
-      <c r="I457" s="53">
+      <c r="I461" s="53">
         <f t="shared" si="13"/>
         <v>7.5082226478378589E-2</v>
       </c>
     </row>
-    <row r="458" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H458">
+    <row r="462" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H462">
         <v>2.08</v>
       </c>
-      <c r="I458" s="53">
+      <c r="I462" s="53">
         <f t="shared" si="13"/>
         <v>7.4841385076353351E-2</v>
       </c>
     </row>
-    <row r="459" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H459">
+    <row r="463" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H463">
         <v>2.09</v>
       </c>
-      <c r="I459" s="53">
+      <c r="I463" s="53">
         <f t="shared" si="13"/>
         <v>7.4602465795738634E-2</v>
       </c>
     </row>
-    <row r="460" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H460">
+    <row r="464" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H464">
         <v>2.1</v>
       </c>
-      <c r="I460" s="53">
+      <c r="I464" s="53">
         <f t="shared" si="13"/>
         <v>7.436544420919991E-2</v>
       </c>
     </row>
-    <row r="461" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H461">
+    <row r="465" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H465">
         <v>2.11</v>
       </c>
-      <c r="I461" s="53">
+      <c r="I465" s="53">
         <f t="shared" si="13"/>
         <v>7.4130296314227115E-2</v>
       </c>
     </row>
-    <row r="462" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H462">
+    <row r="466" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H466">
         <v>2.12</v>
       </c>
-      <c r="I462" s="53">
+      <c r="I466" s="53">
         <f t="shared" si="13"/>
         <v>7.3896998523775778E-2</v>
       </c>
     </row>
-    <row r="463" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H463">
+    <row r="467" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H467">
         <v>2.13</v>
       </c>
-      <c r="I463" s="53">
+      <c r="I467" s="53">
         <f t="shared" si="13"/>
         <v>7.3665527657157295E-2</v>
       </c>
     </row>
-    <row r="464" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H464">
+    <row r="468" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H468">
         <v>2.14</v>
       </c>
-      <c r="I464" s="53">
+      <c r="I468" s="53">
         <f t="shared" si="13"/>
         <v>7.3435860931170702E-2</v>
       </c>
     </row>
-    <row r="465" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H465">
+    <row r="469" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H469">
         <v>2.15</v>
       </c>
-      <c r="I465" s="53">
+      <c r="I469" s="53">
         <f t="shared" si="13"/>
         <v>7.3207975951468302E-2</v>
       </c>
     </row>
-    <row r="466" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H466">
+    <row r="470" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H470">
         <v>2.16</v>
       </c>
-      <c r="I466" s="53">
+      <c r="I470" s="53">
         <f t="shared" si="13"/>
         <v>7.2981850704147921E-2</v>
       </c>
     </row>
-    <row r="467" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H467">
+    <row r="471" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H471">
         <v>2.17</v>
       </c>
-      <c r="I467" s="53">
+      <c r="I471" s="53">
         <f t="shared" si="13"/>
         <v>7.2757463547565099E-2</v>
       </c>
     </row>
-    <row r="468" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H468">
+    <row r="472" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H472">
         <v>2.1800000000000002</v>
       </c>
-      <c r="I468" s="53">
+      <c r="I472" s="53">
         <f t="shared" si="13"/>
         <v>7.2534793204358031E-2</v>
       </c>
     </row>
-    <row r="469" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H469">
+    <row r="473" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H473">
         <v>2.19</v>
       </c>
-      <c r="I469" s="53">
+      <c r="I473" s="53">
         <f t="shared" si="13"/>
         <v>7.231381875367919E-2</v>
       </c>
     </row>
-    <row r="470" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H470">
+    <row r="474" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H474">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I470" s="53">
+      <c r="I474" s="53">
         <f t="shared" si="13"/>
         <v>7.2094519623627146E-2</v>
       </c>
     </row>
-    <row r="471" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H471">
+    <row r="475" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H475">
         <v>2.21</v>
       </c>
-      <c r="I471" s="53">
+      <c r="I475" s="53">
         <f t="shared" si="13"/>
         <v>7.1876875583872596E-2</v>
       </c>
     </row>
-    <row r="472" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H472">
+    <row r="476" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H476">
         <v>2.2200000000000002</v>
       </c>
-      <c r="I472" s="53">
+      <c r="I476" s="53">
         <f t="shared" si="13"/>
         <v>7.1660866738472703E-2</v>
       </c>
     </row>
-    <row r="473" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H473">
+    <row r="477" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H477">
         <v>2.23</v>
       </c>
-      <c r="I473" s="53">
+      <c r="I477" s="53">
         <f t="shared" si="13"/>
         <v>7.1446473518868236E-2</v>
       </c>
     </row>
-    <row r="474" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H474">
+    <row r="478" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H478">
         <v>2.2400000000000002</v>
       </c>
-      <c r="I474" s="53">
+      <c r="I478" s="53">
         <f t="shared" si="13"/>
         <v>7.123367667705803E-2</v>
       </c>
     </row>
-    <row r="475" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H475">
+    <row r="479" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H479">
         <v>2.25</v>
       </c>
-      <c r="I475" s="53">
+      <c r="I479" s="53">
         <f t="shared" si="13"/>
         <v>7.1022457278945364E-2</v>
       </c>
     </row>
-    <row r="476" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H476">
+    <row r="480" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H480">
         <v>2.2599999999999998</v>
       </c>
-      <c r="I476" s="53">
+      <c r="I480" s="53">
         <f t="shared" si="13"/>
         <v>7.0812796697851343E-2</v>
       </c>
     </row>
-    <row r="477" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H477">
+    <row r="481" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H481">
         <v>2.27</v>
       </c>
-      <c r="I477" s="53">
+      <c r="I481" s="53">
         <f t="shared" si="13"/>
         <v>7.0604676608190434E-2</v>
       </c>
     </row>
-    <row r="478" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H478">
+    <row r="482" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H482">
         <v>2.2799999999999998</v>
       </c>
-      <c r="I478" s="53">
+      <c r="I482" s="53">
         <f t="shared" si="13"/>
         <v>7.0398078979303086E-2</v>
       </c>
     </row>
-    <row r="479" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H479">
+    <row r="483" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H483">
         <v>2.29</v>
       </c>
-      <c r="I479" s="53">
+      <c r="I483" s="53">
         <f t="shared" si="13"/>
         <v>7.0192986069441285E-2</v>
       </c>
     </row>
-    <row r="480" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H480">
+    <row r="484" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H484">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I480" s="53">
+      <c r="I484" s="53">
         <f t="shared" si="13"/>
         <v>6.9989380419902256E-2</v>
       </c>
     </row>
-    <row r="481" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H481">
+    <row r="485" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H485">
         <v>2.31</v>
       </c>
-      <c r="I481" s="53">
+      <c r="I485" s="53">
         <f t="shared" si="13"/>
         <v>6.9787244849306276E-2</v>
       </c>
     </row>
-    <row r="482" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H482">
+    <row r="486" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H486">
         <v>2.3199999999999998</v>
       </c>
-      <c r="I482" s="53">
+      <c r="I486" s="53">
         <f t="shared" si="13"/>
         <v>6.9586562448014339E-2</v>
       </c>
     </row>
-    <row r="483" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H483">
+    <row r="487" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H487">
         <v>2.33</v>
       </c>
-      <c r="I483" s="53">
+      <c r="I487" s="53">
         <f t="shared" si="13"/>
         <v>6.9387316572681504E-2</v>
       </c>
     </row>
-    <row r="484" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H484">
+    <row r="488" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H488">
         <v>2.34</v>
       </c>
-      <c r="I484" s="53">
+      <c r="I488" s="53">
         <f t="shared" si="13"/>
         <v>6.91894908409426E-2</v>
       </c>
     </row>
-    <row r="485" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H485">
+    <row r="489" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H489">
         <v>2.35</v>
       </c>
-      <c r="I485" s="53">
+      <c r="I489" s="53">
         <f t="shared" si="13"/>
         <v>6.8993069126225728E-2</v>
       </c>
     </row>
-    <row r="486" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H486">
+    <row r="490" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H490">
         <v>2.36</v>
       </c>
-      <c r="I486" s="53">
+      <c r="I490" s="53">
         <f t="shared" si="13"/>
         <v>6.8798035552690887E-2</v>
       </c>
     </row>
-    <row r="487" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H487">
+    <row r="491" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H491">
         <v>2.37</v>
       </c>
-      <c r="I487" s="53">
+      <c r="I491" s="53">
         <f t="shared" si="13"/>
         <v>6.8604374490289111E-2</v>
       </c>
     </row>
-    <row r="488" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H488">
+    <row r="492" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H492">
         <v>2.38</v>
       </c>
-      <c r="I488" s="53">
+      <c r="I492" s="53">
         <f t="shared" si="13"/>
         <v>6.8412070549939946E-2</v>
       </c>
     </row>
-    <row r="489" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H489">
+    <row r="493" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H493">
         <v>2.39</v>
       </c>
-      <c r="I489" s="53">
+      <c r="I493" s="53">
         <f t="shared" si="13"/>
         <v>6.8221108578822798E-2</v>
       </c>
     </row>
-    <row r="490" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H490">
+    <row r="494" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H494">
         <v>2.4</v>
       </c>
-      <c r="I490" s="53">
+      <c r="I494" s="53">
         <f t="shared" si="13"/>
         <v>6.8031473655779995E-2</v>
       </c>
     </row>
-    <row r="491" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H491">
+    <row r="495" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H495">
         <v>2.41</v>
       </c>
-      <c r="I491" s="53">
+      <c r="I495" s="53">
         <f t="shared" si="13"/>
         <v>6.7843151086827647E-2</v>
       </c>
     </row>
-    <row r="492" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H492">
+    <row r="496" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H496">
         <v>2.42</v>
       </c>
-      <c r="I492" s="53">
+      <c r="I496" s="53">
         <f t="shared" si="13"/>
         <v>6.7656126400771982E-2</v>
       </c>
     </row>
-    <row r="493" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H493">
+    <row r="497" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H497">
         <v>2.4300000000000002</v>
       </c>
-      <c r="I493" s="53">
+      <c r="I497" s="53">
         <f t="shared" si="13"/>
         <v>6.7470385344927691E-2</v>
       </c>
     </row>
-    <row r="494" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H494">
+    <row r="498" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H498">
         <v>2.44</v>
       </c>
-      <c r="I494" s="53">
+      <c r="I498" s="53">
         <f t="shared" si="13"/>
         <v>6.7285913880936132E-2</v>
       </c>
     </row>
-    <row r="495" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H495">
+    <row r="499" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H499">
         <v>2.4500000000000002</v>
       </c>
-      <c r="I495" s="53">
+      <c r="I499" s="53">
         <f t="shared" si="13"/>
         <v>6.7102698180679973E-2</v>
       </c>
     </row>
-    <row r="496" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H496">
+    <row r="500" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H500">
         <v>2.46</v>
       </c>
-      <c r="I496" s="53">
+      <c r="I500" s="53">
         <f t="shared" si="13"/>
         <v>6.6920724622292219E-2</v>
       </c>
     </row>
-    <row r="497" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H497">
+    <row r="501" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H501">
         <v>2.4700000000000002</v>
       </c>
-      <c r="I497" s="53">
+      <c r="I501" s="53">
         <f t="shared" si="13"/>
         <v>6.6739979786256801E-2</v>
       </c>
     </row>
-    <row r="498" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H498">
+    <row r="502" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H502">
         <v>2.48</v>
       </c>
-      <c r="I498" s="53">
+      <c r="I502" s="53">
         <f t="shared" si="13"/>
         <v>6.6560450451598294E-2</v>
       </c>
     </row>
-    <row r="499" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H499">
+    <row r="503" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H503">
         <v>2.4900000000000002</v>
       </c>
-      <c r="I499" s="53">
+      <c r="I503" s="53">
         <f t="shared" si="13"/>
         <v>6.6382123592158546E-2</v>
       </c>
     </row>
-    <row r="500" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H500">
+    <row r="504" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H504">
         <v>2.5</v>
       </c>
-      <c r="I500" s="53">
+      <c r="I504" s="53">
         <f t="shared" si="13"/>
         <v>6.6204986372957478E-2</v>
       </c>
     </row>
-    <row r="501" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H501">
+    <row r="505" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H505">
         <v>2.5099999999999998</v>
       </c>
-      <c r="I501" s="53">
+      <c r="I505" s="53">
         <f t="shared" si="13"/>
         <v>6.6029026146636471E-2</v>
       </c>
     </row>
-    <row r="502" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H502">
+    <row r="506" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H506">
         <v>2.52</v>
       </c>
-      <c r="I502" s="53">
+      <c r="I506" s="53">
         <f t="shared" si="13"/>
         <v>6.5854230449981385E-2</v>
       </c>
     </row>
-    <row r="503" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H503">
+    <row r="507" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H507">
         <v>2.5299999999999998</v>
       </c>
-      <c r="I503" s="53">
+      <c r="I507" s="53">
         <f t="shared" si="13"/>
         <v>6.5680587000523913E-2</v>
       </c>
     </row>
-    <row r="504" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H504">
+    <row r="508" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H508">
         <v>2.54</v>
       </c>
-      <c r="I504" s="53">
+      <c r="I508" s="53">
         <f t="shared" si="13"/>
         <v>6.5508083693218408E-2</v>
       </c>
     </row>
-    <row r="505" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H505">
+    <row r="509" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H509">
         <v>2.5499999999999998</v>
       </c>
-      <c r="I505" s="53">
+      <c r="I509" s="53">
         <f t="shared" si="13"/>
         <v>6.5336708597192955E-2</v>
       </c>
     </row>
-    <row r="506" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H506">
+    <row r="510" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H510">
         <v>2.56</v>
       </c>
-      <c r="I506" s="53">
+      <c r="I510" s="53">
         <f t="shared" si="13"/>
         <v>6.5166449952572161E-2</v>
       </c>
     </row>
-    <row r="507" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H507">
+    <row r="511" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H511">
         <v>2.57</v>
       </c>
-      <c r="I507" s="53">
+      <c r="I511" s="53">
         <f t="shared" si="13"/>
         <v>6.4997296167370169E-2</v>
       </c>
     </row>
-    <row r="508" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H508">
+    <row r="512" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H512">
         <v>2.58</v>
       </c>
-      <c r="I508" s="53">
-        <f t="shared" ref="I508:I550" si="14">IF(H508&lt;$C$251/3,   ($C$252*$C$249/$C$253)*(1+(3*($C$250-1)*H508/$C$251)),   IF(H508&lt;=$C$251,   $C$252*$C$249*$C$250/$C$253,   $C$252*$C$249*$C$250/$C$253*($C$251/H508)^(2/3)   ))</f>
+      <c r="I512" s="53">
+        <f t="shared" ref="I512:I554" si="14">IF(H512&lt;$C$255/3,   ($C$256*$C$253/$C$257)*(1+(3*($C$254-1)*H512/$C$255)),   IF(H512&lt;=$C$255,   $C$256*$C$253*$C$254/$C$257,   $C$256*$C$253*$C$254/$C$257*($C$255/H512)^(2/3)   ))</f>
         <v>6.4829235814451935E-2</v>
       </c>
     </row>
-    <row r="509" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H509">
+    <row r="513" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H513">
         <v>2.59</v>
       </c>
-      <c r="I509" s="53">
+      <c r="I513" s="53">
         <f t="shared" si="14"/>
         <v>6.4662257628560982E-2</v>
       </c>
     </row>
-    <row r="510" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H510">
+    <row r="514" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H514">
         <v>2.6</v>
       </c>
-      <c r="I510" s="53">
+      <c r="I514" s="53">
         <f t="shared" si="14"/>
         <v>6.449635050341207E-2</v>
       </c>
     </row>
-    <row r="511" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H511">
+    <row r="515" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H515">
         <v>2.61</v>
       </c>
-      <c r="I511" s="53">
+      <c r="I515" s="53">
         <f t="shared" si="14"/>
         <v>6.4331503488846975E-2</v>
       </c>
     </row>
-    <row r="512" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H512">
+    <row r="516" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H516">
         <v>2.62</v>
       </c>
-      <c r="I512" s="53">
+      <c r="I516" s="53">
         <f t="shared" si="14"/>
         <v>6.4167705788051782E-2</v>
       </c>
     </row>
-    <row r="513" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H513">
+    <row r="517" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H517">
         <v>2.63</v>
       </c>
-      <c r="I513" s="53">
+      <c r="I517" s="53">
         <f t="shared" si="14"/>
         <v>6.4004946754834202E-2</v>
       </c>
     </row>
-    <row r="514" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H514">
+    <row r="518" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H518">
         <v>2.64</v>
       </c>
-      <c r="I514" s="53">
+      <c r="I518" s="53">
         <f t="shared" si="14"/>
         <v>6.3843215890959426E-2</v>
       </c>
     </row>
-    <row r="515" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H515">
+    <row r="519" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H519">
         <v>2.65</v>
       </c>
-      <c r="I515" s="53">
+      <c r="I519" s="53">
         <f t="shared" si="14"/>
         <v>6.3682502843542974E-2</v>
       </c>
     </row>
-    <row r="516" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H516">
+    <row r="520" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H520">
         <v>2.66</v>
       </c>
-      <c r="I516" s="53">
+      <c r="I520" s="53">
         <f t="shared" si="14"/>
         <v>6.3522797402498971E-2</v>
       </c>
     </row>
-    <row r="517" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H517">
+    <row r="521" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H521">
         <v>2.67</v>
       </c>
-      <c r="I517" s="53">
+      <c r="I521" s="53">
         <f t="shared" si="14"/>
         <v>6.3364089498042855E-2</v>
       </c>
     </row>
-    <row r="518" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H518">
+    <row r="522" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H522">
         <v>2.68</v>
       </c>
-      <c r="I518" s="53">
+      <c r="I522" s="53">
         <f t="shared" si="14"/>
         <v>6.3206369198246654E-2</v>
       </c>
     </row>
-    <row r="519" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H519">
+    <row r="523" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H523">
         <v>2.69</v>
       </c>
-      <c r="I519" s="53">
+      <c r="I523" s="53">
         <f t="shared" si="14"/>
         <v>6.30496267066461E-2</v>
       </c>
     </row>
-    <row r="520" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H520">
+    <row r="524" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H524">
         <v>2.7</v>
       </c>
-      <c r="I520" s="53">
+      <c r="I524" s="53">
         <f t="shared" si="14"/>
         <v>6.2893852359897653E-2</v>
       </c>
     </row>
-    <row r="521" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H521">
+    <row r="525" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H525">
         <v>2.71</v>
       </c>
-      <c r="I521" s="53">
+      <c r="I525" s="53">
         <f t="shared" si="14"/>
         <v>6.2739036625484884E-2</v>
       </c>
     </row>
-    <row r="522" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H522">
+    <row r="526" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H526">
         <v>2.72</v>
       </c>
-      <c r="I522" s="53">
+      <c r="I526" s="53">
         <f t="shared" si="14"/>
         <v>6.2585170099472384E-2</v>
       </c>
     </row>
-    <row r="523" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H523">
+    <row r="527" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H527">
         <v>2.73</v>
       </c>
-      <c r="I523" s="53">
+      <c r="I527" s="53">
         <f t="shared" si="14"/>
         <v>6.2432243504306546E-2</v>
       </c>
     </row>
-    <row r="524" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H524">
+    <row r="528" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H528">
         <v>2.74</v>
       </c>
-      <c r="I524" s="53">
+      <c r="I528" s="53">
         <f t="shared" si="14"/>
         <v>6.2280247686661676E-2</v>
       </c>
     </row>
-    <row r="525" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H525">
+    <row r="529" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H529">
         <v>2.75</v>
       </c>
-      <c r="I525" s="53">
+      <c r="I529" s="53">
         <f t="shared" si="14"/>
         <v>6.2129173615330699E-2</v>
       </c>
     </row>
-    <row r="526" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H526">
+    <row r="530" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H530">
         <v>2.76</v>
       </c>
-      <c r="I526" s="53">
+      <c r="I530" s="53">
         <f t="shared" si="14"/>
         <v>6.1979012379158996E-2</v>
       </c>
     </row>
-    <row r="527" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H527">
+    <row r="531" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H531">
         <v>2.77</v>
       </c>
-      <c r="I527" s="53">
+      <c r="I531" s="53">
         <f t="shared" si="14"/>
         <v>6.18297551850207E-2</v>
       </c>
     </row>
-    <row r="528" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H528">
+    <row r="532" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H532">
         <v>2.78</v>
       </c>
-      <c r="I528" s="53">
+      <c r="I532" s="53">
         <f t="shared" si="14"/>
         <v>6.1681393355836216E-2</v>
       </c>
     </row>
-    <row r="529" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H529">
+    <row r="533" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H533">
         <v>2.79</v>
       </c>
-      <c r="I529" s="53">
+      <c r="I533" s="53">
         <f t="shared" si="14"/>
         <v>6.153391832862997E-2</v>
       </c>
     </row>
-    <row r="530" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H530">
+    <row r="534" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H534">
         <v>2.8</v>
       </c>
-      <c r="I530" s="53">
+      <c r="I534" s="53">
         <f t="shared" si="14"/>
         <v>6.1387321652627579E-2</v>
       </c>
     </row>
-    <row r="531" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H531">
+    <row r="535" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H535">
         <v>2.81</v>
       </c>
-      <c r="I531" s="53">
+      <c r="I535" s="53">
         <f t="shared" si="14"/>
         <v>6.1241594987391366E-2</v>
       </c>
     </row>
-    <row r="532" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H532">
+    <row r="536" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H536">
         <v>2.82</v>
       </c>
-      <c r="I532" s="53">
+      <c r="I536" s="53">
         <f t="shared" si="14"/>
         <v>6.1096730100993361E-2</v>
       </c>
     </row>
-    <row r="533" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H533">
+    <row r="537" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H537">
         <v>2.83</v>
       </c>
-      <c r="I533" s="53">
+      <c r="I537" s="53">
         <f t="shared" si="14"/>
         <v>6.0952718868224912E-2</v>
       </c>
     </row>
-    <row r="534" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H534">
+    <row r="538" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H538">
         <v>2.84</v>
       </c>
-      <c r="I534" s="53">
+      <c r="I538" s="53">
         <f t="shared" si="14"/>
         <v>6.0809553268842097E-2</v>
       </c>
     </row>
-    <row r="535" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H535">
+    <row r="539" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H539">
         <v>2.85</v>
       </c>
-      <c r="I535" s="53">
+      <c r="I539" s="53">
         <f t="shared" si="14"/>
         <v>6.0667225385845965E-2</v>
       </c>
     </row>
-    <row r="536" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H536">
+    <row r="540" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H540">
         <v>2.86</v>
       </c>
-      <c r="I536" s="53">
+      <c r="I540" s="53">
         <f t="shared" si="14"/>
         <v>6.0525727403796865E-2</v>
       </c>
     </row>
-    <row r="537" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H537">
+    <row r="541" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H541">
         <v>2.87</v>
       </c>
-      <c r="I537" s="53">
+      <c r="I541" s="53">
         <f t="shared" si="14"/>
         <v>6.0385051607162142E-2</v>
       </c>
     </row>
-    <row r="538" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H538">
+    <row r="542" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H542">
         <v>2.88</v>
       </c>
-      <c r="I538" s="53">
+      <c r="I542" s="53">
         <f t="shared" si="14"/>
         <v>6.0245190378696391E-2</v>
       </c>
     </row>
-    <row r="539" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H539">
+    <row r="543" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H543">
         <v>2.89</v>
       </c>
-      <c r="I539" s="53">
+      <c r="I543" s="53">
         <f t="shared" si="14"/>
         <v>6.0106136197853308E-2</v>
       </c>
     </row>
-    <row r="540" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H540">
+    <row r="544" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H544">
         <v>2.9</v>
       </c>
-      <c r="I540" s="53">
+      <c r="I544" s="53">
         <f t="shared" si="14"/>
         <v>5.9967881639228844E-2</v>
       </c>
     </row>
-    <row r="541" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H541">
+    <row r="545" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H545">
         <v>2.91</v>
       </c>
-      <c r="I541" s="53">
+      <c r="I545" s="53">
         <f t="shared" si="14"/>
         <v>5.9830419371034442E-2</v>
       </c>
     </row>
-    <row r="542" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H542">
+    <row r="546" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H546">
         <v>2.92</v>
       </c>
-      <c r="I542" s="53">
+      <c r="I546" s="53">
         <f t="shared" si="14"/>
         <v>5.9693742153600148E-2</v>
       </c>
     </row>
-    <row r="543" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H543">
+    <row r="547" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H547">
         <v>2.93</v>
       </c>
-      <c r="I543" s="53">
+      <c r="I547" s="53">
         <f t="shared" si="14"/>
         <v>5.9557842837906549E-2</v>
       </c>
     </row>
-    <row r="544" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H544">
+    <row r="548" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H548">
         <v>2.94</v>
       </c>
-      <c r="I544" s="53">
+      <c r="I548" s="53">
         <f t="shared" si="14"/>
         <v>5.9422714364145E-2</v>
       </c>
     </row>
-    <row r="545" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H545">
+    <row r="549" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H549">
         <v>2.95</v>
       </c>
-      <c r="I545" s="53">
+      <c r="I549" s="53">
         <f t="shared" si="14"/>
         <v>5.9288349760305649E-2</v>
       </c>
     </row>
-    <row r="546" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H546">
+    <row r="550" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H550">
         <v>2.96</v>
       </c>
-      <c r="I546" s="53">
+      <c r="I550" s="53">
         <f t="shared" si="14"/>
         <v>5.9154742140792402E-2</v>
       </c>
     </row>
-    <row r="547" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H547">
+    <row r="551" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H551">
         <v>2.97</v>
       </c>
-      <c r="I547" s="53">
+      <c r="I551" s="53">
         <f t="shared" si="14"/>
         <v>5.9021884705064413E-2</v>
       </c>
     </row>
-    <row r="548" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H548">
+    <row r="552" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H552">
         <v>2.98</v>
       </c>
-      <c r="I548" s="53">
+      <c r="I552" s="53">
         <f t="shared" si="14"/>
         <v>5.8889770736303346E-2</v>
       </c>
     </row>
-    <row r="549" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H549">
+    <row r="553" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H553">
         <v>2.99</v>
       </c>
-      <c r="I549" s="53">
+      <c r="I553" s="53">
         <f t="shared" si="14"/>
         <v>5.8758393600105874E-2</v>
       </c>
     </row>
-    <row r="550" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H550">
+    <row r="554" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H554">
         <v>3</v>
       </c>
-      <c r="I550" s="53">
+      <c r="I554" s="53">
         <f t="shared" si="14"/>
         <v>5.8627746743201051E-2</v>
       </c>
@@ -13849,11 +14005,11 @@
     <mergeCell ref="AL8:AM8"/>
     <mergeCell ref="AL9:AM9"/>
     <mergeCell ref="F127:G127"/>
-    <mergeCell ref="K233:L233"/>
+    <mergeCell ref="K237:L237"/>
     <mergeCell ref="B173:L173"/>
     <mergeCell ref="E174:G174"/>
     <mergeCell ref="K174:L174"/>
-    <mergeCell ref="H219:J219"/>
+    <mergeCell ref="H223:J223"/>
     <mergeCell ref="C10:E10"/>
   </mergeCells>
   <dataValidations count="4">

--- a/002/002_SISMO_VIENTO_SALVADOR_2.1.xlsx
+++ b/002/002_SISMO_VIENTO_SALVADOR_2.1.xlsx
@@ -2330,7 +2330,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CARGAS Y SISMO F1'!$H$255:$H$554</c:f>
+              <c:f>'CARGAS Y SISMO F1'!$H$256:$H$555</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="300"/>
@@ -3239,7 +3239,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CARGAS Y SISMO F1'!$I$255:$I$554</c:f>
+              <c:f>'CARGAS Y SISMO F1'!$I$256:$I$555</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="300"/>
@@ -4459,13 +4459,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>143435</xdr:colOff>
-      <xdr:row>255</xdr:row>
+      <xdr:row>256</xdr:row>
       <xdr:rowOff>123265</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>179294</xdr:colOff>
-      <xdr:row>273</xdr:row>
+      <xdr:row>274</xdr:row>
       <xdr:rowOff>134471</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4935,13 +4935,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>459440</xdr:colOff>
-      <xdr:row>259</xdr:row>
+      <xdr:row>260</xdr:row>
       <xdr:rowOff>179295</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>377985</xdr:colOff>
-      <xdr:row>283</xdr:row>
+      <xdr:row>284</xdr:row>
       <xdr:rowOff>73236</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5889,7 +5889,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B2:AM554"/>
+  <dimension ref="B2:AM555"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.109375" customWidth="1"/>
@@ -6480,7 +6480,7 @@
         <v>68</v>
       </c>
       <c r="F137" s="36">
-        <v>0.68858</v>
+        <v>0.68382</v>
       </c>
       <c r="G137" t="s">
         <v>66</v>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="F139" s="52">
         <f>P33*Q85*P55/P99*(P57/MAX(P57,MIN(F137,6*P57)))^(2/3)</f>
-        <v>0.156391965113218</v>
+        <v>0.157116877877753</v>
       </c>
     </row>
     <row r="140" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="F143" s="54">
         <f>MAX(F141,F139)</f>
-        <v>0.156391965113218</v>
+        <v>0.157116877877753</v>
       </c>
     </row>
     <row r="148" spans="2:25" s="39" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -6635,14 +6635,14 @@
         <v>87</v>
       </c>
       <c r="E165" s="82">
-        <v>13470.77</v>
+        <v>13367.14</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>85</v>
       </c>
       <c r="G165" s="55">
         <f>E165/1000</f>
-        <v>13.47077</v>
+        <v>13.36714</v>
       </c>
       <c r="H165" s="1" t="s">
         <v>86</v>
@@ -6653,14 +6653,14 @@
         <v>88</v>
       </c>
       <c r="E166" s="82">
-        <v>13470.77</v>
+        <v>13367.14</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>85</v>
       </c>
       <c r="G166" s="55">
         <f>E166/1000</f>
-        <v>13.47077</v>
+        <v>13.36714</v>
       </c>
       <c r="H166" s="1" t="s">
         <v>86</v>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="G170" s="51">
         <f>G168*G165</f>
-        <v>2.30927485714286</v>
+        <v>2.29150971428571</v>
       </c>
       <c r="H170" s="1" t="s">
         <v>86</v>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="G171" s="51">
         <f>G168*G166</f>
-        <v>2.30927485714286</v>
+        <v>2.29150971428571</v>
       </c>
       <c r="H171" s="1" t="s">
         <v>86</v>
@@ -6826,13 +6826,13 @@
         <v>1</v>
       </c>
       <c r="C177" s="28">
-        <v>1.452</v>
+        <v>1.462</v>
       </c>
       <c r="D177" s="64">
-        <v>0.68858</v>
+        <v>0.68382</v>
       </c>
       <c r="E177" s="28">
-        <v>77.53</v>
+        <v>77.85</v>
       </c>
       <c r="F177" s="28">
         <v>0</v>
@@ -6845,18 +6845,18 @@
       </c>
       <c r="I177" s="29">
         <f>ROUND(D177,2)</f>
-        <v>0.69</v>
+        <v>0.68</v>
       </c>
       <c r="J177" s="31">
-        <f>VLOOKUP(I177,$H$255:$I$554,2,0)</f>
-        <v>0.156177324696395</v>
+        <f>VLOOKUP(I177,$H$256:$I$555,2,0)</f>
+        <v>0.157704746439153</v>
       </c>
       <c r="K177" s="32">
-        <f>J177*$K$225*E177/100</f>
-        <v>1631.09848430141</v>
+        <f>J177*$K$226*E177/100</f>
+        <v>1641.12581883052</v>
       </c>
       <c r="L177" s="34">
-        <f>J177*$K$226*G177/100</f>
+        <f>J177*$K$227*G177/100</f>
         <v>0</v>
       </c>
       <c r="N177" s="10" t="s">
@@ -6897,15 +6897,15 @@
         <v>0.37</v>
       </c>
       <c r="J178" s="31">
-        <f>VLOOKUP(I178,$H$255:$I$554,2,0)</f>
+        <f>VLOOKUP(I178,$H$256:$I$555,2,0)</f>
         <v>0.17142857142857146</v>
       </c>
       <c r="K178" s="32">
-        <f>J178*$K$225*E178/100</f>
+        <f>J178*$K$226*E178/100</f>
         <v>0</v>
       </c>
       <c r="L178" s="34">
-        <f>J178*$K$226*G178/100</f>
+        <f>J178*$K$227*G178/100</f>
         <v>0</v>
       </c>
       <c r="N178" s="10" t="s">
@@ -6946,15 +6946,15 @@
         <v>0.37</v>
       </c>
       <c r="J179" s="31">
-        <f t="shared" ref="J179" si="2">VLOOKUP(I179,$H$255:$I$554,2,0)</f>
+        <f t="shared" ref="J179" si="2">VLOOKUP(I179,$H$256:$I$555,2,0)</f>
         <v>0.17142857142857146</v>
       </c>
       <c r="K179" s="32">
-        <f t="shared" ref="K179" si="3">J179*$K$225*E179/100</f>
-        <v>0.230927485714286</v>
+        <f t="shared" ref="K179" si="3">J179*$K$226*E179/100</f>
+        <v>0.229150971428571</v>
       </c>
       <c r="L179" s="34">
-        <f t="shared" ref="L179" si="4">J179*$K$226*G179/100</f>
+        <f t="shared" ref="L179" si="4">J179*$K$227*G179/100</f>
         <v>0</v>
       </c>
       <c r="N179" s="10"/>
@@ -6965,13 +6965,13 @@
         <v>4</v>
       </c>
       <c r="C180" s="28">
-        <v>2.801</v>
+        <v>2.8</v>
       </c>
       <c r="D180" s="64">
-        <v>0.35706</v>
+        <v>0.3572</v>
       </c>
       <c r="E180" s="28">
-        <v>7.97</v>
+        <v>8.16</v>
       </c>
       <c r="F180" s="28">
         <v>0</v>
@@ -6983,19 +6983,19 @@
         <v>113</v>
       </c>
       <c r="I180" s="29">
-        <f t="shared" ref="I180:I222" si="5">ROUND(D180,2)</f>
+        <f t="shared" ref="I180:I223" si="5">ROUND(D180,2)</f>
         <v>0.36</v>
       </c>
       <c r="J180" s="31">
-        <f t="shared" ref="J180:J222" si="6">VLOOKUP(I180,$H$255:$I$554,2,0)</f>
+        <f t="shared" ref="J180:J223" si="6">VLOOKUP(I180,$H$256:$I$555,2,0)</f>
         <v>0.17142857142857146</v>
       </c>
       <c r="K180" s="32">
-        <f t="shared" ref="K180:K222" si="7">J180*$K$225*E180/100</f>
-        <v>184.049206114286</v>
+        <f t="shared" ref="K180:K223" si="7">J180*$K$226*E180/100</f>
+        <v>186.987192685714</v>
       </c>
       <c r="L180" s="34">
-        <f t="shared" ref="L180:L222" si="8">J180*$K$226*G180/100</f>
+        <f t="shared" ref="L180:L223" si="8">J180*$K$227*G180/100</f>
         <v>0</v>
       </c>
       <c r="N180" s="10"/>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="K182" s="32">
         <f t="shared" si="7"/>
-        <v>0.461854971428572</v>
+        <v>0.458301942857143</v>
       </c>
       <c r="L182" s="34">
         <f t="shared" si="8"/>
@@ -7088,10 +7088,10 @@
         <v>7</v>
       </c>
       <c r="C183" s="28">
-        <v>3.437</v>
+        <v>3.492</v>
       </c>
       <c r="D183" s="64">
-        <v>0.29098</v>
+        <v>0.28636</v>
       </c>
       <c r="E183" s="28">
         <v>0</v>
@@ -7100,7 +7100,7 @@
         <v>0</v>
       </c>
       <c r="G183" s="28">
-        <v>61.3</v>
+        <v>67.66</v>
       </c>
       <c r="H183" s="28" t="s">
         <v>113</v>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="L183" s="34">
         <f t="shared" si="8"/>
-        <v>1415.58548742857</v>
+        <v>1550.43547268571</v>
       </c>
       <c r="N183" s="10"/>
       <c r="O183" s="26"/>
@@ -7129,13 +7129,13 @@
         <v>8</v>
       </c>
       <c r="C184" s="28">
-        <v>4.169</v>
+        <v>4.174</v>
       </c>
       <c r="D184" s="64">
-        <v>0.23988</v>
+        <v>0.23958</v>
       </c>
       <c r="E184" s="28">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="F184" s="28">
         <v>0</v>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="K184" s="32">
         <f t="shared" si="7"/>
-        <v>16.3958514857143</v>
+        <v>16.040568</v>
       </c>
       <c r="L184" s="34">
         <f t="shared" si="8"/>
@@ -7170,10 +7170,10 @@
         <v>9</v>
       </c>
       <c r="C185" s="28">
-        <v>4.401</v>
+        <v>4.439</v>
       </c>
       <c r="D185" s="64">
-        <v>0.2272</v>
+        <v>0.22528</v>
       </c>
       <c r="E185" s="28">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="G185" s="28">
-        <v>6.52</v>
+        <v>2.15</v>
       </c>
       <c r="H185" s="28" t="s">
         <v>113</v>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="L185" s="34">
         <f t="shared" si="8"/>
-        <v>150.564720685714</v>
+        <v>49.2674588571429</v>
       </c>
       <c r="N185" s="10"/>
     </row>
@@ -7292,10 +7292,10 @@
         <v>12</v>
       </c>
       <c r="C188" s="28">
-        <v>4.806</v>
+        <v>4.95</v>
       </c>
       <c r="D188" s="64">
-        <v>0.20808</v>
+        <v>0.20203</v>
       </c>
       <c r="E188" s="28">
         <v>0</v>
@@ -7304,14 +7304,14 @@
         <v>0</v>
       </c>
       <c r="G188" s="28">
-        <v>18.27</v>
+        <v>16.49</v>
       </c>
       <c r="H188" s="28" t="s">
         <v>113</v>
       </c>
       <c r="I188" s="29">
         <f t="shared" si="5"/>
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="J188" s="31">
         <f t="shared" si="6"/>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="L188" s="34">
         <f t="shared" si="8"/>
-        <v>421.9045164</v>
+        <v>377.869951885714</v>
       </c>
       <c r="N188" s="10" t="s">
         <v>114</v>
@@ -7493,10 +7493,10 @@
         <v>15</v>
       </c>
       <c r="C191" s="28">
-        <v>6.105</v>
+        <v>6.405</v>
       </c>
       <c r="D191" s="64">
-        <v>0.16379</v>
+        <v>0.15613</v>
       </c>
       <c r="E191" s="28">
         <v>0</v>
@@ -7557,13 +7557,13 @@
         <v>16</v>
       </c>
       <c r="C192" s="28">
-        <v>6.339</v>
+        <v>7.086</v>
       </c>
       <c r="D192" s="64">
-        <v>0.15776</v>
+        <v>0.14112</v>
       </c>
       <c r="E192" s="28">
-        <v>1.3</v>
+        <v>0.74</v>
       </c>
       <c r="F192" s="28">
         <v>0</v>
@@ -7576,15 +7576,15 @@
       </c>
       <c r="I192" s="29">
         <f t="shared" si="5"/>
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="J192" s="31">
         <f t="shared" si="6"/>
-        <v>0.148571428571429</v>
+        <v>0.137142857142857</v>
       </c>
       <c r="K192" s="32">
         <f t="shared" si="7"/>
-        <v>26.0178300571429</v>
+        <v>13.5657375085714</v>
       </c>
       <c r="L192" s="34">
         <f t="shared" si="8"/>
@@ -7621,10 +7621,10 @@
         <v>17</v>
       </c>
       <c r="C193" s="28">
-        <v>7.114</v>
+        <v>7.128</v>
       </c>
       <c r="D193" s="64">
-        <v>0.14057</v>
+        <v>0.14029</v>
       </c>
       <c r="E193" s="28">
         <v>0</v>
@@ -7684,13 +7684,13 @@
         <v>18</v>
       </c>
       <c r="C194" s="28">
-        <v>7.211</v>
+        <v>7.212</v>
       </c>
       <c r="D194" s="64">
-        <v>0.13868</v>
+        <v>0.13865</v>
       </c>
       <c r="E194" s="28">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="F194" s="28">
         <v>0</v>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="K194" s="32">
         <f t="shared" si="7"/>
-        <v>29.3739761828572</v>
+        <v>0</v>
       </c>
       <c r="L194" s="34">
         <f t="shared" si="8"/>
@@ -7810,13 +7810,13 @@
         <v>20</v>
       </c>
       <c r="C196" s="28">
-        <v>7.212</v>
+        <v>7.225</v>
       </c>
       <c r="D196" s="64">
-        <v>0.13865</v>
+        <v>0.13841</v>
       </c>
       <c r="E196" s="28">
-        <v>0.01</v>
+        <v>2.15</v>
       </c>
       <c r="F196" s="28">
         <v>0</v>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="K196" s="32">
         <f t="shared" si="7"/>
-        <v>0.184741988571429</v>
+        <v>39.4139670857143</v>
       </c>
       <c r="L196" s="34">
         <f t="shared" si="8"/>
@@ -7873,13 +7873,13 @@
         <v>21</v>
       </c>
       <c r="C197" s="28">
-        <v>7.236</v>
+        <v>7.311</v>
       </c>
       <c r="D197" s="64">
-        <v>0.13819</v>
+        <v>0.13678</v>
       </c>
       <c r="E197" s="28">
-        <v>0.37</v>
+        <v>0.14</v>
       </c>
       <c r="F197" s="28">
         <v>0</v>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="K197" s="32">
         <f t="shared" si="7"/>
-        <v>6.83545357714286</v>
+        <v>2.56649088</v>
       </c>
       <c r="L197" s="34">
         <f t="shared" si="8"/>
@@ -7936,10 +7936,10 @@
         <v>22</v>
       </c>
       <c r="C198" s="28">
-        <v>7.419</v>
+        <v>7.418</v>
       </c>
       <c r="D198" s="64">
-        <v>0.13479</v>
+        <v>0.1348</v>
       </c>
       <c r="E198" s="28">
         <v>0</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="L199" s="34">
         <f t="shared" si="8"/>
-        <v>1.23931084</v>
+        <v>1.22977688</v>
       </c>
       <c r="T199">
         <v>12</v>
@@ -8125,13 +8125,13 @@
         <v>25</v>
       </c>
       <c r="C201" s="28">
-        <v>7.549</v>
+        <v>7.555</v>
       </c>
       <c r="D201" s="64">
-        <v>0.13247</v>
+        <v>0.13237</v>
       </c>
       <c r="E201" s="28">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="F201" s="28">
         <v>0</v>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="K201" s="32">
         <f t="shared" si="7"/>
-        <v>10.9767531542857</v>
+        <v>9.66253262857143</v>
       </c>
       <c r="L201" s="34">
         <f t="shared" si="8"/>
@@ -8251,10 +8251,10 @@
         <v>27</v>
       </c>
       <c r="C203" s="28">
-        <v>7.583</v>
+        <v>7.585</v>
       </c>
       <c r="D203" s="64">
-        <v>0.13187</v>
+        <v>0.13184</v>
       </c>
       <c r="E203" s="28">
         <v>0.22</v>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="K203" s="32">
         <f t="shared" si="7"/>
-        <v>3.89497692571429</v>
+        <v>3.86501305142857</v>
       </c>
       <c r="L203" s="34">
         <f t="shared" si="8"/>
@@ -8378,13 +8378,13 @@
         <v>29</v>
       </c>
       <c r="C205" s="28">
-        <v>7.592</v>
+        <v>7.593</v>
       </c>
       <c r="D205" s="64">
-        <v>0.13171</v>
+        <v>0.1317</v>
       </c>
       <c r="E205" s="28">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="F205" s="28">
         <v>0</v>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="K205" s="32">
         <f t="shared" si="7"/>
-        <v>1.41635524571429</v>
+        <v>1.05409446857143</v>
       </c>
       <c r="L205" s="34">
         <f t="shared" si="8"/>
@@ -8504,10 +8504,10 @@
         <v>31</v>
       </c>
       <c r="C207" s="28">
-        <v>7.596</v>
+        <v>7.597</v>
       </c>
       <c r="D207" s="64">
-        <v>0.13164</v>
+        <v>0.13163</v>
       </c>
       <c r="E207" s="28">
         <v>0.02</v>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="K207" s="32">
         <f t="shared" si="7"/>
-        <v>0.354088811428571</v>
+        <v>0.351364822857143</v>
       </c>
       <c r="L207" s="34">
         <f t="shared" si="8"/>
@@ -8756,13 +8756,13 @@
         <v>35</v>
       </c>
       <c r="C211" s="28">
-        <v>7.64</v>
+        <v>7.656</v>
       </c>
       <c r="D211" s="64">
-        <v>0.13088</v>
+        <v>0.13062</v>
       </c>
       <c r="E211" s="28">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F211" s="28">
         <v>0</v>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="K211" s="32">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.175682411428571</v>
       </c>
       <c r="L211" s="34">
         <f t="shared" si="8"/>
@@ -8825,7 +8825,7 @@
         <v>0.13058</v>
       </c>
       <c r="E212" s="28">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="F212" s="28">
         <v>0</v>
@@ -8846,7 +8846,7 @@
       </c>
       <c r="K212" s="32">
         <f t="shared" si="7"/>
-        <v>7.61290944571429</v>
+        <v>5.79751957714286</v>
       </c>
       <c r="L212" s="34">
         <f t="shared" si="8"/>
@@ -8888,7 +8888,7 @@
         <v>0.13058</v>
       </c>
       <c r="E213" s="28">
-        <v>0.41</v>
+        <v>0.51</v>
       </c>
       <c r="F213" s="28">
         <v>0</v>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="K213" s="32">
         <f t="shared" si="7"/>
-        <v>7.25882063428572</v>
+        <v>8.95980298285714</v>
       </c>
       <c r="L213" s="34">
         <f t="shared" si="8"/>
@@ -8945,13 +8945,13 @@
         <v>38</v>
       </c>
       <c r="C214" s="28">
-        <v>8.202</v>
+        <v>8.767</v>
       </c>
       <c r="D214" s="64">
-        <v>0.12192</v>
+        <v>0.11407</v>
       </c>
       <c r="E214" s="28">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F214" s="28">
         <v>0</v>
@@ -8964,15 +8964,15 @@
       </c>
       <c r="I214" s="29">
         <f t="shared" si="5"/>
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J214" s="31">
         <f t="shared" si="6"/>
-        <v>0.125714285714286</v>
+        <v>0.12</v>
       </c>
       <c r="K214" s="32">
         <f t="shared" si="7"/>
-        <v>0.169346822857143</v>
+        <v>0</v>
       </c>
       <c r="L214" s="34">
         <f t="shared" si="8"/>
@@ -9008,10 +9008,10 @@
         <v>39</v>
       </c>
       <c r="C215" s="28">
-        <v>9.386</v>
+        <v>9.389</v>
       </c>
       <c r="D215" s="64">
-        <v>0.10654</v>
+        <v>0.10651</v>
       </c>
       <c r="E215" s="28">
         <v>0</v>
@@ -9039,7 +9039,7 @@
       </c>
       <c r="L215" s="34">
         <f t="shared" si="8"/>
-        <v>0.32329848</v>
+        <v>0.32081136</v>
       </c>
       <c r="T215">
         <v>30</v>
@@ -9071,13 +9071,13 @@
         <v>40</v>
       </c>
       <c r="C216" s="28">
-        <v>10.17</v>
+        <v>10.231</v>
       </c>
       <c r="D216" s="64">
-        <v>0.09833</v>
+        <v>0.09774</v>
       </c>
       <c r="E216" s="28">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="F216" s="28">
         <v>0</v>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="K216" s="32">
         <f t="shared" si="7"/>
-        <v>0.923709942857143</v>
+        <v>1.0693712</v>
       </c>
       <c r="L216" s="34">
         <f t="shared" si="8"/>
@@ -9134,13 +9134,13 @@
         <v>41</v>
       </c>
       <c r="C217" s="28">
-        <v>10.672</v>
+        <v>10.645</v>
       </c>
       <c r="D217" s="64">
-        <v>0.09371</v>
+        <v>0.09394</v>
       </c>
       <c r="E217" s="28">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="F217" s="28">
         <v>0</v>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="K217" s="32">
         <f t="shared" si="7"/>
-        <v>4.53387630285714</v>
+        <v>4.06361056</v>
       </c>
       <c r="L217" s="34">
         <f t="shared" si="8"/>
@@ -9197,13 +9197,13 @@
         <v>42</v>
       </c>
       <c r="C218" s="28">
-        <v>11.028</v>
+        <v>11.455</v>
       </c>
       <c r="D218" s="64">
-        <v>0.09068</v>
+        <v>0.0873</v>
       </c>
       <c r="E218" s="28">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F218" s="28">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="K218" s="32">
         <f t="shared" si="7"/>
-        <v>0.292508148571429</v>
+        <v>0.145128948571429</v>
       </c>
       <c r="L218" s="34">
         <f t="shared" si="8"/>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="L219" s="34">
         <f t="shared" si="8"/>
-        <v>3.21758963428571</v>
+        <v>3.19283686857143</v>
       </c>
       <c r="T219">
         <v>51</v>
@@ -9323,10 +9323,10 @@
         <v>44</v>
       </c>
       <c r="C220" s="28">
-        <v>11.759</v>
+        <v>11.79</v>
       </c>
       <c r="D220" s="64">
-        <v>0.08504</v>
+        <v>0.08482</v>
       </c>
       <c r="E220" s="28">
         <v>0</v>
@@ -9342,11 +9342,11 @@
       </c>
       <c r="I220" s="29">
         <f t="shared" si="5"/>
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J220" s="31">
         <f t="shared" si="6"/>
-        <v>0.108571428571429</v>
+        <v>0.102857142857143</v>
       </c>
       <c r="K220" s="32">
         <f t="shared" si="7"/>
@@ -9386,10 +9386,10 @@
         <v>45</v>
       </c>
       <c r="C221" s="28">
-        <v>12.403</v>
+        <v>12.437</v>
       </c>
       <c r="D221" s="64">
-        <v>0.08063</v>
+        <v>0.0804</v>
       </c>
       <c r="E221" s="28">
         <v>0</v>
@@ -9398,7 +9398,7 @@
         <v>0</v>
       </c>
       <c r="G221" s="28">
-        <v>6.08</v>
+        <v>5.96</v>
       </c>
       <c r="H221" s="28" t="s">
         <v>113</v>
@@ -9417,7 +9417,7 @@
       </c>
       <c r="L221" s="34">
         <f t="shared" si="8"/>
-        <v>84.2423467885714</v>
+        <v>81.9443873828571</v>
       </c>
       <c r="T221">
         <v>53</v>
@@ -9449,10 +9449,10 @@
         <v>46</v>
       </c>
       <c r="C222" s="28">
-        <v>12.717</v>
+        <v>12.723</v>
       </c>
       <c r="D222" s="64">
-        <v>0.07863</v>
+        <v>0.0786</v>
       </c>
       <c r="E222" s="28">
         <v>0</v>
@@ -9461,7 +9461,7 @@
         <v>0</v>
       </c>
       <c r="G222" s="28">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H222" s="28" t="s">
         <v>113</v>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="L222" s="34">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.137490582857143</v>
       </c>
       <c r="T222">
         <v>54</v>
@@ -9507,36 +9507,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="2:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B223" s="114" t="s">
-        <v>130</v>
-      </c>
-      <c r="C223" s="115"/>
-      <c r="D223" s="115"/>
-      <c r="E223" s="116">
-        <f>SUM(E177:E222)</f>
-        <v>91.69</v>
-      </c>
-      <c r="F223" s="116">
-        <f t="shared" ref="F223" si="9">SUM(F177:F222)</f>
-        <v>0</v>
-      </c>
-      <c r="G223" s="116">
-        <f>SUM(G177:G222)</f>
-        <v>92.48</v>
-      </c>
-      <c r="H223" s="140" t="s">
-        <v>131</v>
-      </c>
-      <c r="I223" s="141"/>
-      <c r="J223" s="142"/>
-      <c r="K223" s="117">
-        <f>SQRT(SUMSQ(K177:K222))</f>
-        <v>1642.09681311277</v>
-      </c>
-      <c r="L223" s="117">
-        <f>SQRT(SUMSQ(L177:L222))</f>
-        <v>1487.16649860768</v>
+    <row r="223" spans="2:27" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B223" s="33">
+        <v>47</v>
+      </c>
+      <c r="C223" s="28">
+        <v>12.816</v>
+      </c>
+      <c r="D223" s="64">
+        <v>0.07803</v>
+      </c>
+      <c r="E223" s="28">
+        <v>0.06</v>
+      </c>
+      <c r="F223" s="28">
+        <v>0</v>
+      </c>
+      <c r="G223" s="28">
+        <v>0</v>
+      </c>
+      <c r="H223" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="I223" s="29">
+        <f t="shared" si="5"/>
+        <v>0.08</v>
+      </c>
+      <c r="J223" s="31">
+        <f t="shared" si="6"/>
+        <v>0.102857142857143</v>
+      </c>
+      <c r="K223" s="32">
+        <f t="shared" si="7"/>
+        <v>0.824943497142857</v>
+      </c>
+      <c r="L223" s="34">
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="T223">
         <v>55</v>
@@ -9563,7 +9570,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B224" s="114" t="s">
+        <v>130</v>
+      </c>
+      <c r="C224" s="115"/>
+      <c r="D224" s="115"/>
+      <c r="E224" s="116">
+        <f>SUM(E177:E223)</f>
+        <v>91.89</v>
+      </c>
+      <c r="F224" s="116">
+        <f t="shared" ref="F224" si="9">SUM(F177:F223)</f>
+        <v>0</v>
+      </c>
+      <c r="G224" s="116">
+        <f>SUM(G177:G223)</f>
+        <v>92.58</v>
+      </c>
+      <c r="H224" s="140" t="s">
+        <v>131</v>
+      </c>
+      <c r="I224" s="141"/>
+      <c r="J224" s="142"/>
+      <c r="K224" s="117">
+        <f>SQRT(SUMSQ(K177:K223))</f>
+        <v>1652.42295385476</v>
+      </c>
+      <c r="L224" s="117">
+        <f>SQRT(SUMSQ(L177:L223))</f>
+        <v>1598.68378643436</v>
+      </c>
       <c r="T224">
         <v>56</v>
       </c>
@@ -9590,19 +9627,6 @@
       </c>
     </row>
     <row r="225" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H225" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="J225" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="K225" s="30">
-        <f>E165</f>
-        <v>13470.77</v>
-      </c>
-      <c r="L225" t="s">
-        <v>134</v>
-      </c>
       <c r="T225">
         <v>57</v>
       </c>
@@ -9630,14 +9654,14 @@
     </row>
     <row r="226" spans="2:27" x14ac:dyDescent="0.3">
       <c r="H226" s="12" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J226" s="12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="K226" s="30">
-        <f>E166</f>
-        <v>13470.77</v>
+        <f>E165</f>
+        <v>13367.14</v>
       </c>
       <c r="L226" t="s">
         <v>134</v>
@@ -9668,8 +9692,19 @@
       </c>
     </row>
     <row r="227" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="K227" s="53"/>
-      <c r="L227" s="53"/>
+      <c r="H227" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="J227" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="K227" s="30">
+        <f>E166</f>
+        <v>13367.14</v>
+      </c>
+      <c r="L227" t="s">
+        <v>134</v>
+      </c>
       <c r="T227">
         <v>59</v>
       </c>
@@ -9696,20 +9731,8 @@
       </c>
     </row>
     <row r="228" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H228" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="J228" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="K228" s="30">
-        <f>K225*VLOOKUP(MAX(E177:E222),E177:J222,6,0)</f>
-        <v>2103.82882020045</v>
-      </c>
-      <c r="L228" s="30">
-        <f>K225*VLOOKUP(MAX(G177:G222),G177:J222,4,0)</f>
-        <v>2309.27485714286</v>
-      </c>
+      <c r="K228" s="53"/>
+      <c r="L228" s="53"/>
       <c r="T228">
         <v>60</v>
       </c>
@@ -9736,16 +9759,19 @@
       </c>
     </row>
     <row r="229" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H229" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="J229" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K229" s="30">
-        <f>0.9*K228</f>
-        <v>1893.44593818041</v>
+        <f>K226*VLOOKUP(MAX(E177:E223),E177:J223,6,0)</f>
+        <v>2108.06142431666</v>
       </c>
       <c r="L229" s="30">
-        <f>0.9*L228</f>
-        <v>2078.34737142857</v>
+        <f>K226*VLOOKUP(MAX(G177:G223),G177:J223,4,0)</f>
+        <v>2291.50971428571</v>
       </c>
       <c r="T229">
         <v>61</v>
@@ -9773,9 +9799,17 @@
       </c>
     </row>
     <row r="230" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="J230" s="12"/>
-      <c r="K230" s="53"/>
-      <c r="L230" s="53"/>
+      <c r="J230" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="K230" s="30">
+        <f>0.9*K229</f>
+        <v>1897.25528188499</v>
+      </c>
+      <c r="L230" s="30">
+        <f>0.9*L229</f>
+        <v>2062.35874285714</v>
+      </c>
       <c r="T230">
         <v>62</v>
       </c>
@@ -9802,20 +9836,9 @@
       </c>
     </row>
     <row r="231" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H231" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="J231" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="K231" s="30">
-        <f>K225*G168</f>
-        <v>2309.27485714286</v>
-      </c>
-      <c r="L231" s="30">
-        <f>K225*G168</f>
-        <v>2309.27485714286</v>
-      </c>
+      <c r="J231" s="12"/>
+      <c r="K231" s="53"/>
+      <c r="L231" s="53"/>
       <c r="T231">
         <v>63</v>
       </c>
@@ -9842,16 +9865,19 @@
       </c>
     </row>
     <row r="232" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H232" s="12" t="s">
+        <v>140</v>
+      </c>
       <c r="J232" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K232" s="30">
-        <f>0.8*K231</f>
-        <v>1847.41988571429</v>
+        <f>K226*G168</f>
+        <v>2291.50971428571</v>
       </c>
       <c r="L232" s="30">
-        <f>0.8*L231</f>
-        <v>1847.41988571429</v>
+        <f>K226*G168</f>
+        <v>2291.50971428571</v>
       </c>
       <c r="T232">
         <v>64</v>
@@ -9879,7 +9905,17 @@
       </c>
     </row>
     <row r="233" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="J233" s="12"/>
+      <c r="J233" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="K233" s="30">
+        <f>0.8*K232</f>
+        <v>1833.20777142857</v>
+      </c>
+      <c r="L233" s="30">
+        <f>0.8*L232</f>
+        <v>1833.20777142857</v>
+      </c>
       <c r="T233">
         <v>65</v>
       </c>
@@ -9906,6 +9942,7 @@
       </c>
     </row>
     <row r="234" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="J234" s="12"/>
       <c r="T234">
         <v>66</v>
       </c>
@@ -9932,20 +9969,6 @@
       </c>
     </row>
     <row r="235" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H235" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="J235" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="K235" s="44">
-        <f>MAX(K232,K229)</f>
-        <v>1893.44593818041</v>
-      </c>
-      <c r="L235" s="44">
-        <f>MAX(L232,L229)</f>
-        <v>2078.34737142857</v>
-      </c>
       <c r="T235">
         <v>67</v>
       </c>
@@ -9972,7 +9995,20 @@
       </c>
     </row>
     <row r="236" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H236" s="12"/>
+      <c r="H236" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="J236" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="K236" s="44">
+        <f>MAX(K233,K230)</f>
+        <v>1897.25528188499</v>
+      </c>
+      <c r="L236" s="44">
+        <f>MAX(L233,L230)</f>
+        <v>2062.35874285714</v>
+      </c>
       <c r="T236">
         <v>68</v>
       </c>
@@ -9999,10 +10035,7 @@
       </c>
     </row>
     <row r="237" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="K237" s="134" t="s">
-        <v>145</v>
-      </c>
-      <c r="L237" s="135"/>
+      <c r="H237" s="12"/>
       <c r="T237">
         <v>69</v>
       </c>
@@ -10029,12 +10062,10 @@
       </c>
     </row>
     <row r="238" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="K238" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="L238" s="23" t="s">
-        <v>147</v>
-      </c>
+      <c r="K238" s="134" t="s">
+        <v>145</v>
+      </c>
+      <c r="L238" s="135"/>
       <c r="T238">
         <v>70</v>
       </c>
@@ -10061,16 +10092,11 @@
       </c>
     </row>
     <row r="239" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="J239" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="K239" s="47">
-        <f>K235/1000</f>
-        <v>1.89344593818041</v>
-      </c>
-      <c r="L239" s="47">
-        <f>L235/1000</f>
-        <v>2.07834737142857</v>
+      <c r="K239" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="L239" s="23" t="s">
+        <v>147</v>
       </c>
       <c r="T239">
         <v>71</v>
@@ -10099,15 +10125,15 @@
     </row>
     <row r="240" spans="2:27" x14ac:dyDescent="0.3">
       <c r="J240" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K240" s="47">
-        <f>K223/1000</f>
-        <v>1.64209681311277</v>
+        <f>K236/1000</f>
+        <v>1.89725528188499</v>
       </c>
       <c r="L240" s="47">
-        <f>L223/1000</f>
-        <v>1.48716649860768</v>
+        <f>L236/1000</f>
+        <v>2.06235874285714</v>
       </c>
       <c r="T240">
         <v>72</v>
@@ -10136,15 +10162,15 @@
     </row>
     <row r="241" spans="2:27" x14ac:dyDescent="0.3">
       <c r="J241" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="K241" s="68" t="str">
-        <f>IF(K223&gt;=K235,"Se Cumple","No se Cumple")</f>
-        <v>No se Cumple</v>
-      </c>
-      <c r="L241" s="68" t="str">
-        <f>IF(L223&gt;=K235,"Se Cumple","No se Cumple")</f>
-        <v>No se Cumple</v>
+        <v>149</v>
+      </c>
+      <c r="K241" s="47">
+        <f>K224/1000</f>
+        <v>1.65242295385476</v>
+      </c>
+      <c r="L241" s="47">
+        <f>L224/1000</f>
+        <v>1.59868378643436</v>
       </c>
       <c r="T241">
         <v>73</v>
@@ -10172,16 +10198,16 @@
       </c>
     </row>
     <row r="242" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="J242" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="K242" s="86">
-        <f>MAX(K239/K240,1)</f>
-        <v>1.15306595997296</v>
-      </c>
-      <c r="L242" s="86">
-        <f>MAX(L239/L240,1)</f>
-        <v>1.39752164493644</v>
+      <c r="J242" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="K242" s="68" t="str">
+        <f>IF(K224&gt;=K236,"Se Cumple","No se Cumple")</f>
+        <v>No se Cumple</v>
+      </c>
+      <c r="L242" s="68" t="str">
+        <f>IF(L224&gt;=K236,"Se Cumple","No se Cumple")</f>
+        <v>No se Cumple</v>
       </c>
       <c r="T242">
         <v>74</v>
@@ -10209,6 +10235,17 @@
       </c>
     </row>
     <row r="243" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="J243" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="K243" s="86">
+        <f>MAX(K240/K241,1)</f>
+        <v>1.14816565423464</v>
+      </c>
+      <c r="L243" s="86">
+        <f>MAX(L240/L241,1)</f>
+        <v>1.29003544062766</v>
+      </c>
       <c r="T243">
         <v>75</v>
       </c>
@@ -10235,17 +10272,6 @@
       </c>
     </row>
     <row r="244" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="J244" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="K244" s="86">
-        <f>IF(K229/K223&lt;1,"N/A",K229/K223)</f>
-        <v>1.15306595997296</v>
-      </c>
-      <c r="L244" s="86">
-        <f>IF(L229/L223&lt;1,"N/A",L229/L223)</f>
-        <v>1.39752164493644</v>
-      </c>
       <c r="T244">
         <v>76</v>
       </c>
@@ -10272,6 +10298,17 @@
       </c>
     </row>
     <row r="245" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="J245" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="K245" s="86">
+        <f>IF(K230/K224&lt;1,"N/A",K230/K224)</f>
+        <v>1.14816565423464</v>
+      </c>
+      <c r="L245" s="86">
+        <f>IF(L230/L224&lt;1,"N/A",L230/L224)</f>
+        <v>1.29003544062766</v>
+      </c>
       <c r="T245">
         <v>77</v>
       </c>
@@ -10298,14 +10335,6 @@
       </c>
     </row>
     <row r="246" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="K246" s="53">
-        <f>K228/K223</f>
-        <v>1.28118439996995</v>
-      </c>
-      <c r="L246" s="53">
-        <f>L228/L223</f>
-        <v>1.55280182770715</v>
-      </c>
       <c r="T246">
         <v>78</v>
       </c>
@@ -10332,6 +10361,14 @@
       </c>
     </row>
     <row r="247" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="K247" s="53">
+        <f>K229/K224</f>
+        <v>1.27573961581627</v>
+      </c>
+      <c r="L247" s="53">
+        <f>L229/L224</f>
+        <v>1.43337271180851</v>
+      </c>
       <c r="T247">
         <v>79</v>
       </c>
@@ -10384,22 +10421,6 @@
       </c>
     </row>
     <row r="249" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B249" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C249" s="4"/>
-      <c r="D249" s="4"/>
-      <c r="E249" s="4"/>
-      <c r="F249" s="4"/>
-      <c r="G249" s="4"/>
-      <c r="H249" s="4"/>
-      <c r="I249" s="4"/>
-      <c r="J249" s="4"/>
-      <c r="K249" s="4"/>
-      <c r="L249" s="4"/>
-      <c r="M249" s="4"/>
-      <c r="N249" s="4"/>
-      <c r="O249" s="4"/>
       <c r="T249">
         <v>81</v>
       </c>
@@ -10426,6 +10447,22 @@
       </c>
     </row>
     <row r="250" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B250" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C250" s="4"/>
+      <c r="D250" s="4"/>
+      <c r="E250" s="4"/>
+      <c r="F250" s="4"/>
+      <c r="G250" s="4"/>
+      <c r="H250" s="4"/>
+      <c r="I250" s="4"/>
+      <c r="J250" s="4"/>
+      <c r="K250" s="4"/>
+      <c r="L250" s="4"/>
+      <c r="M250" s="4"/>
+      <c r="N250" s="4"/>
+      <c r="O250" s="4"/>
       <c r="T250">
         <v>82</v>
       </c>
@@ -10452,9 +10489,6 @@
       </c>
     </row>
     <row r="251" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B251" t="s">
-        <v>154</v>
-      </c>
       <c r="T251">
         <v>83</v>
       </c>
@@ -10481,6 +10515,9 @@
       </c>
     </row>
     <row r="252" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B252" t="s">
+        <v>154</v>
+      </c>
       <c r="T252">
         <v>84</v>
       </c>
@@ -10507,250 +10544,243 @@
       </c>
     </row>
     <row r="253" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B253" s="12" t="s">
+      <c r="T253">
+        <v>85</v>
+      </c>
+      <c r="U253" t="s">
+        <v>129</v>
+      </c>
+      <c r="V253">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="W253">
+        <v>-1.621</v>
+      </c>
+      <c r="X253">
+        <v>-0.97299999999999998</v>
+      </c>
+      <c r="Y253">
+        <v>0</v>
+      </c>
+      <c r="Z253">
+        <v>0</v>
+      </c>
+      <c r="AA253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B254" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C253" s="40">
+      <c r="C254" s="40">
         <f>P33</f>
         <v>0.4</v>
       </c>
-      <c r="H253" t="s">
+      <c r="H254" t="s">
         <v>99</v>
       </c>
-      <c r="I253" t="s">
+      <c r="I254" t="s">
         <v>155</v>
       </c>
-      <c r="T253">
-        <v>85</v>
-      </c>
-      <c r="U253" t="s">
+      <c r="T254">
+        <v>88</v>
+      </c>
+      <c r="U254" t="s">
         <v>129</v>
       </c>
-      <c r="V253">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="W253">
-        <v>-1.621</v>
-      </c>
-      <c r="X253">
-        <v>-0.97299999999999998</v>
-      </c>
-      <c r="Y253">
-        <v>0</v>
-      </c>
-      <c r="Z253">
-        <v>0</v>
-      </c>
-      <c r="AA253">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B254" s="12" t="s">
+      <c r="V254">
+        <v>-3.0379999999999998</v>
+      </c>
+      <c r="W254">
+        <v>-4.657</v>
+      </c>
+      <c r="X254">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="Y254">
+        <v>0</v>
+      </c>
+      <c r="Z254">
+        <v>0</v>
+      </c>
+      <c r="AA254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B255" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C254" s="40">
+      <c r="C255" s="40">
         <f>P55</f>
         <v>3</v>
       </c>
-      <c r="H254" t="s">
+      <c r="H255" t="s">
         <v>108</v>
       </c>
-      <c r="I254" t="s">
+      <c r="I255" t="s">
         <v>110</v>
       </c>
-      <c r="T254">
-        <v>88</v>
-      </c>
-      <c r="U254" t="s">
+      <c r="T255">
+        <v>90</v>
+      </c>
+      <c r="U255" t="s">
         <v>129</v>
       </c>
-      <c r="V254">
-        <v>-3.0379999999999998</v>
-      </c>
-      <c r="W254">
-        <v>-4.657</v>
-      </c>
-      <c r="X254">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="Y254">
-        <v>0</v>
-      </c>
-      <c r="Z254">
-        <v>0</v>
-      </c>
-      <c r="AA254">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B255" s="12" t="s">
+      <c r="V255">
+        <v>-2.149</v>
+      </c>
+      <c r="W255">
+        <v>-1.8620000000000001</v>
+      </c>
+      <c r="X255">
+        <v>1.2E-2</v>
+      </c>
+      <c r="Y255">
+        <v>0</v>
+      </c>
+      <c r="Z255">
+        <v>0</v>
+      </c>
+      <c r="AA255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B256" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="C255" s="40">
+      <c r="C256" s="40">
         <f>P57</f>
         <v>0.6</v>
       </c>
-      <c r="H255">
+      <c r="H256">
         <v>0.01</v>
       </c>
-      <c r="I255" s="53">
+      <c r="I256" s="53">
         <v>6.2857142857142861E-2</v>
       </c>
-      <c r="T255">
-        <v>90</v>
-      </c>
-      <c r="U255" t="s">
+      <c r="T256">
+        <v>92</v>
+      </c>
+      <c r="U256" t="s">
         <v>129</v>
       </c>
-      <c r="V255">
-        <v>-2.149</v>
-      </c>
-      <c r="W255">
-        <v>-1.8620000000000001</v>
-      </c>
-      <c r="X255">
-        <v>1.2E-2</v>
-      </c>
-      <c r="Y255">
-        <v>0</v>
-      </c>
-      <c r="Z255">
-        <v>0</v>
-      </c>
-      <c r="AA255">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B256" s="12" t="s">
+      <c r="V256">
+        <v>-4.29</v>
+      </c>
+      <c r="W256">
+        <v>0.99299999999999999</v>
+      </c>
+      <c r="X256">
+        <v>2E-3</v>
+      </c>
+      <c r="Y256">
+        <v>0</v>
+      </c>
+      <c r="Z256">
+        <v>0</v>
+      </c>
+      <c r="AA256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B257" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="C256" s="40">
+      <c r="C257" s="40">
         <f>Q85</f>
         <v>1</v>
       </c>
-      <c r="H256">
+      <c r="H257">
         <v>0.02</v>
       </c>
-      <c r="I256" s="53">
-        <f>IF(H256&lt;$C$255/3,   ($C$256*$C$253/$C$257)*(1+(3*($C$254-1)*H256/$C$255)),   IF(H256&lt;=$C$255,   $C$256*$C$253*$C$254/$C$257,   $C$256*$C$253*$C$254/$C$257*($C$255/H256)^(2/3)   ))</f>
+      <c r="I257" s="53">
+        <f>IF(H257&lt;$C$256/3,   ($C$257*$C$254/$C$258)*(1+(3*($C$255-1)*H257/$C$256)),   IF(H257&lt;=$C$256,   $C$257*$C$254*$C$255/$C$258,   $C$257*$C$254*$C$255/$C$258*($C$256/H257)^(2/3)   ))</f>
         <v>6.8571428571428575E-2</v>
       </c>
-      <c r="T256">
-        <v>92</v>
-      </c>
-      <c r="U256" t="s">
+      <c r="T257">
+        <v>94</v>
+      </c>
+      <c r="U257" t="s">
         <v>129</v>
       </c>
-      <c r="V256">
-        <v>-4.29</v>
-      </c>
-      <c r="W256">
-        <v>0.99299999999999999</v>
-      </c>
-      <c r="X256">
-        <v>2E-3</v>
-      </c>
-      <c r="Y256">
-        <v>0</v>
-      </c>
-      <c r="Z256">
-        <v>0</v>
-      </c>
-      <c r="AA256">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B257" s="12" t="s">
+      <c r="V257">
+        <v>-3.952</v>
+      </c>
+      <c r="W257">
+        <v>1.1240000000000001</v>
+      </c>
+      <c r="X257">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="Y257">
+        <v>0</v>
+      </c>
+      <c r="Z257">
+        <v>0</v>
+      </c>
+      <c r="AA257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B258" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="C257" s="40">
+      <c r="C258" s="40">
         <f>P99</f>
         <v>7</v>
       </c>
-      <c r="H257">
+      <c r="H258">
         <v>0.03</v>
       </c>
-      <c r="I257" s="53">
-        <f t="shared" ref="I257:I319" si="10">IF(H257&lt;$C$255/3,   ($C$256*$C$253/$C$257)*(1+(3*($C$254-1)*H257/$C$255)),   IF(H257&lt;=$C$255,   $C$256*$C$253*$C$254/$C$257,   $C$256*$C$253*$C$254/$C$257*($C$255/H257)^(2/3)   ))</f>
+      <c r="I258" s="53">
+        <f t="shared" ref="I258:I320" si="10">IF(H258&lt;$C$256/3,   ($C$257*$C$254/$C$258)*(1+(3*($C$255-1)*H258/$C$256)),   IF(H258&lt;=$C$256,   $C$257*$C$254*$C$255/$C$258,   $C$257*$C$254*$C$255/$C$258*($C$256/H258)^(2/3)   ))</f>
         <v>7.4285714285714288E-2</v>
       </c>
-      <c r="T257">
-        <v>94</v>
-      </c>
-      <c r="U257" t="s">
+      <c r="T258">
+        <v>97</v>
+      </c>
+      <c r="U258" t="s">
         <v>129</v>
       </c>
-      <c r="V257">
-        <v>-3.952</v>
-      </c>
-      <c r="W257">
-        <v>1.1240000000000001</v>
-      </c>
-      <c r="X257">
+      <c r="V258">
+        <v>-3.2480000000000002</v>
+      </c>
+      <c r="W258">
+        <v>0.83499999999999996</v>
+      </c>
+      <c r="X258">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="Y257">
-        <v>0</v>
-      </c>
-      <c r="Z257">
-        <v>0</v>
-      </c>
-      <c r="AA257">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B258" s="12" t="s">
+      <c r="Y258">
+        <v>0</v>
+      </c>
+      <c r="Z258">
+        <v>0</v>
+      </c>
+      <c r="AA258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B259" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="C258" s="40">
+      <c r="C259" s="40">
         <f>P97</f>
         <v>6</v>
       </c>
-      <c r="H258">
+      <c r="H259">
         <v>0.04</v>
       </c>
-      <c r="I258" s="53">
+      <c r="I259" s="53">
         <f t="shared" si="10"/>
         <v>0.08</v>
       </c>
-      <c r="T258">
-        <v>97</v>
-      </c>
-      <c r="U258" t="s">
-        <v>129</v>
-      </c>
-      <c r="V258">
-        <v>-3.2480000000000002</v>
-      </c>
-      <c r="W258">
-        <v>0.83499999999999996</v>
-      </c>
-      <c r="X258">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="Y258">
-        <v>0</v>
-      </c>
-      <c r="Z258">
-        <v>0</v>
-      </c>
-      <c r="AA258">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H259">
-        <v>0.05</v>
-      </c>
-      <c r="I259" s="53">
-        <f>IF(H259&lt;$C$255/3,   ($C$256*$C$253/$C$257)*(1+(3*($C$254-1)*H259/$C$255)),   IF(H259&lt;=$C$255,   $C$256*$C$253*$C$254/$C$257,   $C$256*$C$253*$C$254/$C$257*($C$255/H259)^(2/3)   ))</f>
-        <v>8.5714285714285715E-2</v>
-      </c>
       <c r="T259">
         <v>101</v>
       </c>
@@ -10778,474 +10808,474 @@
     </row>
     <row r="260" spans="2:27" x14ac:dyDescent="0.3">
       <c r="H260">
+        <v>0.05</v>
+      </c>
+      <c r="I260" s="53">
+        <f>IF(H260&lt;$C$256/3,   ($C$257*$C$254/$C$258)*(1+(3*($C$255-1)*H260/$C$256)),   IF(H260&lt;=$C$256,   $C$257*$C$254*$C$255/$C$258,   $C$257*$C$254*$C$255/$C$258*($C$256/H260)^(2/3)   ))</f>
+        <v>8.5714285714285715E-2</v>
+      </c>
+      <c r="T260">
+        <v>104</v>
+      </c>
+      <c r="U260" t="s">
+        <v>129</v>
+      </c>
+      <c r="V260">
+        <v>-2.2410000000000001</v>
+      </c>
+      <c r="W260">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="X260">
+        <v>2E-3</v>
+      </c>
+      <c r="Y260">
+        <v>0</v>
+      </c>
+      <c r="Z260">
+        <v>0</v>
+      </c>
+      <c r="AA260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H261">
         <v>0.06</v>
       </c>
-      <c r="I260" s="53">
+      <c r="I261" s="53">
         <f t="shared" si="10"/>
         <v>9.1428571428571442E-2</v>
       </c>
-      <c r="T260">
-        <v>104</v>
-      </c>
-      <c r="U260" t="s">
+      <c r="T261">
+        <v>107</v>
+      </c>
+      <c r="U261" t="s">
         <v>129</v>
       </c>
-      <c r="V260">
-        <v>-2.2410000000000001</v>
-      </c>
-      <c r="W260">
-        <v>0.56100000000000005</v>
-      </c>
-      <c r="X260">
-        <v>2E-3</v>
-      </c>
-      <c r="Y260">
-        <v>0</v>
-      </c>
-      <c r="Z260">
-        <v>0</v>
-      </c>
-      <c r="AA260">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H261">
+      <c r="V261">
+        <v>-1.9279999999999999</v>
+      </c>
+      <c r="W261">
+        <v>0.443</v>
+      </c>
+      <c r="X261">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="Y261">
+        <v>0</v>
+      </c>
+      <c r="Z261">
+        <v>0</v>
+      </c>
+      <c r="AA261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H262">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I261" s="53">
+      <c r="I262" s="53">
         <f t="shared" si="10"/>
         <v>9.7142857142857156E-2</v>
       </c>
-      <c r="T261">
-        <v>107</v>
-      </c>
-      <c r="U261" t="s">
+      <c r="T262">
+        <v>111</v>
+      </c>
+      <c r="U262" t="s">
         <v>129</v>
       </c>
-      <c r="V261">
-        <v>-1.9279999999999999</v>
-      </c>
-      <c r="W261">
-        <v>0.443</v>
-      </c>
-      <c r="X261">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="Y261">
-        <v>0</v>
-      </c>
-      <c r="Z261">
-        <v>0</v>
-      </c>
-      <c r="AA261">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H262">
+      <c r="V262">
+        <v>-1.6220000000000001</v>
+      </c>
+      <c r="W262">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="X262">
+        <v>0.01</v>
+      </c>
+      <c r="Y262">
+        <v>0</v>
+      </c>
+      <c r="Z262">
+        <v>0</v>
+      </c>
+      <c r="AA262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H263">
         <v>0.08</v>
       </c>
-      <c r="I262" s="53">
+      <c r="I263" s="53">
         <f t="shared" si="10"/>
         <v>0.10285714285714287</v>
       </c>
-      <c r="T262">
-        <v>111</v>
-      </c>
-      <c r="U262" t="s">
+      <c r="T263">
+        <v>115</v>
+      </c>
+      <c r="U263" t="s">
         <v>129</v>
       </c>
-      <c r="V262">
-        <v>-1.6220000000000001</v>
-      </c>
-      <c r="W262">
-        <v>0.38900000000000001</v>
-      </c>
-      <c r="X262">
-        <v>0.01</v>
-      </c>
-      <c r="Y262">
-        <v>0</v>
-      </c>
-      <c r="Z262">
-        <v>0</v>
-      </c>
-      <c r="AA262">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H263">
+      <c r="V263">
+        <v>-1.383</v>
+      </c>
+      <c r="W263">
+        <v>0.33100000000000002</v>
+      </c>
+      <c r="X263">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="Y263">
+        <v>0</v>
+      </c>
+      <c r="Z263">
+        <v>0</v>
+      </c>
+      <c r="AA263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H264">
         <v>0.09</v>
       </c>
-      <c r="I263" s="53">
+      <c r="I264" s="53">
         <f t="shared" si="10"/>
         <v>0.10857142857142858</v>
       </c>
-      <c r="T263">
-        <v>115</v>
-      </c>
-      <c r="U263" t="s">
+      <c r="T264">
+        <v>116</v>
+      </c>
+      <c r="U264" t="s">
         <v>129</v>
       </c>
-      <c r="V263">
-        <v>-1.383</v>
-      </c>
-      <c r="W263">
-        <v>0.33100000000000002</v>
-      </c>
-      <c r="X263">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="Y263">
-        <v>0</v>
-      </c>
-      <c r="Z263">
-        <v>0</v>
-      </c>
-      <c r="AA263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H264">
+      <c r="V264">
+        <v>-0.06</v>
+      </c>
+      <c r="W264">
+        <v>-0.06</v>
+      </c>
+      <c r="X264">
+        <v>-0.371</v>
+      </c>
+      <c r="Y264">
+        <v>-1.704</v>
+      </c>
+      <c r="Z264">
+        <v>0</v>
+      </c>
+      <c r="AA264">
+        <v>0.27600000000000002</v>
+      </c>
+    </row>
+    <row r="265" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H265">
         <v>0.1</v>
       </c>
-      <c r="I264" s="53">
+      <c r="I265" s="53">
         <f t="shared" si="10"/>
         <v>0.1142857142857143</v>
       </c>
-      <c r="T264">
-        <v>116</v>
-      </c>
-      <c r="U264" t="s">
+      <c r="T265">
+        <v>120</v>
+      </c>
+      <c r="U265" t="s">
         <v>129</v>
       </c>
-      <c r="V264">
-        <v>-0.06</v>
-      </c>
-      <c r="W264">
-        <v>-0.06</v>
-      </c>
-      <c r="X264">
-        <v>-0.371</v>
-      </c>
-      <c r="Y264">
-        <v>-1.704</v>
-      </c>
-      <c r="Z264">
-        <v>0</v>
-      </c>
-      <c r="AA264">
-        <v>0.27600000000000002</v>
-      </c>
-    </row>
-    <row r="265" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H265">
+      <c r="V265">
+        <v>-1.2230000000000001</v>
+      </c>
+      <c r="W265">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="X265">
+        <v>0</v>
+      </c>
+      <c r="Y265">
+        <v>0</v>
+      </c>
+      <c r="Z265">
+        <v>0</v>
+      </c>
+      <c r="AA265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H266">
         <v>0.11</v>
       </c>
-      <c r="I265" s="53">
+      <c r="I266" s="53">
         <f t="shared" si="10"/>
         <v>0.12000000000000001</v>
       </c>
-      <c r="T265">
-        <v>120</v>
-      </c>
-      <c r="U265" t="s">
+      <c r="T266">
+        <v>121</v>
+      </c>
+      <c r="U266" t="s">
         <v>129</v>
       </c>
-      <c r="V265">
-        <v>-1.2230000000000001</v>
-      </c>
-      <c r="W265">
-        <v>0.28699999999999998</v>
-      </c>
-      <c r="X265">
-        <v>0</v>
-      </c>
-      <c r="Y265">
-        <v>0</v>
-      </c>
-      <c r="Z265">
-        <v>0</v>
-      </c>
-      <c r="AA265">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H266">
+      <c r="V266">
+        <v>-1.123</v>
+      </c>
+      <c r="W266">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="X266">
+        <v>0</v>
+      </c>
+      <c r="Y266">
+        <v>0</v>
+      </c>
+      <c r="Z266">
+        <v>0</v>
+      </c>
+      <c r="AA266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H267">
         <v>0.12</v>
       </c>
-      <c r="I266" s="53">
+      <c r="I267" s="53">
         <f t="shared" si="10"/>
         <v>0.12571428571428572</v>
       </c>
-      <c r="T266">
-        <v>121</v>
-      </c>
-      <c r="U266" t="s">
+      <c r="T267">
+        <v>122</v>
+      </c>
+      <c r="U267" t="s">
         <v>129</v>
       </c>
-      <c r="V266">
-        <v>-1.123</v>
-      </c>
-      <c r="W266">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="X266">
-        <v>0</v>
-      </c>
-      <c r="Y266">
-        <v>0</v>
-      </c>
-      <c r="Z266">
-        <v>0</v>
-      </c>
-      <c r="AA266">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H267">
+      <c r="V267">
+        <v>-1.0820000000000001</v>
+      </c>
+      <c r="W267">
+        <v>-0.16600000000000001</v>
+      </c>
+      <c r="X267">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="Y267">
+        <v>0</v>
+      </c>
+      <c r="Z267">
+        <v>0</v>
+      </c>
+      <c r="AA267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H268">
         <v>0.13</v>
       </c>
-      <c r="I267" s="53">
+      <c r="I268" s="53">
         <f t="shared" si="10"/>
         <v>0.13142857142857142</v>
       </c>
-      <c r="T267">
-        <v>122</v>
-      </c>
-      <c r="U267" t="s">
+      <c r="T268">
+        <v>124</v>
+      </c>
+      <c r="U268" t="s">
         <v>129</v>
       </c>
-      <c r="V267">
-        <v>-1.0820000000000001</v>
-      </c>
-      <c r="W267">
-        <v>-0.16600000000000001</v>
-      </c>
-      <c r="X267">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="Y267">
-        <v>0</v>
-      </c>
-      <c r="Z267">
-        <v>0</v>
-      </c>
-      <c r="AA267">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="H268">
+      <c r="V268">
+        <v>-0.92200000000000004</v>
+      </c>
+      <c r="W268">
+        <v>-0.33700000000000002</v>
+      </c>
+      <c r="X268">
+        <v>1.2E-2</v>
+      </c>
+      <c r="Y268">
+        <v>0</v>
+      </c>
+      <c r="Z268">
+        <v>0</v>
+      </c>
+      <c r="AA268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="H269">
         <v>0.14000000000000001</v>
       </c>
-      <c r="I268" s="53">
+      <c r="I269" s="53">
         <f t="shared" si="10"/>
         <v>0.13714285714285718</v>
       </c>
-      <c r="T268">
-        <v>124</v>
-      </c>
-      <c r="U268" t="s">
+      <c r="T269">
+        <v>125</v>
+      </c>
+      <c r="U269" t="s">
         <v>129</v>
       </c>
-      <c r="V268">
-        <v>-0.92200000000000004</v>
-      </c>
-      <c r="W268">
-        <v>-0.33700000000000002</v>
-      </c>
-      <c r="X268">
-        <v>1.2E-2</v>
-      </c>
-      <c r="Y268">
-        <v>0</v>
-      </c>
-      <c r="Z268">
-        <v>0</v>
-      </c>
-      <c r="AA268">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269" spans="8:27" x14ac:dyDescent="0.3">
-      <c r="H269">
+      <c r="V269">
+        <v>-0.81899999999999995</v>
+      </c>
+      <c r="W269">
+        <v>-0.23100000000000001</v>
+      </c>
+      <c r="X269">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="Y269">
+        <v>0</v>
+      </c>
+      <c r="Z269">
+        <v>0</v>
+      </c>
+      <c r="AA269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="8:27" x14ac:dyDescent="0.3">
+      <c r="H270">
         <v>0.15</v>
       </c>
-      <c r="I269" s="53">
+      <c r="I270" s="53">
         <f t="shared" si="10"/>
         <v>0.14285714285714288</v>
       </c>
-      <c r="T269">
-        <v>125</v>
-      </c>
-      <c r="U269" t="s">
+      <c r="T270">
+        <v>126</v>
+      </c>
+      <c r="U270" t="s">
         <v>129</v>
       </c>
-      <c r="V269">
-        <v>-0.81899999999999995</v>
-      </c>
-      <c r="W269">
-        <v>-0.23100000000000001</v>
-      </c>
-      <c r="X269">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="Y269">
-        <v>0</v>
-      </c>
-      <c r="Z269">
-        <v>0</v>
-      </c>
-      <c r="AA269">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270" spans="8:27" x14ac:dyDescent="0.3">
-      <c r="H270">
+      <c r="V270">
+        <v>-0.90400000000000003</v>
+      </c>
+      <c r="W270">
+        <v>-9.8000000000000004E-2</v>
+      </c>
+      <c r="X270">
+        <v>0</v>
+      </c>
+      <c r="Y270">
+        <v>0</v>
+      </c>
+      <c r="Z270">
+        <v>0</v>
+      </c>
+      <c r="AA270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="8:27" x14ac:dyDescent="0.3">
+      <c r="H271">
         <v>0.16</v>
       </c>
-      <c r="I270" s="53">
+      <c r="I271" s="53">
         <f t="shared" si="10"/>
         <v>0.14857142857142858</v>
       </c>
-      <c r="T270">
-        <v>126</v>
-      </c>
-      <c r="U270" t="s">
+      <c r="T271">
+        <v>127</v>
+      </c>
+      <c r="U271" t="s">
         <v>129</v>
       </c>
-      <c r="V270">
-        <v>-0.90400000000000003</v>
-      </c>
-      <c r="W270">
-        <v>-9.8000000000000004E-2</v>
-      </c>
-      <c r="X270">
-        <v>0</v>
-      </c>
-      <c r="Y270">
-        <v>0</v>
-      </c>
-      <c r="Z270">
-        <v>0</v>
-      </c>
-      <c r="AA270">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="271" spans="8:27" x14ac:dyDescent="0.3">
-      <c r="H271">
+      <c r="V271">
+        <v>-1.0409999999999999</v>
+      </c>
+      <c r="W271">
+        <v>-0.17</v>
+      </c>
+      <c r="X271">
+        <v>0</v>
+      </c>
+      <c r="Y271">
+        <v>0</v>
+      </c>
+      <c r="Z271">
+        <v>0</v>
+      </c>
+      <c r="AA271">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="8:27" x14ac:dyDescent="0.3">
+      <c r="H272">
         <v>0.17</v>
       </c>
-      <c r="I271" s="53">
+      <c r="I272" s="53">
         <f t="shared" si="10"/>
         <v>0.1542857142857143</v>
       </c>
-      <c r="T271">
-        <v>127</v>
-      </c>
-      <c r="U271" t="s">
+      <c r="T272">
+        <v>128</v>
+      </c>
+      <c r="U272" t="s">
         <v>129</v>
       </c>
-      <c r="V271">
-        <v>-1.0409999999999999</v>
-      </c>
-      <c r="W271">
-        <v>-0.17</v>
-      </c>
-      <c r="X271">
-        <v>0</v>
-      </c>
-      <c r="Y271">
-        <v>0</v>
-      </c>
-      <c r="Z271">
-        <v>0</v>
-      </c>
-      <c r="AA271">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272" spans="8:27" x14ac:dyDescent="0.3">
-      <c r="H272">
+      <c r="V272">
+        <v>-1.222</v>
+      </c>
+      <c r="W272">
+        <v>-0.42699999999999999</v>
+      </c>
+      <c r="X272">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="Y272">
+        <v>0</v>
+      </c>
+      <c r="Z272">
+        <v>0</v>
+      </c>
+      <c r="AA272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="8:27" x14ac:dyDescent="0.3">
+      <c r="H273">
         <v>0.18</v>
       </c>
-      <c r="I272" s="53">
+      <c r="I273" s="53">
         <f t="shared" si="10"/>
         <v>0.16000000000000003</v>
       </c>
-      <c r="T272">
-        <v>128</v>
-      </c>
-      <c r="U272" t="s">
+      <c r="T273">
+        <v>130</v>
+      </c>
+      <c r="U273" t="s">
         <v>129</v>
       </c>
-      <c r="V272">
-        <v>-1.222</v>
-      </c>
-      <c r="W272">
-        <v>-0.42699999999999999</v>
-      </c>
-      <c r="X272">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="Y272">
-        <v>0</v>
-      </c>
-      <c r="Z272">
-        <v>0</v>
-      </c>
-      <c r="AA272">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273" spans="8:27" x14ac:dyDescent="0.3">
-      <c r="H273">
+      <c r="V273">
+        <v>-1.3320000000000001</v>
+      </c>
+      <c r="W273">
+        <v>-0.66300000000000003</v>
+      </c>
+      <c r="X273">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="Y273">
+        <v>0</v>
+      </c>
+      <c r="Z273">
+        <v>0</v>
+      </c>
+      <c r="AA273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="8:27" x14ac:dyDescent="0.3">
+      <c r="H274">
         <v>0.19</v>
       </c>
-      <c r="I273" s="53">
+      <c r="I274" s="53">
         <f t="shared" si="10"/>
         <v>0.16571428571428576</v>
       </c>
-      <c r="T273">
-        <v>130</v>
-      </c>
-      <c r="U273" t="s">
-        <v>129</v>
-      </c>
-      <c r="V273">
-        <v>-1.3320000000000001</v>
-      </c>
-      <c r="W273">
-        <v>-0.66300000000000003</v>
-      </c>
-      <c r="X273">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="Y273">
-        <v>0</v>
-      </c>
-      <c r="Z273">
-        <v>0</v>
-      </c>
-      <c r="AA273">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274" spans="8:27" x14ac:dyDescent="0.3">
-      <c r="H274">
-        <v>0.2</v>
-      </c>
-      <c r="I274" s="53">
-        <f t="shared" si="10"/>
-        <v>0.17142857142857146</v>
-      </c>
       <c r="T274">
         <v>131</v>
       </c>
@@ -11273,7 +11303,7 @@
     </row>
     <row r="275" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H275">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="I275" s="53">
         <f t="shared" si="10"/>
@@ -11306,7 +11336,7 @@
     </row>
     <row r="276" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H276">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="I276" s="53">
         <f t="shared" si="10"/>
@@ -11339,7 +11369,7 @@
     </row>
     <row r="277" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H277">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="I277" s="53">
         <f t="shared" si="10"/>
@@ -11372,18 +11402,12 @@
     </row>
     <row r="278" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H278">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="I278" s="53">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
-      <c r="K278">
-        <v>0.5</v>
-      </c>
-      <c r="L278">
-        <v>0</v>
-      </c>
       <c r="T278">
         <v>136</v>
       </c>
@@ -11411,7 +11435,7 @@
     </row>
     <row r="279" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H279">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="I279" s="53">
         <f t="shared" si="10"/>
@@ -11421,7 +11445,7 @@
         <v>0.5</v>
       </c>
       <c r="L279">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="T279">
         <v>137</v>
@@ -11450,12 +11474,18 @@
     </row>
     <row r="280" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H280">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="I280" s="53">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
+      <c r="K280">
+        <v>0.5</v>
+      </c>
+      <c r="L280">
+        <v>0.33</v>
+      </c>
       <c r="T280">
         <v>138</v>
       </c>
@@ -11483,18 +11513,12 @@
     </row>
     <row r="281" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H281">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="I281" s="53">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
-      <c r="K281">
-        <v>0.71</v>
-      </c>
-      <c r="L281">
-        <v>0</v>
-      </c>
       <c r="T281">
         <v>140</v>
       </c>
@@ -11522,7 +11546,7 @@
     </row>
     <row r="282" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H282">
-        <v>0.28000000000000003</v>
+        <v>0.27</v>
       </c>
       <c r="I282" s="53">
         <f t="shared" si="10"/>
@@ -11532,17 +11556,23 @@
         <v>0.71</v>
       </c>
       <c r="L282">
-        <v>0.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H283">
-        <v>0.28999999999999998</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I283" s="53">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
+      <c r="K283">
+        <v>0.71</v>
+      </c>
+      <c r="L283">
+        <v>0.26</v>
+      </c>
       <c r="V283">
         <f>SUM(V190:V281)</f>
         <v>-96.689999999999955</v>
@@ -11550,22 +11580,16 @@
     </row>
     <row r="284" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H284">
-        <v>0.3</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I284" s="53">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
-      <c r="K284">
-        <v>0.94</v>
-      </c>
-      <c r="L284">
-        <v>0</v>
-      </c>
     </row>
     <row r="285" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H285">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="I285" s="53">
         <f t="shared" si="10"/>
@@ -11575,21 +11599,27 @@
         <v>0.94</v>
       </c>
       <c r="L285">
-        <v>0.217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H286">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="I286" s="53">
         <f t="shared" si="10"/>
         <v>0.17142857142857146</v>
       </c>
+      <c r="K286">
+        <v>0.94</v>
+      </c>
+      <c r="L286">
+        <v>0.217</v>
+      </c>
     </row>
     <row r="287" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H287">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="I287" s="53">
         <f t="shared" si="10"/>
@@ -11598,7 +11628,7 @@
     </row>
     <row r="288" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H288">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="I288" s="53">
         <f t="shared" si="10"/>
@@ -11607,7 +11637,7 @@
     </row>
     <row r="289" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H289">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="I289" s="53">
         <f t="shared" si="10"/>
@@ -11616,7 +11646,7 @@
     </row>
     <row r="290" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H290">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="I290" s="53">
         <f t="shared" si="10"/>
@@ -11625,7 +11655,7 @@
     </row>
     <row r="291" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H291">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="I291" s="53">
         <f t="shared" si="10"/>
@@ -11634,7 +11664,7 @@
     </row>
     <row r="292" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H292">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="I292" s="53">
         <f t="shared" si="10"/>
@@ -11643,7 +11673,7 @@
     </row>
     <row r="293" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H293">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="I293" s="53">
         <f t="shared" si="10"/>
@@ -11652,7 +11682,7 @@
     </row>
     <row r="294" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H294">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="I294" s="53">
         <f t="shared" si="10"/>
@@ -11661,7 +11691,7 @@
     </row>
     <row r="295" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H295">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="I295" s="53">
         <f t="shared" si="10"/>
@@ -11670,7 +11700,7 @@
     </row>
     <row r="296" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H296">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="I296" s="53">
         <f t="shared" si="10"/>
@@ -11679,7 +11709,7 @@
     </row>
     <row r="297" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H297">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="I297" s="53">
         <f t="shared" si="10"/>
@@ -11688,7 +11718,7 @@
     </row>
     <row r="298" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H298">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="I298" s="53">
         <f t="shared" si="10"/>
@@ -11697,7 +11727,7 @@
     </row>
     <row r="299" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H299">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I299" s="53">
         <f t="shared" si="10"/>
@@ -11706,7 +11736,7 @@
     </row>
     <row r="300" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H300">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="I300" s="53">
         <f t="shared" si="10"/>
@@ -11715,7 +11745,7 @@
     </row>
     <row r="301" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H301">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="I301" s="53">
         <f t="shared" si="10"/>
@@ -11724,7 +11754,7 @@
     </row>
     <row r="302" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H302">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="I302" s="53">
         <f t="shared" si="10"/>
@@ -11733,7 +11763,7 @@
     </row>
     <row r="303" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H303">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="I303" s="53">
         <f t="shared" si="10"/>
@@ -11742,7 +11772,7 @@
     </row>
     <row r="304" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H304">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="I304" s="53">
         <f t="shared" si="10"/>
@@ -11751,7 +11781,7 @@
     </row>
     <row r="305" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H305">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="I305" s="53">
         <f t="shared" si="10"/>
@@ -11760,7 +11790,7 @@
     </row>
     <row r="306" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H306">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="I306" s="53">
         <f t="shared" si="10"/>
@@ -11769,7 +11799,7 @@
     </row>
     <row r="307" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H307">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="I307" s="53">
         <f t="shared" si="10"/>
@@ -11778,7 +11808,7 @@
     </row>
     <row r="308" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H308">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="I308" s="53">
         <f t="shared" si="10"/>
@@ -11787,7 +11817,7 @@
     </row>
     <row r="309" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H309">
-        <v>0.55000000000000004</v>
+        <v>0.54</v>
       </c>
       <c r="I309" s="53">
         <f t="shared" si="10"/>
@@ -11796,7 +11826,7 @@
     </row>
     <row r="310" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H310">
-        <v>0.56000000000000005</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="I310" s="53">
         <f t="shared" si="10"/>
@@ -11805,7 +11835,7 @@
     </row>
     <row r="311" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H311">
-        <v>0.56999999999999995</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I311" s="53">
         <f t="shared" si="10"/>
@@ -11814,7 +11844,7 @@
     </row>
     <row r="312" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H312">
-        <v>0.57999999999999996</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I312" s="53">
         <f t="shared" si="10"/>
@@ -11823,7 +11853,7 @@
     </row>
     <row r="313" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H313">
-        <v>0.59</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I313" s="53">
         <f t="shared" si="10"/>
@@ -11832,7 +11862,7 @@
     </row>
     <row r="314" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H314">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="I314" s="53">
         <f t="shared" si="10"/>
@@ -11841,2160 +11871,2169 @@
     </row>
     <row r="315" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H315">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="I315" s="53">
         <f t="shared" si="10"/>
-        <v>0.16954987852001016</v>
+        <v>0.17142857142857146</v>
       </c>
     </row>
     <row r="316" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H316">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="I316" s="53">
         <f t="shared" si="10"/>
-        <v>0.1677218252289068</v>
-      </c>
-    </row>
-    <row r="317" spans="8:9" x14ac:dyDescent="0.3">
+        <v>0.16954987852001016</v>
+      </c>
+    </row>
+    <row r="317" spans="8:27" x14ac:dyDescent="0.3">
       <c r="H317">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="I317" s="53">
         <f t="shared" si="10"/>
-        <v>0.16594226233711895</v>
+        <v>0.1677218252289068</v>
       </c>
     </row>
     <row r="318" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H318">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="I318" s="53">
         <f t="shared" si="10"/>
-        <v>0.16420916408433284</v>
+        <v>0.16594226233711895</v>
       </c>
     </row>
     <row r="319" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H319">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="I319" s="53">
         <f t="shared" si="10"/>
-        <v>0.16252061928129335</v>
+        <v>0.16420916408433284</v>
       </c>
     </row>
     <row r="320" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H320">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="I320" s="53">
-        <f t="shared" ref="I320:I383" si="11">IF(H320&lt;$C$255/3,   ($C$256*$C$253/$C$257)*(1+(3*($C$254-1)*H320/$C$255)),   IF(H320&lt;=$C$255,   $C$256*$C$253*$C$254/$C$257,   $C$256*$C$253*$C$254/$C$257*($C$255/H320)^(2/3)   ))</f>
-        <v>0.16087482318800531</v>
+        <f t="shared" si="10"/>
+        <v>0.16252061928129335</v>
       </c>
     </row>
     <row r="321" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H321">
+        <v>0.66</v>
+      </c>
+      <c r="I321" s="53">
+        <f t="shared" ref="I321:I384" si="11">IF(H321&lt;$C$256/3,   ($C$257*$C$254/$C$258)*(1+(3*($C$255-1)*H321/$C$256)),   IF(H321&lt;=$C$256,   $C$257*$C$254*$C$255/$C$258,   $C$257*$C$254*$C$255/$C$258*($C$256/H321)^(2/3)   ))</f>
+        <v>0.16087482318800531</v>
+      </c>
+    </row>
+    <row r="322" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H322">
         <v>0.67</v>
       </c>
-      <c r="I321" s="53">
+      <c r="I322" s="53">
         <f t="shared" si="11"/>
         <v>0.15927007008059582</v>
       </c>
     </row>
-    <row r="322" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H322">
+    <row r="323" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H323">
         <v>0.68</v>
       </c>
-      <c r="I322" s="53">
+      <c r="I323" s="53">
         <f t="shared" si="11"/>
         <v>0.15770474643915294</v>
       </c>
     </row>
-    <row r="323" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H323">
+    <row r="324" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H324">
         <v>0.69</v>
       </c>
-      <c r="I323" s="53">
+      <c r="I324" s="53">
         <f t="shared" si="11"/>
         <v>0.15617732469639467</v>
       </c>
     </row>
-    <row r="324" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H324">
+    <row r="325" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H325">
         <v>0.7</v>
       </c>
-      <c r="I324" s="53">
+      <c r="I325" s="53">
         <f t="shared" si="11"/>
         <v>0.15468635749362564</v>
       </c>
     </row>
-    <row r="325" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H325">
+    <row r="326" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H326">
         <v>0.71</v>
       </c>
-      <c r="I325" s="53">
+      <c r="I326" s="53">
         <f t="shared" si="11"/>
         <v>0.15323047239623552</v>
       </c>
     </row>
-    <row r="326" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H326">
+    <row r="327" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H327">
         <v>0.72</v>
       </c>
-      <c r="I326" s="53">
+      <c r="I327" s="53">
         <f t="shared" si="11"/>
         <v>0.15180836702608733</v>
       </c>
     </row>
-    <row r="327" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H327">
+    <row r="328" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H328">
         <v>0.73</v>
       </c>
-      <c r="I327" s="53">
+      <c r="I328" s="53">
         <f t="shared" si="11"/>
         <v>0.15041880457263548</v>
       </c>
     </row>
-    <row r="328" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H328">
+    <row r="329" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H329">
         <v>0.74</v>
       </c>
-      <c r="I328" s="53">
+      <c r="I329" s="53">
         <f t="shared" si="11"/>
         <v>0.14906060964857532</v>
       </c>
     </row>
-    <row r="329" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H329">
+    <row r="330" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H330">
         <v>0.75</v>
       </c>
-      <c r="I329" s="53">
+      <c r="I330" s="53">
         <f t="shared" si="11"/>
         <v>0.1477326644593292</v>
       </c>
     </row>
-    <row r="330" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H330">
+    <row r="331" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H331">
         <v>0.76</v>
       </c>
-      <c r="I330" s="53">
+      <c r="I331" s="53">
         <f t="shared" si="11"/>
         <v>0.14643390525877864</v>
       </c>
     </row>
-    <row r="331" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H331">
+    <row r="332" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H332">
         <v>0.77</v>
       </c>
-      <c r="I331" s="53">
+      <c r="I332" s="53">
         <f t="shared" si="11"/>
         <v>0.14516331906640431</v>
       </c>
     </row>
-    <row r="332" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H332">
+    <row r="333" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H333">
         <v>0.78</v>
       </c>
-      <c r="I332" s="53">
+      <c r="I333" s="53">
         <f t="shared" si="11"/>
         <v>0.14391994062344254</v>
       </c>
     </row>
-    <row r="333" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H333">
+    <row r="334" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H334">
         <v>0.79</v>
       </c>
-      <c r="I333" s="53">
+      <c r="I334" s="53">
         <f t="shared" si="11"/>
         <v>0.1427028495678451</v>
       </c>
     </row>
-    <row r="334" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H334">
+    <row r="335" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H335">
         <v>0.8</v>
       </c>
-      <c r="I334" s="53">
+      <c r="I335" s="53">
         <f t="shared" si="11"/>
         <v>0.14151116780976972</v>
       </c>
     </row>
-    <row r="335" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H335">
+    <row r="336" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H336">
         <v>0.81</v>
       </c>
-      <c r="I335" s="53">
+      <c r="I336" s="53">
         <f t="shared" si="11"/>
         <v>0.14034405709106237</v>
       </c>
     </row>
-    <row r="336" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H336">
+    <row r="337" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H337">
         <v>0.82</v>
       </c>
-      <c r="I336" s="53">
+      <c r="I337" s="53">
         <f t="shared" si="11"/>
         <v>0.13920071671374129</v>
       </c>
     </row>
-    <row r="337" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H337">
+    <row r="338" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H338">
         <v>0.83</v>
       </c>
-      <c r="I337" s="53">
+      <c r="I338" s="53">
         <f t="shared" si="11"/>
         <v>0.13808038142388113</v>
       </c>
     </row>
-    <row r="338" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H338">
+    <row r="339" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H339">
         <v>0.84</v>
       </c>
-      <c r="I338" s="53">
+      <c r="I339" s="53">
         <f t="shared" si="11"/>
         <v>0.13698231943853842</v>
       </c>
     </row>
-    <row r="339" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H339">
+    <row r="340" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H340">
         <v>0.85</v>
       </c>
-      <c r="I339" s="53">
+      <c r="I340" s="53">
         <f t="shared" si="11"/>
         <v>0.13590583060447733</v>
       </c>
     </row>
-    <row r="340" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H340">
+    <row r="341" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H341">
         <v>0.86</v>
       </c>
-      <c r="I340" s="53">
+      <c r="I341" s="53">
         <f t="shared" si="11"/>
         <v>0.13485024467845858</v>
       </c>
     </row>
-    <row r="341" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H341">
+    <row r="342" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H342">
         <v>0.87</v>
       </c>
-      <c r="I341" s="53">
+      <c r="I342" s="53">
         <f t="shared" si="11"/>
         <v>0.13381491971975773</v>
       </c>
     </row>
-    <row r="342" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H342">
+    <row r="343" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H343">
         <v>0.88</v>
       </c>
-      <c r="I342" s="53">
+      <c r="I343" s="53">
         <f t="shared" si="11"/>
         <v>0.13279924058639495</v>
       </c>
     </row>
-    <row r="343" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H343">
+    <row r="344" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H344">
         <v>0.89</v>
       </c>
-      <c r="I343" s="53">
+      <c r="I344" s="53">
         <f t="shared" si="11"/>
         <v>0.131802617527292</v>
       </c>
     </row>
-    <row r="344" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H344">
+    <row r="345" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H345">
         <v>0.9</v>
       </c>
-      <c r="I344" s="53">
+      <c r="I345" s="53">
         <f t="shared" si="11"/>
         <v>0.13082448486323794</v>
       </c>
     </row>
-    <row r="345" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H345">
+    <row r="346" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H346">
         <v>0.91</v>
       </c>
-      <c r="I345" s="53">
+      <c r="I346" s="53">
         <f t="shared" si="11"/>
         <v>0.12986429975014538</v>
       </c>
     </row>
-    <row r="346" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H346">
+    <row r="347" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H347">
         <v>0.92</v>
       </c>
-      <c r="I346" s="53">
+      <c r="I347" s="53">
         <f t="shared" si="11"/>
         <v>0.1289215410186223</v>
       </c>
     </row>
-    <row r="347" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H347">
+    <row r="348" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H348">
         <v>0.93</v>
       </c>
-      <c r="I347" s="53">
+      <c r="I348" s="53">
         <f t="shared" si="11"/>
         <v>0.12799570808438024</v>
       </c>
     </row>
-    <row r="348" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H348">
+    <row r="349" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H349">
         <v>0.94</v>
       </c>
-      <c r="I348" s="53">
+      <c r="I349" s="53">
         <f t="shared" si="11"/>
         <v>0.12708631992444461</v>
       </c>
     </row>
-    <row r="349" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H349">
+    <row r="350" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H350">
         <v>0.95</v>
       </c>
-      <c r="I349" s="53">
+      <c r="I350" s="53">
         <f t="shared" si="11"/>
         <v>0.126192914114542</v>
       </c>
     </row>
-    <row r="350" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H350">
+    <row r="351" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H351">
         <v>0.96</v>
       </c>
-      <c r="I350" s="53">
+      <c r="I351" s="53">
         <f t="shared" si="11"/>
         <v>0.12531504592340856</v>
       </c>
     </row>
-    <row r="351" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H351">
+    <row r="352" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H352">
         <v>0.97</v>
       </c>
-      <c r="I351" s="53">
+      <c r="I352" s="53">
         <f t="shared" si="11"/>
         <v>0.12445228746010001</v>
       </c>
     </row>
-    <row r="352" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H352">
+    <row r="353" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H353">
         <v>0.98</v>
       </c>
-      <c r="I352" s="53">
+      <c r="I353" s="53">
         <f t="shared" si="11"/>
         <v>0.123604226870692</v>
       </c>
     </row>
-    <row r="353" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H353">
+    <row r="354" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H354">
         <v>0.99</v>
       </c>
-      <c r="I353" s="53">
+      <c r="I354" s="53">
         <f t="shared" si="11"/>
         <v>0.12277046758103911</v>
       </c>
     </row>
-    <row r="354" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H354">
+    <row r="355" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H355">
         <v>1</v>
       </c>
-      <c r="I354" s="53">
+      <c r="I355" s="53">
         <f t="shared" si="11"/>
         <v>0.12195062758251644</v>
       </c>
     </row>
-    <row r="355" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H355">
+    <row r="356" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H356">
         <v>1.01</v>
       </c>
-      <c r="I355" s="53">
+      <c r="I356" s="53">
         <f t="shared" si="11"/>
         <v>0.12114433875790227</v>
       </c>
     </row>
-    <row r="356" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H356">
+    <row r="357" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H357">
         <v>1.02</v>
       </c>
-      <c r="I356" s="53">
+      <c r="I357" s="53">
         <f t="shared" si="11"/>
         <v>0.1203512462447735</v>
       </c>
     </row>
-    <row r="357" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H357">
+    <row r="358" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H358">
         <v>1.03</v>
       </c>
-      <c r="I357" s="53">
+      <c r="I358" s="53">
         <f t="shared" si="11"/>
         <v>0.11957100783398215</v>
       </c>
     </row>
-    <row r="358" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H358">
+    <row r="359" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H359">
         <v>1.04</v>
       </c>
-      <c r="I358" s="53">
+      <c r="I359" s="53">
         <f t="shared" si="11"/>
         <v>0.11880329340096042</v>
       </c>
     </row>
-    <row r="359" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H359">
+    <row r="360" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H360">
         <v>1.05</v>
       </c>
-      <c r="I359" s="53">
+      <c r="I360" s="53">
         <f t="shared" si="11"/>
         <v>0.11804778436776639</v>
       </c>
     </row>
-    <row r="360" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H360">
+    <row r="361" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H361">
         <v>1.06</v>
       </c>
-      <c r="I360" s="53">
+      <c r="I361" s="53">
         <f t="shared" si="11"/>
         <v>0.11730417319393414</v>
       </c>
     </row>
-    <row r="361" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H361">
+    <row r="362" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H362">
         <v>1.07</v>
       </c>
-      <c r="I361" s="53">
+      <c r="I362" s="53">
         <f t="shared" si="11"/>
         <v>0.11657216289433078</v>
       </c>
     </row>
-    <row r="362" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H362">
+    <row r="363" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H363">
         <v>1.08</v>
       </c>
-      <c r="I362" s="53">
+      <c r="I363" s="53">
         <f t="shared" si="11"/>
         <v>0.1158514665823505</v>
       </c>
     </row>
-    <row r="363" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H363">
+    <row r="364" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H364">
         <v>1.0900000000000001</v>
       </c>
-      <c r="I363" s="53">
+      <c r="I364" s="53">
         <f t="shared" si="11"/>
         <v>0.11514180703689374</v>
       </c>
     </row>
-    <row r="364" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H364">
+    <row r="365" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H365">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I364" s="53">
+      <c r="I365" s="53">
         <f t="shared" si="11"/>
         <v>0.11444291629168775</v>
       </c>
     </row>
-    <row r="365" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H365">
+    <row r="366" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H366">
         <v>1.1100000000000001</v>
       </c>
-      <c r="I365" s="53">
+      <c r="I366" s="53">
         <f t="shared" si="11"/>
         <v>0.1137545352456045</v>
       </c>
     </row>
-    <row r="366" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H366">
+    <row r="367" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H367">
         <v>1.1200000000000001</v>
       </c>
-      <c r="I366" s="53">
+      <c r="I367" s="53">
         <f t="shared" si="11"/>
         <v>0.11307641329272453</v>
       </c>
     </row>
-    <row r="367" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H367">
+    <row r="368" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H368">
         <v>1.1299999999999999</v>
       </c>
-      <c r="I367" s="53">
+      <c r="I368" s="53">
         <f t="shared" si="11"/>
         <v>0.11240830797097949</v>
       </c>
     </row>
-    <row r="368" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H368">
+    <row r="369" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H369">
         <v>1.1399999999999999</v>
       </c>
-      <c r="I368" s="53">
+      <c r="I369" s="53">
         <f t="shared" si="11"/>
         <v>0.11174998462828611</v>
       </c>
     </row>
-    <row r="369" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H369">
+    <row r="370" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H370">
         <v>1.1499999999999999</v>
       </c>
-      <c r="I369" s="53">
+      <c r="I370" s="53">
         <f t="shared" si="11"/>
         <v>0.11110121610515532</v>
       </c>
     </row>
-    <row r="370" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H370">
+    <row r="371" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H371">
         <v>1.1599999999999999</v>
       </c>
-      <c r="I370" s="53">
+      <c r="I371" s="53">
         <f t="shared" si="11"/>
         <v>0.11046178243282875</v>
       </c>
     </row>
-    <row r="371" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H371">
+    <row r="372" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H372">
         <v>1.17</v>
       </c>
-      <c r="I371" s="53">
+      <c r="I372" s="53">
         <f t="shared" si="11"/>
         <v>0.10983147054605637</v>
       </c>
     </row>
-    <row r="372" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H372">
+    <row r="373" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H373">
         <v>1.18</v>
       </c>
-      <c r="I372" s="53">
+      <c r="I373" s="53">
         <f t="shared" si="11"/>
         <v>0.10921007400968709</v>
       </c>
     </row>
-    <row r="373" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H373">
+    <row r="374" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H374">
         <v>1.19</v>
       </c>
-      <c r="I373" s="53">
+      <c r="I374" s="53">
         <f t="shared" si="11"/>
         <v>0.10859739275829733</v>
       </c>
     </row>
-    <row r="374" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H374">
+    <row r="375" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H375">
         <v>1.2</v>
       </c>
-      <c r="I374" s="53">
+      <c r="I375" s="53">
         <f t="shared" si="11"/>
         <v>0.107993232848132</v>
       </c>
     </row>
-    <row r="375" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H375">
+    <row r="376" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H376">
         <v>1.21</v>
       </c>
-      <c r="I375" s="53">
+      <c r="I376" s="53">
         <f t="shared" si="11"/>
         <v>0.10739740622067891</v>
       </c>
     </row>
-    <row r="376" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H376">
+    <row r="377" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H377">
         <v>1.22</v>
       </c>
-      <c r="I376" s="53">
+      <c r="I377" s="53">
         <f t="shared" si="11"/>
         <v>0.10680973047723971</v>
       </c>
     </row>
-    <row r="377" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H377">
+    <row r="378" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H378">
         <v>1.23</v>
       </c>
-      <c r="I377" s="53">
+      <c r="I378" s="53">
         <f t="shared" si="11"/>
         <v>0.10623002866390084</v>
       </c>
     </row>
-    <row r="378" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H378">
+    <row r="379" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H379">
         <v>1.24</v>
       </c>
-      <c r="I378" s="53">
+      <c r="I379" s="53">
         <f t="shared" si="11"/>
         <v>0.10565812906634435</v>
       </c>
     </row>
-    <row r="379" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H379">
+    <row r="380" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H380">
         <v>1.25</v>
       </c>
-      <c r="I379" s="53">
+      <c r="I380" s="53">
         <f t="shared" si="11"/>
         <v>0.10509386501397301</v>
       </c>
     </row>
-    <row r="380" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H380">
+    <row r="381" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H381">
         <v>1.26</v>
       </c>
-      <c r="I380" s="53">
+      <c r="I381" s="53">
         <f t="shared" si="11"/>
         <v>0.1045370746928567</v>
       </c>
     </row>
-    <row r="381" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H381">
+    <row r="382" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H382">
         <v>1.27</v>
       </c>
-      <c r="I381" s="53">
+      <c r="I382" s="53">
         <f t="shared" si="11"/>
         <v>0.10398760096703577</v>
       </c>
     </row>
-    <row r="382" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H382">
+    <row r="383" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H383">
         <v>1.28</v>
       </c>
-      <c r="I382" s="53">
+      <c r="I383" s="53">
         <f t="shared" si="11"/>
         <v>0.10344529120774607</v>
       </c>
     </row>
-    <row r="383" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H383">
+    <row r="384" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H384">
         <v>1.29</v>
       </c>
-      <c r="I383" s="53">
+      <c r="I384" s="53">
         <f t="shared" si="11"/>
         <v>0.10290999713015545</v>
       </c>
     </row>
-    <row r="384" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H384">
-        <v>1.3</v>
-      </c>
-      <c r="I384" s="53">
-        <f t="shared" ref="I384:I447" si="12">IF(H384&lt;$C$255/3,   ($C$256*$C$253/$C$257)*(1+(3*($C$254-1)*H384/$C$255)),   IF(H384&lt;=$C$255,   $C$256*$C$253*$C$254/$C$257,   $C$256*$C$253*$C$254/$C$257*($C$255/H384)^(2/3)   ))</f>
-        <v>0.10238157463722605</v>
-      </c>
-    </row>
     <row r="385" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H385">
+        <v>1.3</v>
+      </c>
+      <c r="I385" s="53">
+        <f t="shared" ref="I385:I448" si="12">IF(H385&lt;$C$256/3,   ($C$257*$C$254/$C$258)*(1+(3*($C$255-1)*H385/$C$256)),   IF(H385&lt;=$C$256,   $C$257*$C$254*$C$255/$C$258,   $C$257*$C$254*$C$255/$C$258*($C$256/H385)^(2/3)   ))</f>
+        <v>0.10238157463722605</v>
+      </c>
+    </row>
+    <row r="386" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H386">
         <v>1.31</v>
       </c>
-      <c r="I385" s="53">
+      <c r="I386" s="53">
         <f t="shared" si="12"/>
         <v>0.10185988367033932</v>
       </c>
     </row>
-    <row r="386" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H386">
+    <row r="387" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H387">
         <v>1.32</v>
       </c>
-      <c r="I386" s="53">
+      <c r="I387" s="53">
         <f t="shared" si="12"/>
         <v>0.10134478806634185</v>
       </c>
     </row>
-    <row r="387" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H387">
+    <row r="388" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H388">
         <v>1.33</v>
       </c>
-      <c r="I387" s="53">
+      <c r="I388" s="53">
         <f t="shared" si="12"/>
         <v>0.10083615542068967</v>
       </c>
     </row>
-    <row r="388" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H388">
+    <row r="389" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H389">
         <v>1.34</v>
       </c>
-      <c r="I388" s="53">
+      <c r="I389" s="53">
         <f t="shared" si="12"/>
         <v>0.10033385695638715</v>
       </c>
     </row>
-    <row r="389" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H389">
+    <row r="390" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H390">
         <v>1.35</v>
       </c>
-      <c r="I389" s="53">
+      <c r="I390" s="53">
         <f t="shared" si="12"/>
         <v>9.9837767398434168E-2</v>
       </c>
     </row>
-    <row r="390" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H390">
+    <row r="391" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H391">
         <v>1.36</v>
       </c>
-      <c r="I390" s="53">
+      <c r="I391" s="53">
         <f t="shared" si="12"/>
         <v>9.934776485351117E-2</v>
       </c>
     </row>
-    <row r="391" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H391">
+    <row r="392" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H392">
         <v>1.37</v>
       </c>
-      <c r="I391" s="53">
+      <c r="I392" s="53">
         <f t="shared" si="12"/>
         <v>9.8863730694646768E-2</v>
       </c>
     </row>
-    <row r="392" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H392">
+    <row r="393" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H393">
         <v>1.38</v>
       </c>
-      <c r="I392" s="53">
+      <c r="I393" s="53">
         <f t="shared" si="12"/>
         <v>9.8385549450627038E-2</v>
       </c>
     </row>
-    <row r="393" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H393">
+    <row r="394" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H394">
         <v>1.39</v>
       </c>
-      <c r="I393" s="53">
+      <c r="I394" s="53">
         <f t="shared" si="12"/>
         <v>9.7913108699918719E-2</v>
       </c>
     </row>
-    <row r="394" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H394">
+    <row r="395" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H395">
         <v>1.4</v>
       </c>
-      <c r="I394" s="53">
+      <c r="I395" s="53">
         <f t="shared" si="12"/>
         <v>9.7446298968891246E-2</v>
       </c>
     </row>
-    <row r="395" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H395">
+    <row r="396" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H396">
         <v>1.41</v>
       </c>
-      <c r="I395" s="53">
+      <c r="I396" s="53">
         <f t="shared" si="12"/>
         <v>9.6985013634134004E-2</v>
       </c>
     </row>
-    <row r="396" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H396">
+    <row r="397" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H397">
         <v>1.42</v>
       </c>
-      <c r="I396" s="53">
+      <c r="I397" s="53">
         <f t="shared" si="12"/>
         <v>9.6529148828676206E-2</v>
       </c>
     </row>
-    <row r="397" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H397">
+    <row r="398" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H398">
         <v>1.43</v>
       </c>
-      <c r="I397" s="53">
+      <c r="I398" s="53">
         <f t="shared" si="12"/>
         <v>9.6078603351927624E-2</v>
       </c>
     </row>
-    <row r="398" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H398">
+    <row r="399" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H399">
         <v>1.44</v>
       </c>
-      <c r="I398" s="53">
+      <c r="I399" s="53">
         <f t="shared" si="12"/>
         <v>9.56332785831671E-2</v>
       </c>
     </row>
-    <row r="399" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H399">
+    <row r="400" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H400">
         <v>1.45</v>
       </c>
-      <c r="I399" s="53">
+      <c r="I400" s="53">
         <f t="shared" si="12"/>
         <v>9.5193078398416328E-2</v>
       </c>
     </row>
-    <row r="400" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H400">
+    <row r="401" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H401">
         <v>1.46</v>
       </c>
-      <c r="I400" s="53">
+      <c r="I401" s="53">
         <f t="shared" si="12"/>
         <v>9.4757909090543324E-2</v>
       </c>
     </row>
-    <row r="401" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H401">
+    <row r="402" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H402">
         <v>1.47</v>
       </c>
-      <c r="I401" s="53">
+      <c r="I402" s="53">
         <f t="shared" si="12"/>
         <v>9.432767929244959E-2</v>
       </c>
     </row>
-    <row r="402" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H402">
+    <row r="403" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H403">
         <v>1.48</v>
       </c>
-      <c r="I402" s="53">
+      <c r="I403" s="53">
         <f t="shared" si="12"/>
         <v>9.3902299903201439E-2</v>
       </c>
     </row>
-    <row r="403" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H403">
+    <row r="404" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H404">
         <v>1.49</v>
       </c>
-      <c r="I403" s="53">
+      <c r="I404" s="53">
         <f t="shared" si="12"/>
         <v>9.3481684016974015E-2</v>
       </c>
     </row>
-    <row r="404" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H404">
+    <row r="405" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H405">
         <v>1.5</v>
       </c>
-      <c r="I404" s="53">
+      <c r="I405" s="53">
         <f t="shared" si="12"/>
         <v>9.3065746854682524E-2</v>
       </c>
     </row>
-    <row r="405" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H405">
+    <row r="406" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H406">
         <v>1.51</v>
       </c>
-      <c r="I405" s="53">
+      <c r="I406" s="53">
         <f t="shared" si="12"/>
         <v>9.2654405698182091E-2</v>
       </c>
     </row>
-    <row r="406" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H406">
+    <row r="407" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H407">
         <v>1.52</v>
       </c>
-      <c r="I406" s="53">
+      <c r="I407" s="53">
         <f t="shared" si="12"/>
         <v>9.2247579826923401E-2</v>
       </c>
     </row>
-    <row r="407" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H407">
+    <row r="408" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H408">
         <v>1.53</v>
       </c>
-      <c r="I407" s="53">
+      <c r="I408" s="53">
         <f t="shared" si="12"/>
         <v>9.1845190456956952E-2</v>
       </c>
     </row>
-    <row r="408" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H408">
+    <row r="409" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H409">
         <v>1.54</v>
       </c>
-      <c r="I408" s="53">
+      <c r="I409" s="53">
         <f t="shared" si="12"/>
         <v>9.1447160682184309E-2</v>
       </c>
     </row>
-    <row r="409" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H409">
+    <row r="410" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H410">
         <v>1.55</v>
       </c>
-      <c r="I409" s="53">
+      <c r="I410" s="53">
         <f t="shared" si="12"/>
         <v>9.105341541775934E-2</v>
       </c>
     </row>
-    <row r="410" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H410">
+    <row r="411" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H411">
         <v>1.56</v>
       </c>
-      <c r="I410" s="53">
+      <c r="I411" s="53">
         <f t="shared" si="12"/>
         <v>9.0663881345547773E-2</v>
       </c>
     </row>
-    <row r="411" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H411">
+    <row r="412" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H412">
         <v>1.57</v>
       </c>
-      <c r="I411" s="53">
+      <c r="I412" s="53">
         <f t="shared" si="12"/>
         <v>9.0278486861557219E-2</v>
       </c>
     </row>
-    <row r="412" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H412">
+    <row r="413" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H413">
         <v>1.58</v>
       </c>
-      <c r="I412" s="53">
+      <c r="I413" s="53">
         <f t="shared" si="12"/>
         <v>8.9897162025254787E-2</v>
       </c>
     </row>
-    <row r="413" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H413">
+    <row r="414" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H414">
         <v>1.59</v>
       </c>
-      <c r="I413" s="53">
+      <c r="I414" s="53">
         <f t="shared" si="12"/>
         <v>8.9519838510692798E-2</v>
       </c>
     </row>
-    <row r="414" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H414">
+    <row r="415" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H415">
         <v>1.6</v>
       </c>
-      <c r="I414" s="53">
+      <c r="I415" s="53">
         <f t="shared" si="12"/>
         <v>8.9146449559367333E-2</v>
       </c>
     </row>
-    <row r="415" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H415">
+    <row r="416" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H416">
         <v>1.61</v>
       </c>
-      <c r="I415" s="53">
+      <c r="I416" s="53">
         <f t="shared" si="12"/>
         <v>8.8776929934737764E-2</v>
       </c>
     </row>
-    <row r="416" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H416">
+    <row r="417" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H417">
         <v>1.62</v>
       </c>
-      <c r="I416" s="53">
+      <c r="I417" s="53">
         <f t="shared" si="12"/>
         <v>8.8411215878338653E-2</v>
       </c>
     </row>
-    <row r="417" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H417">
+    <row r="418" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H418">
         <v>1.63</v>
       </c>
-      <c r="I417" s="53">
+      <c r="I418" s="53">
         <f t="shared" si="12"/>
         <v>8.8049245067419249E-2</v>
       </c>
     </row>
-    <row r="418" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H418">
+    <row r="419" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H419">
         <v>1.64</v>
       </c>
-      <c r="I418" s="53">
+      <c r="I419" s="53">
         <f t="shared" si="12"/>
         <v>8.7690956574047879E-2</v>
       </c>
     </row>
-    <row r="419" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H419">
+    <row r="420" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H420">
         <v>1.65</v>
       </c>
-      <c r="I419" s="53">
+      <c r="I420" s="53">
         <f t="shared" si="12"/>
         <v>8.7336290825622484E-2</v>
       </c>
     </row>
-    <row r="420" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H420">
+    <row r="421" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H421">
         <v>1.66</v>
       </c>
-      <c r="I420" s="53">
+      <c r="I421" s="53">
         <f t="shared" si="12"/>
         <v>8.6985189566730431E-2</v>
       </c>
     </row>
-    <row r="421" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H421">
+    <row r="422" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H422">
         <v>1.67</v>
       </c>
-      <c r="I421" s="53">
+      <c r="I422" s="53">
         <f t="shared" si="12"/>
         <v>8.6637595822303889E-2</v>
       </c>
     </row>
-    <row r="422" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H422">
+    <row r="423" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H423">
         <v>1.68</v>
       </c>
-      <c r="I422" s="53">
+      <c r="I423" s="53">
         <f t="shared" si="12"/>
         <v>8.6293453862019115E-2</v>
       </c>
     </row>
-    <row r="423" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H423">
+    <row r="424" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H424">
         <v>1.69</v>
       </c>
-      <c r="I423" s="53">
+      <c r="I424" s="53">
         <f t="shared" si="12"/>
         <v>8.5952709165890706E-2</v>
       </c>
     </row>
-    <row r="424" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H424">
+    <row r="425" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H425">
         <v>1.7</v>
       </c>
-      <c r="I424" s="53">
+      <c r="I425" s="53">
         <f t="shared" si="12"/>
         <v>8.5615308391013945E-2</v>
       </c>
     </row>
-    <row r="425" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H425">
+    <row r="426" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H426">
         <v>1.71</v>
       </c>
-      <c r="I425" s="53">
+      <c r="I426" s="53">
         <f t="shared" si="12"/>
         <v>8.5281199339410016E-2</v>
       </c>
     </row>
-    <row r="426" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H426">
+    <row r="427" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H427">
         <v>1.72</v>
       </c>
-      <c r="I426" s="53">
+      <c r="I427" s="53">
         <f t="shared" si="12"/>
         <v>8.4950330926932036E-2</v>
       </c>
     </row>
-    <row r="427" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H427">
+    <row r="428" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H428">
         <v>1.73</v>
       </c>
-      <c r="I427" s="53">
+      <c r="I428" s="53">
         <f t="shared" si="12"/>
         <v>8.462265315319023E-2</v>
       </c>
     </row>
-    <row r="428" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H428">
+    <row r="429" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H429">
         <v>1.74</v>
       </c>
-      <c r="I428" s="53">
+      <c r="I429" s="53">
         <f t="shared" si="12"/>
         <v>8.4298117072457671E-2</v>
       </c>
     </row>
-    <row r="429" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H429">
+    <row r="430" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H430">
         <v>1.75</v>
       </c>
-      <c r="I429" s="53">
+      <c r="I430" s="53">
         <f t="shared" si="12"/>
         <v>8.3976674765518997E-2</v>
       </c>
     </row>
-    <row r="430" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H430">
+    <row r="431" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H431">
         <v>1.76</v>
       </c>
-      <c r="I430" s="53">
+      <c r="I431" s="53">
         <f t="shared" si="12"/>
         <v>8.3658279312426295E-2</v>
       </c>
     </row>
-    <row r="431" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H431">
+    <row r="432" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H432">
         <v>1.77</v>
       </c>
-      <c r="I431" s="53">
+      <c r="I432" s="53">
         <f t="shared" si="12"/>
         <v>8.3342884766128181E-2</v>
       </c>
     </row>
-    <row r="432" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H432">
+    <row r="433" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H433">
         <v>1.78</v>
       </c>
-      <c r="I432" s="53">
+      <c r="I433" s="53">
         <f t="shared" si="12"/>
         <v>8.3030446126939078E-2</v>
       </c>
     </row>
-    <row r="433" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H433">
+    <row r="434" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H434">
         <v>1.79</v>
       </c>
-      <c r="I433" s="53">
+      <c r="I434" s="53">
         <f t="shared" si="12"/>
         <v>8.2720919317817471E-2</v>
       </c>
     </row>
-    <row r="434" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H434">
+    <row r="435" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H435">
         <v>1.8</v>
       </c>
-      <c r="I434" s="53">
+      <c r="I435" s="53">
         <f t="shared" si="12"/>
         <v>8.2414261160423344E-2</v>
       </c>
     </row>
-    <row r="435" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H435">
+    <row r="436" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H436">
         <v>1.81</v>
       </c>
-      <c r="I435" s="53">
+      <c r="I436" s="53">
         <f t="shared" si="12"/>
         <v>8.2110429351925696E-2</v>
       </c>
     </row>
-    <row r="436" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H436">
+    <row r="437" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H437">
         <v>1.82</v>
       </c>
-      <c r="I436" s="53">
+      <c r="I437" s="53">
         <f t="shared" si="12"/>
         <v>8.180938244253283E-2</v>
       </c>
     </row>
-    <row r="437" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H437">
+    <row r="438" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H438">
         <v>1.83</v>
       </c>
-      <c r="I437" s="53">
+      <c r="I438" s="53">
         <f t="shared" si="12"/>
         <v>8.1511079813719314E-2</v>
       </c>
     </row>
-    <row r="438" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H438">
+    <row r="439" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H439">
         <v>1.84</v>
       </c>
-      <c r="I438" s="53">
+      <c r="I439" s="53">
         <f t="shared" si="12"/>
         <v>8.1215481657123792E-2</v>
       </c>
     </row>
-    <row r="439" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H439">
+    <row r="440" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H440">
         <v>1.85</v>
       </c>
-      <c r="I439" s="53">
+      <c r="I440" s="53">
         <f t="shared" si="12"/>
         <v>8.0922548954093912E-2</v>
       </c>
     </row>
-    <row r="440" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H440">
+    <row r="441" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H441">
         <v>1.86</v>
       </c>
-      <c r="I440" s="53">
+      <c r="I441" s="53">
         <f t="shared" si="12"/>
         <v>8.063224345585504E-2</v>
       </c>
     </row>
-    <row r="441" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H441">
+    <row r="442" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H442">
         <v>1.87</v>
       </c>
-      <c r="I441" s="53">
+      <c r="I442" s="53">
         <f t="shared" si="12"/>
         <v>8.0344527664280296E-2</v>
       </c>
     </row>
-    <row r="442" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H442">
+    <row r="443" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H443">
         <v>1.88</v>
       </c>
-      <c r="I442" s="53">
+      <c r="I443" s="53">
         <f t="shared" si="12"/>
         <v>8.0059364813240996E-2</v>
       </c>
     </row>
-    <row r="443" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H443">
+    <row r="444" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H444">
         <v>1.89</v>
       </c>
-      <c r="I443" s="53">
+      <c r="I444" s="53">
         <f t="shared" si="12"/>
         <v>7.9776718850516348E-2</v>
       </c>
     </row>
-    <row r="444" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H444">
+    <row r="445" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H445">
         <v>1.9</v>
       </c>
-      <c r="I444" s="53">
+      <c r="I445" s="53">
         <f t="shared" si="12"/>
         <v>7.9496554420243656E-2</v>
       </c>
     </row>
-    <row r="445" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H445">
+    <row r="446" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H446">
         <v>1.91</v>
       </c>
-      <c r="I445" s="53">
+      <c r="I446" s="53">
         <f t="shared" si="12"/>
         <v>7.9218836845889234E-2</v>
       </c>
     </row>
-    <row r="446" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H446">
+    <row r="447" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H447">
         <v>1.92</v>
       </c>
-      <c r="I446" s="53">
+      <c r="I447" s="53">
         <f t="shared" si="12"/>
         <v>7.8943532113722584E-2</v>
       </c>
     </row>
-    <row r="447" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H447">
+    <row r="448" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H448">
         <v>1.93</v>
       </c>
-      <c r="I447" s="53">
+      <c r="I448" s="53">
         <f t="shared" si="12"/>
         <v>7.8670606856776112E-2</v>
       </c>
     </row>
-    <row r="448" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H448">
-        <v>1.94</v>
-      </c>
-      <c r="I448" s="53">
-        <f t="shared" ref="I448:I511" si="13">IF(H448&lt;$C$255/3,   ($C$256*$C$253/$C$257)*(1+(3*($C$254-1)*H448/$C$255)),   IF(H448&lt;=$C$255,   $C$256*$C$253*$C$254/$C$257,   $C$256*$C$253*$C$254/$C$257*($C$255/H448)^(2/3)   ))</f>
-        <v>7.8400028339273883E-2</v>
-      </c>
-    </row>
     <row r="449" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H449">
+        <v>1.94</v>
+      </c>
+      <c r="I449" s="53">
+        <f t="shared" ref="I449:I512" si="13">IF(H449&lt;$C$256/3,   ($C$257*$C$254/$C$258)*(1+(3*($C$255-1)*H449/$C$256)),   IF(H449&lt;=$C$256,   $C$257*$C$254*$C$255/$C$258,   $C$257*$C$254*$C$255/$C$258*($C$256/H449)^(2/3)   ))</f>
+        <v>7.8400028339273883E-2</v>
+      </c>
+    </row>
+    <row r="450" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H450">
         <v>1.95</v>
       </c>
-      <c r="I449" s="53">
+      <c r="I450" s="53">
         <f t="shared" si="13"/>
         <v>7.8131764441513082E-2</v>
       </c>
     </row>
-    <row r="450" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H450">
+    <row r="451" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H451">
         <v>1.96</v>
       </c>
-      <c r="I450" s="53">
+      <c r="I451" s="53">
         <f t="shared" si="13"/>
         <v>7.7865783645183179E-2</v>
       </c>
     </row>
-    <row r="451" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H451">
+    <row r="452" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H452">
         <v>1.97</v>
       </c>
-      <c r="I451" s="53">
+      <c r="I452" s="53">
         <f t="shared" si="13"/>
         <v>7.7602055019107566E-2</v>
       </c>
     </row>
-    <row r="452" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H452">
+    <row r="453" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H453">
         <v>1.98</v>
       </c>
-      <c r="I452" s="53">
+      <c r="I453" s="53">
         <f t="shared" si="13"/>
         <v>7.7340548205393655E-2</v>
       </c>
     </row>
-    <row r="453" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H453">
+    <row r="454" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H454">
         <v>1.99</v>
       </c>
-      <c r="I453" s="53">
+      <c r="I454" s="53">
         <f t="shared" si="13"/>
         <v>7.708123340597775E-2</v>
       </c>
     </row>
-    <row r="454" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H454">
+    <row r="455" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H455">
         <v>2</v>
       </c>
-      <c r="I454" s="53">
+      <c r="I455" s="53">
         <f t="shared" si="13"/>
         <v>7.6824081369551406E-2</v>
       </c>
     </row>
-    <row r="455" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H455">
+    <row r="456" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H456">
         <v>2.0099999999999998</v>
       </c>
-      <c r="I455" s="53">
+      <c r="I456" s="53">
         <f t="shared" si="13"/>
         <v>7.6569063378856717E-2</v>
       </c>
     </row>
-    <row r="456" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H456">
+    <row r="457" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H457">
         <v>2.02</v>
       </c>
-      <c r="I456" s="53">
+      <c r="I457" s="53">
         <f t="shared" si="13"/>
         <v>7.6316151238338195E-2</v>
       </c>
     </row>
-    <row r="457" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H457">
+    <row r="458" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H458">
         <v>2.0299999999999998</v>
       </c>
-      <c r="I457" s="53">
+      <c r="I458" s="53">
         <f t="shared" si="13"/>
         <v>7.6065317262139873E-2</v>
       </c>
     </row>
-    <row r="458" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H458">
+    <row r="459" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H459">
         <v>2.04</v>
       </c>
-      <c r="I458" s="53">
+      <c r="I459" s="53">
         <f t="shared" si="13"/>
         <v>7.5816534262435717E-2</v>
       </c>
     </row>
-    <row r="459" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H459">
+    <row r="460" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H460">
         <v>2.0499999999999998</v>
       </c>
-      <c r="I459" s="53">
+      <c r="I460" s="53">
         <f t="shared" si="13"/>
         <v>7.5569775538083292E-2</v>
       </c>
     </row>
-    <row r="460" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H460">
+    <row r="461" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H461">
         <v>2.06</v>
       </c>
-      <c r="I460" s="53">
+      <c r="I461" s="53">
         <f t="shared" si="13"/>
         <v>7.532501486358946E-2</v>
       </c>
     </row>
-    <row r="461" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H461">
+    <row r="462" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H462">
         <v>2.0699999999999998</v>
       </c>
-      <c r="I461" s="53">
+      <c r="I462" s="53">
         <f t="shared" si="13"/>
         <v>7.5082226478378589E-2</v>
       </c>
     </row>
-    <row r="462" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H462">
+    <row r="463" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H463">
         <v>2.08</v>
       </c>
-      <c r="I462" s="53">
+      <c r="I463" s="53">
         <f t="shared" si="13"/>
         <v>7.4841385076353351E-2</v>
       </c>
     </row>
-    <row r="463" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H463">
+    <row r="464" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H464">
         <v>2.09</v>
       </c>
-      <c r="I463" s="53">
+      <c r="I464" s="53">
         <f t="shared" si="13"/>
         <v>7.4602465795738634E-2</v>
       </c>
     </row>
-    <row r="464" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H464">
+    <row r="465" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H465">
         <v>2.1</v>
       </c>
-      <c r="I464" s="53">
+      <c r="I465" s="53">
         <f t="shared" si="13"/>
         <v>7.436544420919991E-2</v>
       </c>
     </row>
-    <row r="465" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H465">
+    <row r="466" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H466">
         <v>2.11</v>
       </c>
-      <c r="I465" s="53">
+      <c r="I466" s="53">
         <f t="shared" si="13"/>
         <v>7.4130296314227115E-2</v>
       </c>
     </row>
-    <row r="466" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H466">
+    <row r="467" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H467">
         <v>2.12</v>
       </c>
-      <c r="I466" s="53">
+      <c r="I467" s="53">
         <f t="shared" si="13"/>
         <v>7.3896998523775778E-2</v>
       </c>
     </row>
-    <row r="467" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H467">
+    <row r="468" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H468">
         <v>2.13</v>
       </c>
-      <c r="I467" s="53">
+      <c r="I468" s="53">
         <f t="shared" si="13"/>
         <v>7.3665527657157295E-2</v>
       </c>
     </row>
-    <row r="468" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H468">
+    <row r="469" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H469">
         <v>2.14</v>
       </c>
-      <c r="I468" s="53">
+      <c r="I469" s="53">
         <f t="shared" si="13"/>
         <v>7.3435860931170702E-2</v>
       </c>
     </row>
-    <row r="469" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H469">
+    <row r="470" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H470">
         <v>2.15</v>
       </c>
-      <c r="I469" s="53">
+      <c r="I470" s="53">
         <f t="shared" si="13"/>
         <v>7.3207975951468302E-2</v>
       </c>
     </row>
-    <row r="470" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H470">
+    <row r="471" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H471">
         <v>2.16</v>
       </c>
-      <c r="I470" s="53">
+      <c r="I471" s="53">
         <f t="shared" si="13"/>
         <v>7.2981850704147921E-2</v>
       </c>
     </row>
-    <row r="471" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H471">
+    <row r="472" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H472">
         <v>2.17</v>
       </c>
-      <c r="I471" s="53">
+      <c r="I472" s="53">
         <f t="shared" si="13"/>
         <v>7.2757463547565099E-2</v>
       </c>
     </row>
-    <row r="472" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H472">
+    <row r="473" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H473">
         <v>2.1800000000000002</v>
       </c>
-      <c r="I472" s="53">
+      <c r="I473" s="53">
         <f t="shared" si="13"/>
         <v>7.2534793204358031E-2</v>
       </c>
     </row>
-    <row r="473" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H473">
+    <row r="474" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H474">
         <v>2.19</v>
       </c>
-      <c r="I473" s="53">
+      <c r="I474" s="53">
         <f t="shared" si="13"/>
         <v>7.231381875367919E-2</v>
       </c>
     </row>
-    <row r="474" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H474">
+    <row r="475" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H475">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I474" s="53">
+      <c r="I475" s="53">
         <f t="shared" si="13"/>
         <v>7.2094519623627146E-2</v>
       </c>
     </row>
-    <row r="475" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H475">
+    <row r="476" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H476">
         <v>2.21</v>
       </c>
-      <c r="I475" s="53">
+      <c r="I476" s="53">
         <f t="shared" si="13"/>
         <v>7.1876875583872596E-2</v>
       </c>
     </row>
-    <row r="476" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H476">
+    <row r="477" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H477">
         <v>2.2200000000000002</v>
       </c>
-      <c r="I476" s="53">
+      <c r="I477" s="53">
         <f t="shared" si="13"/>
         <v>7.1660866738472703E-2</v>
       </c>
     </row>
-    <row r="477" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H477">
+    <row r="478" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H478">
         <v>2.23</v>
       </c>
-      <c r="I477" s="53">
+      <c r="I478" s="53">
         <f t="shared" si="13"/>
         <v>7.1446473518868236E-2</v>
       </c>
     </row>
-    <row r="478" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H478">
+    <row r="479" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H479">
         <v>2.2400000000000002</v>
       </c>
-      <c r="I478" s="53">
+      <c r="I479" s="53">
         <f t="shared" si="13"/>
         <v>7.123367667705803E-2</v>
       </c>
     </row>
-    <row r="479" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H479">
+    <row r="480" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H480">
         <v>2.25</v>
       </c>
-      <c r="I479" s="53">
+      <c r="I480" s="53">
         <f t="shared" si="13"/>
         <v>7.1022457278945364E-2</v>
       </c>
     </row>
-    <row r="480" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H480">
+    <row r="481" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H481">
         <v>2.2599999999999998</v>
       </c>
-      <c r="I480" s="53">
+      <c r="I481" s="53">
         <f t="shared" si="13"/>
         <v>7.0812796697851343E-2</v>
       </c>
     </row>
-    <row r="481" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H481">
+    <row r="482" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H482">
         <v>2.27</v>
       </c>
-      <c r="I481" s="53">
+      <c r="I482" s="53">
         <f t="shared" si="13"/>
         <v>7.0604676608190434E-2</v>
       </c>
     </row>
-    <row r="482" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H482">
+    <row r="483" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H483">
         <v>2.2799999999999998</v>
       </c>
-      <c r="I482" s="53">
+      <c r="I483" s="53">
         <f t="shared" si="13"/>
         <v>7.0398078979303086E-2</v>
       </c>
     </row>
-    <row r="483" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H483">
+    <row r="484" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H484">
         <v>2.29</v>
       </c>
-      <c r="I483" s="53">
+      <c r="I484" s="53">
         <f t="shared" si="13"/>
         <v>7.0192986069441285E-2</v>
       </c>
     </row>
-    <row r="484" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H484">
+    <row r="485" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H485">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I484" s="53">
+      <c r="I485" s="53">
         <f t="shared" si="13"/>
         <v>6.9989380419902256E-2</v>
       </c>
     </row>
-    <row r="485" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H485">
+    <row r="486" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H486">
         <v>2.31</v>
       </c>
-      <c r="I485" s="53">
+      <c r="I486" s="53">
         <f t="shared" si="13"/>
         <v>6.9787244849306276E-2</v>
       </c>
     </row>
-    <row r="486" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H486">
+    <row r="487" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H487">
         <v>2.3199999999999998</v>
       </c>
-      <c r="I486" s="53">
+      <c r="I487" s="53">
         <f t="shared" si="13"/>
         <v>6.9586562448014339E-2</v>
       </c>
     </row>
-    <row r="487" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H487">
+    <row r="488" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H488">
         <v>2.33</v>
       </c>
-      <c r="I487" s="53">
+      <c r="I488" s="53">
         <f t="shared" si="13"/>
         <v>6.9387316572681504E-2</v>
       </c>
     </row>
-    <row r="488" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H488">
+    <row r="489" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H489">
         <v>2.34</v>
       </c>
-      <c r="I488" s="53">
+      <c r="I489" s="53">
         <f t="shared" si="13"/>
         <v>6.91894908409426E-2</v>
       </c>
     </row>
-    <row r="489" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H489">
+    <row r="490" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H490">
         <v>2.35</v>
       </c>
-      <c r="I489" s="53">
+      <c r="I490" s="53">
         <f t="shared" si="13"/>
         <v>6.8993069126225728E-2</v>
       </c>
     </row>
-    <row r="490" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H490">
+    <row r="491" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H491">
         <v>2.36</v>
       </c>
-      <c r="I490" s="53">
+      <c r="I491" s="53">
         <f t="shared" si="13"/>
         <v>6.8798035552690887E-2</v>
       </c>
     </row>
-    <row r="491" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H491">
+    <row r="492" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H492">
         <v>2.37</v>
       </c>
-      <c r="I491" s="53">
+      <c r="I492" s="53">
         <f t="shared" si="13"/>
         <v>6.8604374490289111E-2</v>
       </c>
     </row>
-    <row r="492" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H492">
+    <row r="493" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H493">
         <v>2.38</v>
       </c>
-      <c r="I492" s="53">
+      <c r="I493" s="53">
         <f t="shared" si="13"/>
         <v>6.8412070549939946E-2</v>
       </c>
     </row>
-    <row r="493" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H493">
+    <row r="494" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H494">
         <v>2.39</v>
       </c>
-      <c r="I493" s="53">
+      <c r="I494" s="53">
         <f t="shared" si="13"/>
         <v>6.8221108578822798E-2</v>
       </c>
     </row>
-    <row r="494" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H494">
+    <row r="495" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H495">
         <v>2.4</v>
       </c>
-      <c r="I494" s="53">
+      <c r="I495" s="53">
         <f t="shared" si="13"/>
         <v>6.8031473655779995E-2</v>
       </c>
     </row>
-    <row r="495" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H495">
+    <row r="496" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H496">
         <v>2.41</v>
       </c>
-      <c r="I495" s="53">
+      <c r="I496" s="53">
         <f t="shared" si="13"/>
         <v>6.7843151086827647E-2</v>
       </c>
     </row>
-    <row r="496" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H496">
+    <row r="497" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H497">
         <v>2.42</v>
       </c>
-      <c r="I496" s="53">
+      <c r="I497" s="53">
         <f t="shared" si="13"/>
         <v>6.7656126400771982E-2</v>
       </c>
     </row>
-    <row r="497" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H497">
+    <row r="498" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H498">
         <v>2.4300000000000002</v>
       </c>
-      <c r="I497" s="53">
+      <c r="I498" s="53">
         <f t="shared" si="13"/>
         <v>6.7470385344927691E-2</v>
       </c>
     </row>
-    <row r="498" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H498">
+    <row r="499" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H499">
         <v>2.44</v>
       </c>
-      <c r="I498" s="53">
+      <c r="I499" s="53">
         <f t="shared" si="13"/>
         <v>6.7285913880936132E-2</v>
       </c>
     </row>
-    <row r="499" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H499">
+    <row r="500" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H500">
         <v>2.4500000000000002</v>
       </c>
-      <c r="I499" s="53">
+      <c r="I500" s="53">
         <f t="shared" si="13"/>
         <v>6.7102698180679973E-2</v>
       </c>
     </row>
-    <row r="500" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H500">
+    <row r="501" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H501">
         <v>2.46</v>
       </c>
-      <c r="I500" s="53">
+      <c r="I501" s="53">
         <f t="shared" si="13"/>
         <v>6.6920724622292219E-2</v>
       </c>
     </row>
-    <row r="501" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H501">
+    <row r="502" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H502">
         <v>2.4700000000000002</v>
       </c>
-      <c r="I501" s="53">
+      <c r="I502" s="53">
         <f t="shared" si="13"/>
         <v>6.6739979786256801E-2</v>
       </c>
     </row>
-    <row r="502" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H502">
+    <row r="503" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H503">
         <v>2.48</v>
       </c>
-      <c r="I502" s="53">
+      <c r="I503" s="53">
         <f t="shared" si="13"/>
         <v>6.6560450451598294E-2</v>
       </c>
     </row>
-    <row r="503" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H503">
+    <row r="504" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H504">
         <v>2.4900000000000002</v>
       </c>
-      <c r="I503" s="53">
+      <c r="I504" s="53">
         <f t="shared" si="13"/>
         <v>6.6382123592158546E-2</v>
       </c>
     </row>
-    <row r="504" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H504">
+    <row r="505" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H505">
         <v>2.5</v>
       </c>
-      <c r="I504" s="53">
+      <c r="I505" s="53">
         <f t="shared" si="13"/>
         <v>6.6204986372957478E-2</v>
       </c>
     </row>
-    <row r="505" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H505">
+    <row r="506" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H506">
         <v>2.5099999999999998</v>
       </c>
-      <c r="I505" s="53">
+      <c r="I506" s="53">
         <f t="shared" si="13"/>
         <v>6.6029026146636471E-2</v>
       </c>
     </row>
-    <row r="506" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H506">
+    <row r="507" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H507">
         <v>2.52</v>
       </c>
-      <c r="I506" s="53">
+      <c r="I507" s="53">
         <f t="shared" si="13"/>
         <v>6.5854230449981385E-2</v>
       </c>
     </row>
-    <row r="507" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H507">
+    <row r="508" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H508">
         <v>2.5299999999999998</v>
       </c>
-      <c r="I507" s="53">
+      <c r="I508" s="53">
         <f t="shared" si="13"/>
         <v>6.5680587000523913E-2</v>
       </c>
     </row>
-    <row r="508" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H508">
+    <row r="509" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H509">
         <v>2.54</v>
       </c>
-      <c r="I508" s="53">
+      <c r="I509" s="53">
         <f t="shared" si="13"/>
         <v>6.5508083693218408E-2</v>
       </c>
     </row>
-    <row r="509" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H509">
+    <row r="510" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H510">
         <v>2.5499999999999998</v>
       </c>
-      <c r="I509" s="53">
+      <c r="I510" s="53">
         <f t="shared" si="13"/>
         <v>6.5336708597192955E-2</v>
       </c>
     </row>
-    <row r="510" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H510">
+    <row r="511" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H511">
         <v>2.56</v>
       </c>
-      <c r="I510" s="53">
+      <c r="I511" s="53">
         <f t="shared" si="13"/>
         <v>6.5166449952572161E-2</v>
       </c>
     </row>
-    <row r="511" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H511">
+    <row r="512" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H512">
         <v>2.57</v>
       </c>
-      <c r="I511" s="53">
+      <c r="I512" s="53">
         <f t="shared" si="13"/>
         <v>6.4997296167370169E-2</v>
       </c>
     </row>
-    <row r="512" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H512">
-        <v>2.58</v>
-      </c>
-      <c r="I512" s="53">
-        <f t="shared" ref="I512:I554" si="14">IF(H512&lt;$C$255/3,   ($C$256*$C$253/$C$257)*(1+(3*($C$254-1)*H512/$C$255)),   IF(H512&lt;=$C$255,   $C$256*$C$253*$C$254/$C$257,   $C$256*$C$253*$C$254/$C$257*($C$255/H512)^(2/3)   ))</f>
-        <v>6.4829235814451935E-2</v>
-      </c>
-    </row>
     <row r="513" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H513">
+        <v>2.58</v>
+      </c>
+      <c r="I513" s="53">
+        <f t="shared" ref="I513:I555" si="14">IF(H513&lt;$C$256/3,   ($C$257*$C$254/$C$258)*(1+(3*($C$255-1)*H513/$C$256)),   IF(H513&lt;=$C$256,   $C$257*$C$254*$C$255/$C$258,   $C$257*$C$254*$C$255/$C$258*($C$256/H513)^(2/3)   ))</f>
+        <v>6.4829235814451935E-2</v>
+      </c>
+    </row>
+    <row r="514" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H514">
         <v>2.59</v>
       </c>
-      <c r="I513" s="53">
+      <c r="I514" s="53">
         <f t="shared" si="14"/>
         <v>6.4662257628560982E-2</v>
       </c>
     </row>
-    <row r="514" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H514">
+    <row r="515" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H515">
         <v>2.6</v>
       </c>
-      <c r="I514" s="53">
+      <c r="I515" s="53">
         <f t="shared" si="14"/>
         <v>6.449635050341207E-2</v>
       </c>
     </row>
-    <row r="515" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H515">
+    <row r="516" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H516">
         <v>2.61</v>
       </c>
-      <c r="I515" s="53">
+      <c r="I516" s="53">
         <f t="shared" si="14"/>
         <v>6.4331503488846975E-2</v>
       </c>
     </row>
-    <row r="516" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H516">
+    <row r="517" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H517">
         <v>2.62</v>
       </c>
-      <c r="I516" s="53">
+      <c r="I517" s="53">
         <f t="shared" si="14"/>
         <v>6.4167705788051782E-2</v>
       </c>
     </row>
-    <row r="517" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H517">
+    <row r="518" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H518">
         <v>2.63</v>
       </c>
-      <c r="I517" s="53">
+      <c r="I518" s="53">
         <f t="shared" si="14"/>
         <v>6.4004946754834202E-2</v>
       </c>
     </row>
-    <row r="518" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H518">
+    <row r="519" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H519">
         <v>2.64</v>
       </c>
-      <c r="I518" s="53">
+      <c r="I519" s="53">
         <f t="shared" si="14"/>
         <v>6.3843215890959426E-2</v>
       </c>
     </row>
-    <row r="519" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H519">
+    <row r="520" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H520">
         <v>2.65</v>
       </c>
-      <c r="I519" s="53">
+      <c r="I520" s="53">
         <f t="shared" si="14"/>
         <v>6.3682502843542974E-2</v>
       </c>
     </row>
-    <row r="520" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H520">
+    <row r="521" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H521">
         <v>2.66</v>
       </c>
-      <c r="I520" s="53">
+      <c r="I521" s="53">
         <f t="shared" si="14"/>
         <v>6.3522797402498971E-2</v>
       </c>
     </row>
-    <row r="521" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H521">
+    <row r="522" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H522">
         <v>2.67</v>
       </c>
-      <c r="I521" s="53">
+      <c r="I522" s="53">
         <f t="shared" si="14"/>
         <v>6.3364089498042855E-2</v>
       </c>
     </row>
-    <row r="522" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H522">
+    <row r="523" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H523">
         <v>2.68</v>
       </c>
-      <c r="I522" s="53">
+      <c r="I523" s="53">
         <f t="shared" si="14"/>
         <v>6.3206369198246654E-2</v>
       </c>
     </row>
-    <row r="523" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H523">
+    <row r="524" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H524">
         <v>2.69</v>
       </c>
-      <c r="I523" s="53">
+      <c r="I524" s="53">
         <f t="shared" si="14"/>
         <v>6.30496267066461E-2</v>
       </c>
     </row>
-    <row r="524" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H524">
+    <row r="525" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H525">
         <v>2.7</v>
       </c>
-      <c r="I524" s="53">
+      <c r="I525" s="53">
         <f t="shared" si="14"/>
         <v>6.2893852359897653E-2</v>
       </c>
     </row>
-    <row r="525" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H525">
+    <row r="526" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H526">
         <v>2.71</v>
       </c>
-      <c r="I525" s="53">
+      <c r="I526" s="53">
         <f t="shared" si="14"/>
         <v>6.2739036625484884E-2</v>
       </c>
     </row>
-    <row r="526" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H526">
+    <row r="527" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H527">
         <v>2.72</v>
       </c>
-      <c r="I526" s="53">
+      <c r="I527" s="53">
         <f t="shared" si="14"/>
         <v>6.2585170099472384E-2</v>
       </c>
     </row>
-    <row r="527" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H527">
+    <row r="528" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H528">
         <v>2.73</v>
       </c>
-      <c r="I527" s="53">
+      <c r="I528" s="53">
         <f t="shared" si="14"/>
         <v>6.2432243504306546E-2</v>
       </c>
     </row>
-    <row r="528" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H528">
+    <row r="529" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H529">
         <v>2.74</v>
       </c>
-      <c r="I528" s="53">
+      <c r="I529" s="53">
         <f t="shared" si="14"/>
         <v>6.2280247686661676E-2</v>
       </c>
     </row>
-    <row r="529" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H529">
+    <row r="530" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H530">
         <v>2.75</v>
       </c>
-      <c r="I529" s="53">
+      <c r="I530" s="53">
         <f t="shared" si="14"/>
         <v>6.2129173615330699E-2</v>
       </c>
     </row>
-    <row r="530" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H530">
+    <row r="531" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H531">
         <v>2.76</v>
       </c>
-      <c r="I530" s="53">
+      <c r="I531" s="53">
         <f t="shared" si="14"/>
         <v>6.1979012379158996E-2</v>
       </c>
     </row>
-    <row r="531" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H531">
+    <row r="532" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H532">
         <v>2.77</v>
       </c>
-      <c r="I531" s="53">
+      <c r="I532" s="53">
         <f t="shared" si="14"/>
         <v>6.18297551850207E-2</v>
       </c>
     </row>
-    <row r="532" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H532">
+    <row r="533" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H533">
         <v>2.78</v>
       </c>
-      <c r="I532" s="53">
+      <c r="I533" s="53">
         <f t="shared" si="14"/>
         <v>6.1681393355836216E-2</v>
       </c>
     </row>
-    <row r="533" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H533">
+    <row r="534" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H534">
         <v>2.79</v>
       </c>
-      <c r="I533" s="53">
+      <c r="I534" s="53">
         <f t="shared" si="14"/>
         <v>6.153391832862997E-2</v>
       </c>
     </row>
-    <row r="534" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H534">
+    <row r="535" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H535">
         <v>2.8</v>
       </c>
-      <c r="I534" s="53">
+      <c r="I535" s="53">
         <f t="shared" si="14"/>
         <v>6.1387321652627579E-2</v>
       </c>
     </row>
-    <row r="535" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H535">
+    <row r="536" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H536">
         <v>2.81</v>
       </c>
-      <c r="I535" s="53">
+      <c r="I536" s="53">
         <f t="shared" si="14"/>
         <v>6.1241594987391366E-2</v>
       </c>
     </row>
-    <row r="536" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H536">
+    <row r="537" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H537">
         <v>2.82</v>
       </c>
-      <c r="I536" s="53">
+      <c r="I537" s="53">
         <f t="shared" si="14"/>
         <v>6.1096730100993361E-2</v>
       </c>
     </row>
-    <row r="537" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H537">
+    <row r="538" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H538">
         <v>2.83</v>
       </c>
-      <c r="I537" s="53">
+      <c r="I538" s="53">
         <f t="shared" si="14"/>
         <v>6.0952718868224912E-2</v>
       </c>
     </row>
-    <row r="538" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H538">
+    <row r="539" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H539">
         <v>2.84</v>
       </c>
-      <c r="I538" s="53">
+      <c r="I539" s="53">
         <f t="shared" si="14"/>
         <v>6.0809553268842097E-2</v>
       </c>
     </row>
-    <row r="539" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H539">
+    <row r="540" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H540">
         <v>2.85</v>
       </c>
-      <c r="I539" s="53">
+      <c r="I540" s="53">
         <f t="shared" si="14"/>
         <v>6.0667225385845965E-2</v>
       </c>
     </row>
-    <row r="540" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H540">
+    <row r="541" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H541">
         <v>2.86</v>
       </c>
-      <c r="I540" s="53">
+      <c r="I541" s="53">
         <f t="shared" si="14"/>
         <v>6.0525727403796865E-2</v>
       </c>
     </row>
-    <row r="541" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H541">
+    <row r="542" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H542">
         <v>2.87</v>
       </c>
-      <c r="I541" s="53">
+      <c r="I542" s="53">
         <f t="shared" si="14"/>
         <v>6.0385051607162142E-2</v>
       </c>
     </row>
-    <row r="542" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H542">
+    <row r="543" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H543">
         <v>2.88</v>
       </c>
-      <c r="I542" s="53">
+      <c r="I543" s="53">
         <f t="shared" si="14"/>
         <v>6.0245190378696391E-2</v>
       </c>
     </row>
-    <row r="543" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H543">
+    <row r="544" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H544">
         <v>2.89</v>
       </c>
-      <c r="I543" s="53">
+      <c r="I544" s="53">
         <f t="shared" si="14"/>
         <v>6.0106136197853308E-2</v>
       </c>
     </row>
-    <row r="544" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H544">
+    <row r="545" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H545">
         <v>2.9</v>
       </c>
-      <c r="I544" s="53">
+      <c r="I545" s="53">
         <f t="shared" si="14"/>
         <v>5.9967881639228844E-2</v>
       </c>
     </row>
-    <row r="545" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H545">
+    <row r="546" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H546">
         <v>2.91</v>
       </c>
-      <c r="I545" s="53">
+      <c r="I546" s="53">
         <f t="shared" si="14"/>
         <v>5.9830419371034442E-2</v>
       </c>
     </row>
-    <row r="546" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H546">
+    <row r="547" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H547">
         <v>2.92</v>
       </c>
-      <c r="I546" s="53">
+      <c r="I547" s="53">
         <f t="shared" si="14"/>
         <v>5.9693742153600148E-2</v>
       </c>
     </row>
-    <row r="547" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H547">
+    <row r="548" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H548">
         <v>2.93</v>
       </c>
-      <c r="I547" s="53">
+      <c r="I548" s="53">
         <f t="shared" si="14"/>
         <v>5.9557842837906549E-2</v>
       </c>
     </row>
-    <row r="548" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H548">
+    <row r="549" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H549">
         <v>2.94</v>
       </c>
-      <c r="I548" s="53">
+      <c r="I549" s="53">
         <f t="shared" si="14"/>
         <v>5.9422714364145E-2</v>
       </c>
     </row>
-    <row r="549" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H549">
+    <row r="550" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H550">
         <v>2.95</v>
       </c>
-      <c r="I549" s="53">
+      <c r="I550" s="53">
         <f t="shared" si="14"/>
         <v>5.9288349760305649E-2</v>
       </c>
     </row>
-    <row r="550" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H550">
+    <row r="551" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H551">
         <v>2.96</v>
       </c>
-      <c r="I550" s="53">
+      <c r="I551" s="53">
         <f t="shared" si="14"/>
         <v>5.9154742140792402E-2</v>
       </c>
     </row>
-    <row r="551" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H551">
+    <row r="552" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H552">
         <v>2.97</v>
       </c>
-      <c r="I551" s="53">
+      <c r="I552" s="53">
         <f t="shared" si="14"/>
         <v>5.9021884705064413E-2</v>
       </c>
     </row>
-    <row r="552" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H552">
+    <row r="553" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H553">
         <v>2.98</v>
       </c>
-      <c r="I552" s="53">
+      <c r="I553" s="53">
         <f t="shared" si="14"/>
         <v>5.8889770736303346E-2</v>
       </c>
     </row>
-    <row r="553" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H553">
+    <row r="554" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H554">
         <v>2.99</v>
       </c>
-      <c r="I553" s="53">
+      <c r="I554" s="53">
         <f t="shared" si="14"/>
         <v>5.8758393600105874E-2</v>
       </c>
     </row>
-    <row r="554" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H554">
+    <row r="555" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H555">
         <v>3</v>
       </c>
-      <c r="I554" s="53">
+      <c r="I555" s="53">
         <f t="shared" si="14"/>
         <v>5.8627746743201051E-2</v>
       </c>
@@ -14005,11 +14044,11 @@
     <mergeCell ref="AL8:AM8"/>
     <mergeCell ref="AL9:AM9"/>
     <mergeCell ref="F127:G127"/>
-    <mergeCell ref="K237:L237"/>
+    <mergeCell ref="K238:L238"/>
     <mergeCell ref="B173:L173"/>
     <mergeCell ref="E174:G174"/>
     <mergeCell ref="K174:L174"/>
-    <mergeCell ref="H223:J223"/>
+    <mergeCell ref="H224:J224"/>
     <mergeCell ref="C10:E10"/>
   </mergeCells>
   <dataValidations count="4">
